--- a/research/traditional_assets/database/data/turkey/turkey_recreation.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_kstur" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,70 +590,73 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.5186615186615187</v>
+        <v>0.2175531914893617</v>
       </c>
       <c r="H2">
-        <v>-0.5186615186615187</v>
+        <v>0.2175531914893617</v>
       </c>
       <c r="I2">
-        <v>-0.6705276705276705</v>
+        <v>0.2037234042553192</v>
       </c>
       <c r="J2">
-        <v>-0.6705276705276705</v>
+        <v>0.1816958111702128</v>
       </c>
       <c r="K2">
-        <v>0.242</v>
+        <v>1.43</v>
       </c>
       <c r="L2">
-        <v>0.3114543114543115</v>
+        <v>0.7606382978723404</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9285600000000001</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01168</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6493426573426574</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.9285600000000001</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01168</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.6493426573426574</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>2.28</v>
+        <v>1.14</v>
       </c>
       <c r="V2">
-        <v>0.02787286063569682</v>
+        <v>0.01433962264150943</v>
       </c>
       <c r="W2">
-        <v>0.03666666666666667</v>
+        <v>0.2628676470588235</v>
       </c>
       <c r="X2">
-        <v>0.111817679438425</v>
+        <v>0.2083305570732299</v>
       </c>
       <c r="Y2">
-        <v>-0.07515101277175834</v>
+        <v>0.05453708998559353</v>
       </c>
       <c r="Z2">
-        <v>0.253921568627451</v>
+        <v>0.5949367088607593</v>
       </c>
       <c r="AA2">
-        <v>-0.1702614379084968</v>
+        <v>0.1080975079113924</v>
       </c>
       <c r="AB2">
-        <v>0.111817679438425</v>
+        <v>0.2083305570732299</v>
       </c>
       <c r="AC2">
-        <v>-0.2820791173469218</v>
+        <v>-0.1002330491618376</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-2.28</v>
+        <v>-1.14</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -672,28 +677,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.02867203219315895</v>
+        <v>-0.01454823889739663</v>
       </c>
       <c r="AK2">
-        <v>-0.721518987341772</v>
+        <v>-0.5302325581395347</v>
       </c>
       <c r="AL2">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="AM2">
-        <v>-0.016</v>
+        <v>-0.324</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>-65.125</v>
+        <v>31.91666666666667</v>
       </c>
       <c r="AP2">
-        <v>7.450980392156862</v>
+        <v>-2.289156626506024</v>
       </c>
       <c r="AQ2">
-        <v>32.5625</v>
+        <v>-1.182098765432099</v>
       </c>
     </row>
     <row r="3">
@@ -713,70 +718,73 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.5186615186615187</v>
+        <v>0.2175531914893617</v>
       </c>
       <c r="H3">
-        <v>-0.5186615186615187</v>
+        <v>0.2175531914893617</v>
       </c>
       <c r="I3">
-        <v>-0.6705276705276705</v>
+        <v>0.2037234042553192</v>
       </c>
       <c r="J3">
-        <v>-0.6705276705276705</v>
+        <v>0.1816958111702128</v>
       </c>
       <c r="K3">
-        <v>0.242</v>
+        <v>1.43</v>
       </c>
       <c r="L3">
-        <v>0.3114543114543115</v>
+        <v>0.7606382978723404</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.9285600000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01168</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6493426573426574</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.9285600000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01168</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6493426573426574</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2.28</v>
+        <v>1.14</v>
       </c>
       <c r="V3">
-        <v>0.02787286063569682</v>
+        <v>0.01433962264150943</v>
       </c>
       <c r="W3">
-        <v>0.03666666666666667</v>
+        <v>0.2628676470588235</v>
       </c>
       <c r="X3">
-        <v>0.111817679438425</v>
+        <v>0.2083305570732299</v>
       </c>
       <c r="Y3">
-        <v>-0.07515101277175834</v>
+        <v>0.05453708998559353</v>
       </c>
       <c r="Z3">
-        <v>0.253921568627451</v>
+        <v>0.5949367088607593</v>
       </c>
       <c r="AA3">
-        <v>-0.1702614379084968</v>
+        <v>0.1080975079113924</v>
       </c>
       <c r="AB3">
-        <v>0.111817679438425</v>
+        <v>0.2083305570732299</v>
       </c>
       <c r="AC3">
-        <v>-0.2820791173469218</v>
+        <v>-0.1002330491618376</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -788,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.28</v>
+        <v>-1.14</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -797,28 +805,8740 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02867203219315895</v>
+        <v>-0.01454823889739663</v>
       </c>
       <c r="AK3">
-        <v>-0.721518987341772</v>
+        <v>-0.5302325581395347</v>
       </c>
       <c r="AL3">
-        <v>0.008</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>-0.016</v>
+        <v>-0.324</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>-65.125</v>
+        <v>31.91666666666667</v>
       </c>
       <c r="AP3">
-        <v>7.450980392156862</v>
+        <v>-2.289156626506024</v>
       </c>
       <c r="AQ3">
-        <v>32.5625</v>
+        <v>-1.182098765432099</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kustur Kusadasi Turizm Endüstrisi A.S. (IBSE:KSTUR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:KSTUR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.02</v>
+      </c>
+      <c r="G2">
+        <v>79.5</v>
+      </c>
+      <c r="H2">
+        <v>78.2117470861794</v>
+      </c>
+      <c r="I2">
+        <v>78.36</v>
+      </c>
+      <c r="J2">
+        <v>78.6617470861794</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1.59</v>
+      </c>
+      <c r="M2">
+        <v>0.20833055707323</v>
+      </c>
+      <c r="N2">
+        <v>0.207680236510693</v>
+      </c>
+      <c r="O2">
+        <v>0.106510603211009</v>
+      </c>
+      <c r="P2">
+        <v>0.045276</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.20833055707323</v>
+      </c>
+      <c r="T2">
+        <v>0.210994608684381</v>
+      </c>
+      <c r="U2">
+        <v>0.989537804842511</v>
+      </c>
+      <c r="V2">
+        <v>1.00508768463289</v>
+      </c>
+      <c r="W2">
+        <v>4.096607196337654</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>79.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1383254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.498</v>
+      </c>
+      <c r="AH2">
+        <v>0.115</v>
+      </c>
+      <c r="AI2">
+        <v>0.253</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.012</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>1.14</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2083305570732299</v>
+      </c>
+      <c r="C2">
+        <v>79.5</v>
+      </c>
+      <c r="D2">
+        <v>78.36</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.14</v>
+      </c>
+      <c r="H2">
+        <v>79.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.498</v>
+      </c>
+      <c r="K2">
+        <v>0.115</v>
+      </c>
+      <c r="L2">
+        <v>0.383</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.383</v>
+      </c>
+      <c r="O2">
+        <v>0.08809</v>
+      </c>
+      <c r="P2">
+        <v>0.29491</v>
+      </c>
+      <c r="Q2">
+        <v>0.40991</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2083305570732299</v>
+      </c>
+      <c r="T2">
+        <v>0.9895378048425111</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2079461067919615</v>
+      </c>
+      <c r="C3">
+        <v>78.88310356153951</v>
+      </c>
+      <c r="D3">
+        <v>78.53810356153951</v>
+      </c>
+      <c r="E3">
+        <v>0.795</v>
+      </c>
+      <c r="F3">
+        <v>0.795</v>
+      </c>
+      <c r="G3">
+        <v>1.14</v>
+      </c>
+      <c r="H3">
+        <v>79.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.498</v>
+      </c>
+      <c r="K3">
+        <v>0.115</v>
+      </c>
+      <c r="L3">
+        <v>0.383</v>
+      </c>
+      <c r="M3">
+        <v>0.0406245</v>
+      </c>
+      <c r="N3">
+        <v>0.3423755</v>
+      </c>
+      <c r="O3">
+        <v>0.078746365</v>
+      </c>
+      <c r="P3">
+        <v>0.263629135</v>
+      </c>
+      <c r="Q3">
+        <v>0.378629135</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2096491280726884</v>
+      </c>
+      <c r="T3">
+        <v>0.9972342099912863</v>
+      </c>
+      <c r="U3">
+        <v>0.0511</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.039347</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>9.427808342256521</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2076802365106931</v>
+      </c>
+      <c r="C4">
+        <v>78.21174708617939</v>
+      </c>
+      <c r="D4">
+        <v>78.66174708617939</v>
+      </c>
+      <c r="E4">
+        <v>1.59</v>
+      </c>
+      <c r="F4">
+        <v>1.59</v>
+      </c>
+      <c r="G4">
+        <v>1.14</v>
+      </c>
+      <c r="H4">
+        <v>79.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.498</v>
+      </c>
+      <c r="K4">
+        <v>0.115</v>
+      </c>
+      <c r="L4">
+        <v>0.383</v>
+      </c>
+      <c r="M4">
+        <v>0.09349200000000002</v>
+      </c>
+      <c r="N4">
+        <v>0.289508</v>
+      </c>
+      <c r="O4">
+        <v>0.06658683999999999</v>
+      </c>
+      <c r="P4">
+        <v>0.22292116</v>
+      </c>
+      <c r="Q4">
+        <v>0.33792116</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2109946086843807</v>
+      </c>
+      <c r="T4">
+        <v>1.005087684632894</v>
+      </c>
+      <c r="U4">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.045276</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>4.096607196337654</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2110010215752625</v>
+      </c>
+      <c r="C5">
+        <v>75.89980628938768</v>
+      </c>
+      <c r="D5">
+        <v>77.14480628938769</v>
+      </c>
+      <c r="E5">
+        <v>2.385</v>
+      </c>
+      <c r="F5">
+        <v>2.385</v>
+      </c>
+      <c r="G5">
+        <v>1.14</v>
+      </c>
+      <c r="H5">
+        <v>79.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.498</v>
+      </c>
+      <c r="K5">
+        <v>0.115</v>
+      </c>
+      <c r="L5">
+        <v>0.383</v>
+      </c>
+      <c r="M5">
+        <v>0.4688909999999999</v>
+      </c>
+      <c r="N5">
+        <v>-0.08589099999999994</v>
+      </c>
+      <c r="O5">
+        <v>-0.01975492999999998</v>
+      </c>
+      <c r="P5">
+        <v>-0.06613606999999996</v>
+      </c>
+      <c r="Q5">
+        <v>0.04886393000000003</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.212588733906936</v>
+      </c>
+      <c r="T5">
+        <v>1.014392480184825</v>
+      </c>
+      <c r="U5">
+        <v>0.1966</v>
+      </c>
+      <c r="V5">
+        <v>0.187868822391558</v>
+      </c>
+      <c r="W5">
+        <v>0.1596649895178197</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.8168209669198173</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2133438894197725</v>
+      </c>
+      <c r="C6">
+        <v>74.06930692801112</v>
+      </c>
+      <c r="D6">
+        <v>76.10930692801112</v>
+      </c>
+      <c r="E6">
+        <v>3.18</v>
+      </c>
+      <c r="F6">
+        <v>3.18</v>
+      </c>
+      <c r="G6">
+        <v>1.14</v>
+      </c>
+      <c r="H6">
+        <v>79.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.498</v>
+      </c>
+      <c r="K6">
+        <v>0.115</v>
+      </c>
+      <c r="L6">
+        <v>0.383</v>
+      </c>
+      <c r="M6">
+        <v>0.679884</v>
+      </c>
+      <c r="N6">
+        <v>-0.296884</v>
+      </c>
+      <c r="O6">
+        <v>-0.06828332000000001</v>
+      </c>
+      <c r="P6">
+        <v>-0.22860068</v>
+      </c>
+      <c r="Q6">
+        <v>-0.11360068</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2144791038898312</v>
+      </c>
+      <c r="T6">
+        <v>1.025426435334316</v>
+      </c>
+      <c r="U6">
+        <v>0.2138</v>
+      </c>
+      <c r="V6">
+        <v>0.1295662201199028</v>
+      </c>
+      <c r="W6">
+        <v>0.1860987421383648</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.5633313918256644</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2164358719720121</v>
+      </c>
+      <c r="C7">
+        <v>71.94952580991841</v>
+      </c>
+      <c r="D7">
+        <v>74.78452580991841</v>
+      </c>
+      <c r="E7">
+        <v>3.975</v>
+      </c>
+      <c r="F7">
+        <v>3.975</v>
+      </c>
+      <c r="G7">
+        <v>1.14</v>
+      </c>
+      <c r="H7">
+        <v>79.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.498</v>
+      </c>
+      <c r="K7">
+        <v>0.115</v>
+      </c>
+      <c r="L7">
+        <v>0.383</v>
+      </c>
+      <c r="M7">
+        <v>0.94923</v>
+      </c>
+      <c r="N7">
+        <v>-0.56623</v>
+      </c>
+      <c r="O7">
+        <v>-0.1302329</v>
+      </c>
+      <c r="P7">
+        <v>-0.4359971</v>
+      </c>
+      <c r="Q7">
+        <v>-0.3209971</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2164251813541868</v>
+      </c>
+      <c r="T7">
+        <v>1.036785551091248</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.09280153387482484</v>
+      </c>
+      <c r="W7">
+        <v>0.2166389937106918</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.4034849298905429</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2184358719720121</v>
+      </c>
+      <c r="C8">
+        <v>70.32190229225519</v>
+      </c>
+      <c r="D8">
+        <v>73.95190229225518</v>
+      </c>
+      <c r="E8">
+        <v>4.77</v>
+      </c>
+      <c r="F8">
+        <v>4.77</v>
+      </c>
+      <c r="G8">
+        <v>1.14</v>
+      </c>
+      <c r="H8">
+        <v>79.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.498</v>
+      </c>
+      <c r="K8">
+        <v>0.115</v>
+      </c>
+      <c r="L8">
+        <v>0.383</v>
+      </c>
+      <c r="M8">
+        <v>1.139076</v>
+      </c>
+      <c r="N8">
+        <v>-0.756076</v>
+      </c>
+      <c r="O8">
+        <v>-0.17389748</v>
+      </c>
+      <c r="P8">
+        <v>-0.58217852</v>
+      </c>
+      <c r="Q8">
+        <v>-0.46717852</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2183148109430612</v>
+      </c>
+      <c r="T8">
+        <v>1.047815184613495</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.07733461156235404</v>
+      </c>
+      <c r="W8">
+        <v>0.2203324947589099</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.3362374415754524</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.220435871972012</v>
+      </c>
+      <c r="C9">
+        <v>68.71261487766729</v>
+      </c>
+      <c r="D9">
+        <v>73.13761487766729</v>
+      </c>
+      <c r="E9">
+        <v>5.565</v>
+      </c>
+      <c r="F9">
+        <v>5.565</v>
+      </c>
+      <c r="G9">
+        <v>1.14</v>
+      </c>
+      <c r="H9">
+        <v>79.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.498</v>
+      </c>
+      <c r="K9">
+        <v>0.115</v>
+      </c>
+      <c r="L9">
+        <v>0.383</v>
+      </c>
+      <c r="M9">
+        <v>1.328922</v>
+      </c>
+      <c r="N9">
+        <v>-0.9459220000000002</v>
+      </c>
+      <c r="O9">
+        <v>-0.21756206</v>
+      </c>
+      <c r="P9">
+        <v>-0.7283599400000002</v>
+      </c>
+      <c r="Q9">
+        <v>-0.6133599400000002</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2202450777273951</v>
+      </c>
+      <c r="T9">
+        <v>1.059082014555576</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.06628680991058918</v>
+      </c>
+      <c r="W9">
+        <v>0.2229707097933513</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.2882035213503877</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2224358719720121</v>
+      </c>
+      <c r="C10">
+        <v>67.12106446415315</v>
+      </c>
+      <c r="D10">
+        <v>72.34106446415315</v>
+      </c>
+      <c r="E10">
+        <v>6.36</v>
+      </c>
+      <c r="F10">
+        <v>6.36</v>
+      </c>
+      <c r="G10">
+        <v>1.14</v>
+      </c>
+      <c r="H10">
+        <v>79.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.498</v>
+      </c>
+      <c r="K10">
+        <v>0.115</v>
+      </c>
+      <c r="L10">
+        <v>0.383</v>
+      </c>
+      <c r="M10">
+        <v>1.518768</v>
+      </c>
+      <c r="N10">
+        <v>-1.135768</v>
+      </c>
+      <c r="O10">
+        <v>-0.26122664</v>
+      </c>
+      <c r="P10">
+        <v>-0.87454136</v>
+      </c>
+      <c r="Q10">
+        <v>-0.7595413600000001</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2222173068331277</v>
+      </c>
+      <c r="T10">
+        <v>1.070593775583354</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.05800095867176554</v>
+      </c>
+      <c r="W10">
+        <v>0.2249493710691824</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.2521780811815892</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2244358719720121</v>
+      </c>
+      <c r="C11">
+        <v>65.54667776808333</v>
+      </c>
+      <c r="D11">
+        <v>71.56167776808333</v>
+      </c>
+      <c r="E11">
+        <v>7.154999999999999</v>
+      </c>
+      <c r="F11">
+        <v>7.154999999999999</v>
+      </c>
+      <c r="G11">
+        <v>1.14</v>
+      </c>
+      <c r="H11">
+        <v>79.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.498</v>
+      </c>
+      <c r="K11">
+        <v>0.115</v>
+      </c>
+      <c r="L11">
+        <v>0.383</v>
+      </c>
+      <c r="M11">
+        <v>1.708614</v>
+      </c>
+      <c r="N11">
+        <v>-1.325614</v>
+      </c>
+      <c r="O11">
+        <v>-0.30489122</v>
+      </c>
+      <c r="P11">
+        <v>-1.02072278</v>
+      </c>
+      <c r="Q11">
+        <v>-0.9057227799999998</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2242328816334917</v>
+      </c>
+      <c r="T11">
+        <v>1.082358542348006</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.05155640770823603</v>
+      </c>
+      <c r="W11">
+        <v>0.2264883298392733</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.224158294383635</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2264358719720121</v>
+      </c>
+      <c r="C12">
+        <v>63.98890594821769</v>
+      </c>
+      <c r="D12">
+        <v>70.79890594821769</v>
+      </c>
+      <c r="E12">
+        <v>7.95</v>
+      </c>
+      <c r="F12">
+        <v>7.95</v>
+      </c>
+      <c r="G12">
+        <v>1.14</v>
+      </c>
+      <c r="H12">
+        <v>79.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.498</v>
+      </c>
+      <c r="K12">
+        <v>0.115</v>
+      </c>
+      <c r="L12">
+        <v>0.383</v>
+      </c>
+      <c r="M12">
+        <v>1.89846</v>
+      </c>
+      <c r="N12">
+        <v>-1.51546</v>
+      </c>
+      <c r="O12">
+        <v>-0.3485558</v>
+      </c>
+      <c r="P12">
+        <v>-1.1669042</v>
+      </c>
+      <c r="Q12">
+        <v>-1.0519042</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.226293246984975</v>
+      </c>
+      <c r="T12">
+        <v>1.094384748374095</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.04640076693741242</v>
+      </c>
+      <c r="W12">
+        <v>0.2277194968553459</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.2017424649452715</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2284358719720121</v>
+      </c>
+      <c r="C13">
+        <v>62.44722331679376</v>
+      </c>
+      <c r="D13">
+        <v>70.05222331679376</v>
+      </c>
+      <c r="E13">
+        <v>8.744999999999999</v>
+      </c>
+      <c r="F13">
+        <v>8.744999999999999</v>
+      </c>
+      <c r="G13">
+        <v>1.14</v>
+      </c>
+      <c r="H13">
+        <v>79.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.498</v>
+      </c>
+      <c r="K13">
+        <v>0.115</v>
+      </c>
+      <c r="L13">
+        <v>0.383</v>
+      </c>
+      <c r="M13">
+        <v>2.088306</v>
+      </c>
+      <c r="N13">
+        <v>-1.705306</v>
+      </c>
+      <c r="O13">
+        <v>-0.3922203799999999</v>
+      </c>
+      <c r="P13">
+        <v>-1.31308562</v>
+      </c>
+      <c r="Q13">
+        <v>-1.19808562</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2283999126814354</v>
+      </c>
+      <c r="T13">
+        <v>1.106681206220995</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.04218251539764766</v>
+      </c>
+      <c r="W13">
+        <v>0.2287268153230418</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.1834022408593377</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2304358719720121</v>
+      </c>
+      <c r="C14">
+        <v>60.921126131325</v>
+      </c>
+      <c r="D14">
+        <v>69.321126131325</v>
+      </c>
+      <c r="E14">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="F14">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="G14">
+        <v>1.14</v>
+      </c>
+      <c r="H14">
+        <v>79.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.498</v>
+      </c>
+      <c r="K14">
+        <v>0.115</v>
+      </c>
+      <c r="L14">
+        <v>0.383</v>
+      </c>
+      <c r="M14">
+        <v>2.278152</v>
+      </c>
+      <c r="N14">
+        <v>-1.895152</v>
+      </c>
+      <c r="O14">
+        <v>-0.4358849599999999</v>
+      </c>
+      <c r="P14">
+        <v>-1.45926704</v>
+      </c>
+      <c r="Q14">
+        <v>-1.34426704</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2305544571437244</v>
+      </c>
+      <c r="T14">
+        <v>1.119257129018961</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.03866730578117702</v>
+      </c>
+      <c r="W14">
+        <v>0.2295662473794549</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.1681187207877262</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2324358719720121</v>
+      </c>
+      <c r="C15">
+        <v>59.41013146127394</v>
+      </c>
+      <c r="D15">
+        <v>68.60513146127394</v>
+      </c>
+      <c r="E15">
+        <v>10.335</v>
+      </c>
+      <c r="F15">
+        <v>10.335</v>
+      </c>
+      <c r="G15">
+        <v>1.14</v>
+      </c>
+      <c r="H15">
+        <v>79.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.498</v>
+      </c>
+      <c r="K15">
+        <v>0.115</v>
+      </c>
+      <c r="L15">
+        <v>0.383</v>
+      </c>
+      <c r="M15">
+        <v>2.467998</v>
+      </c>
+      <c r="N15">
+        <v>-2.084998</v>
+      </c>
+      <c r="O15">
+        <v>-0.47954954</v>
+      </c>
+      <c r="P15">
+        <v>-1.60544846</v>
+      </c>
+      <c r="Q15">
+        <v>-1.49044846</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2327585313637672</v>
+      </c>
+      <c r="T15">
+        <v>1.132122153490443</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.0356928976441634</v>
+      </c>
+      <c r="W15">
+        <v>0.2302765360425738</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.1551865114963626</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2344358719720121</v>
+      </c>
+      <c r="C16">
+        <v>57.9137761242416</v>
+      </c>
+      <c r="D16">
+        <v>67.9037761242416</v>
+      </c>
+      <c r="E16">
+        <v>11.13</v>
+      </c>
+      <c r="F16">
+        <v>11.13</v>
+      </c>
+      <c r="G16">
+        <v>1.14</v>
+      </c>
+      <c r="H16">
+        <v>79.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.498</v>
+      </c>
+      <c r="K16">
+        <v>0.115</v>
+      </c>
+      <c r="L16">
+        <v>0.383</v>
+      </c>
+      <c r="M16">
+        <v>2.657844</v>
+      </c>
+      <c r="N16">
+        <v>-2.274844</v>
+      </c>
+      <c r="O16">
+        <v>-0.52321412</v>
+      </c>
+      <c r="P16">
+        <v>-1.75162988</v>
+      </c>
+      <c r="Q16">
+        <v>-1.63662988</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.235013863123811</v>
+      </c>
+      <c r="T16">
+        <v>1.145286364577541</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.03314340495529459</v>
+      </c>
+      <c r="W16">
+        <v>0.2308853548966757</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.1441017606751939</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2364358719720121</v>
+      </c>
+      <c r="C17">
+        <v>56.43161568674918</v>
+      </c>
+      <c r="D17">
+        <v>67.21661568674918</v>
+      </c>
+      <c r="E17">
+        <v>11.925</v>
+      </c>
+      <c r="F17">
+        <v>11.925</v>
+      </c>
+      <c r="G17">
+        <v>1.14</v>
+      </c>
+      <c r="H17">
+        <v>79.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.498</v>
+      </c>
+      <c r="K17">
+        <v>0.115</v>
+      </c>
+      <c r="L17">
+        <v>0.383</v>
+      </c>
+      <c r="M17">
+        <v>2.84769</v>
+      </c>
+      <c r="N17">
+        <v>-2.46469</v>
+      </c>
+      <c r="O17">
+        <v>-0.5668787</v>
+      </c>
+      <c r="P17">
+        <v>-1.8978113</v>
+      </c>
+      <c r="Q17">
+        <v>-1.7828113</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2373222615135029</v>
+      </c>
+      <c r="T17">
+        <v>1.158760321807865</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.03093384462494162</v>
+      </c>
+      <c r="W17">
+        <v>0.231412997903564</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.134494976630181</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2384358719720121</v>
+      </c>
+      <c r="C18">
+        <v>54.96322352508224</v>
+      </c>
+      <c r="D18">
+        <v>66.54322352508224</v>
+      </c>
+      <c r="E18">
+        <v>12.72</v>
+      </c>
+      <c r="F18">
+        <v>12.72</v>
+      </c>
+      <c r="G18">
+        <v>1.14</v>
+      </c>
+      <c r="H18">
+        <v>79.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.498</v>
+      </c>
+      <c r="K18">
+        <v>0.115</v>
+      </c>
+      <c r="L18">
+        <v>0.383</v>
+      </c>
+      <c r="M18">
+        <v>3.037536</v>
+      </c>
+      <c r="N18">
+        <v>-2.654536</v>
+      </c>
+      <c r="O18">
+        <v>-0.61054328</v>
+      </c>
+      <c r="P18">
+        <v>-2.04399272</v>
+      </c>
+      <c r="Q18">
+        <v>-1.92899272</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2396856217696161</v>
+      </c>
+      <c r="T18">
+        <v>1.172555087543673</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.02900047933588277</v>
+      </c>
+      <c r="W18">
+        <v>0.2318746855345912</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.1260890405907946</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2404358719720121</v>
+      </c>
+      <c r="C19">
+        <v>53.50818994202695</v>
+      </c>
+      <c r="D19">
+        <v>65.88318994202695</v>
+      </c>
+      <c r="E19">
+        <v>13.515</v>
+      </c>
+      <c r="F19">
+        <v>13.515</v>
+      </c>
+      <c r="G19">
+        <v>1.14</v>
+      </c>
+      <c r="H19">
+        <v>79.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.498</v>
+      </c>
+      <c r="K19">
+        <v>0.115</v>
+      </c>
+      <c r="L19">
+        <v>0.383</v>
+      </c>
+      <c r="M19">
+        <v>3.227382</v>
+      </c>
+      <c r="N19">
+        <v>-2.844382</v>
+      </c>
+      <c r="O19">
+        <v>-0.6542078600000001</v>
+      </c>
+      <c r="P19">
+        <v>-2.19017414</v>
+      </c>
+      <c r="Q19">
+        <v>-2.075174140000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2421059304656355</v>
+      </c>
+      <c r="T19">
+        <v>1.186682257273115</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.02729456878671319</v>
+      </c>
+      <c r="W19">
+        <v>0.2322820569737329</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.1186720382031008</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2424358719720121</v>
+      </c>
+      <c r="C20">
+        <v>52.06612133565604</v>
+      </c>
+      <c r="D20">
+        <v>65.23612133565604</v>
+      </c>
+      <c r="E20">
+        <v>14.31</v>
+      </c>
+      <c r="F20">
+        <v>14.31</v>
+      </c>
+      <c r="G20">
+        <v>1.14</v>
+      </c>
+      <c r="H20">
+        <v>79.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.498</v>
+      </c>
+      <c r="K20">
+        <v>0.115</v>
+      </c>
+      <c r="L20">
+        <v>0.383</v>
+      </c>
+      <c r="M20">
+        <v>3.417228</v>
+      </c>
+      <c r="N20">
+        <v>-3.034228</v>
+      </c>
+      <c r="O20">
+        <v>-0.6978724399999999</v>
+      </c>
+      <c r="P20">
+        <v>-2.33635556</v>
+      </c>
+      <c r="Q20">
+        <v>-2.22135556</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2445852710810701</v>
+      </c>
+      <c r="T20">
+        <v>1.201153992117909</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.02577820385411802</v>
+      </c>
+      <c r="W20">
+        <v>0.2326441649196366</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.1120791471918174</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2444358719720121</v>
+      </c>
+      <c r="C21">
+        <v>50.63663941662068</v>
+      </c>
+      <c r="D21">
+        <v>64.60163941662069</v>
+      </c>
+      <c r="E21">
+        <v>15.105</v>
+      </c>
+      <c r="F21">
+        <v>15.105</v>
+      </c>
+      <c r="G21">
+        <v>1.14</v>
+      </c>
+      <c r="H21">
+        <v>79.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.498</v>
+      </c>
+      <c r="K21">
+        <v>0.115</v>
+      </c>
+      <c r="L21">
+        <v>0.383</v>
+      </c>
+      <c r="M21">
+        <v>3.607074</v>
+      </c>
+      <c r="N21">
+        <v>-3.224074</v>
+      </c>
+      <c r="O21">
+        <v>-0.74153702</v>
+      </c>
+      <c r="P21">
+        <v>-2.48253698</v>
+      </c>
+      <c r="Q21">
+        <v>-2.367536980000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2471258299833055</v>
+      </c>
+      <c r="T21">
+        <v>1.215983053748994</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.02442145628284864</v>
+      </c>
+      <c r="W21">
+        <v>0.2329681562396557</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.1061802447080376</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2464358719720121</v>
+      </c>
+      <c r="C22">
+        <v>49.21938047067776</v>
+      </c>
+      <c r="D22">
+        <v>63.97938047067776</v>
+      </c>
+      <c r="E22">
+        <v>15.9</v>
+      </c>
+      <c r="F22">
+        <v>15.9</v>
+      </c>
+      <c r="G22">
+        <v>1.14</v>
+      </c>
+      <c r="H22">
+        <v>79.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.498</v>
+      </c>
+      <c r="K22">
+        <v>0.115</v>
+      </c>
+      <c r="L22">
+        <v>0.383</v>
+      </c>
+      <c r="M22">
+        <v>3.79692</v>
+      </c>
+      <c r="N22">
+        <v>-3.41392</v>
+      </c>
+      <c r="O22">
+        <v>-0.7852015999999999</v>
+      </c>
+      <c r="P22">
+        <v>-2.6287184</v>
+      </c>
+      <c r="Q22">
+        <v>-2.5137184</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2497299028580968</v>
+      </c>
+      <c r="T22">
+        <v>1.231182841920857</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.02320038346870621</v>
+      </c>
+      <c r="W22">
+        <v>0.233259748427673</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.1008712324726357</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2484358719720121</v>
+      </c>
+      <c r="C23">
+        <v>47.81399466343176</v>
+      </c>
+      <c r="D23">
+        <v>63.36899466343177</v>
+      </c>
+      <c r="E23">
+        <v>16.695</v>
+      </c>
+      <c r="F23">
+        <v>16.695</v>
+      </c>
+      <c r="G23">
+        <v>1.14</v>
+      </c>
+      <c r="H23">
+        <v>79.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.498</v>
+      </c>
+      <c r="K23">
+        <v>0.115</v>
+      </c>
+      <c r="L23">
+        <v>0.383</v>
+      </c>
+      <c r="M23">
+        <v>3.986766</v>
+      </c>
+      <c r="N23">
+        <v>-3.603766</v>
+      </c>
+      <c r="O23">
+        <v>-0.82886618</v>
+      </c>
+      <c r="P23">
+        <v>-2.77489982</v>
+      </c>
+      <c r="Q23">
+        <v>-2.659899820000001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2523999016284525</v>
+      </c>
+      <c r="T23">
+        <v>1.246767434856564</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.02209560330352973</v>
+      </c>
+      <c r="W23">
+        <v>0.2335235699311171</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.09606784045012928</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2504358719720121</v>
+      </c>
+      <c r="C24">
+        <v>46.42014538449845</v>
+      </c>
+      <c r="D24">
+        <v>62.77014538449846</v>
+      </c>
+      <c r="E24">
+        <v>17.49</v>
+      </c>
+      <c r="F24">
+        <v>17.49</v>
+      </c>
+      <c r="G24">
+        <v>1.14</v>
+      </c>
+      <c r="H24">
+        <v>79.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.498</v>
+      </c>
+      <c r="K24">
+        <v>0.115</v>
+      </c>
+      <c r="L24">
+        <v>0.383</v>
+      </c>
+      <c r="M24">
+        <v>4.176612</v>
+      </c>
+      <c r="N24">
+        <v>-3.793612</v>
+      </c>
+      <c r="O24">
+        <v>-0.8725307599999998</v>
+      </c>
+      <c r="P24">
+        <v>-2.921081239999999</v>
+      </c>
+      <c r="Q24">
+        <v>-2.806081239999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2551383619057404</v>
+      </c>
+      <c r="T24">
+        <v>1.26275163273934</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.02109125769882383</v>
+      </c>
+      <c r="W24">
+        <v>0.2337634076615209</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.09170112042966883</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2524358719720121</v>
+      </c>
+      <c r="C25">
+        <v>45.0375086285072</v>
+      </c>
+      <c r="D25">
+        <v>62.1825086285072</v>
+      </c>
+      <c r="E25">
+        <v>18.285</v>
+      </c>
+      <c r="F25">
+        <v>18.285</v>
+      </c>
+      <c r="G25">
+        <v>1.14</v>
+      </c>
+      <c r="H25">
+        <v>79.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.498</v>
+      </c>
+      <c r="K25">
+        <v>0.115</v>
+      </c>
+      <c r="L25">
+        <v>0.383</v>
+      </c>
+      <c r="M25">
+        <v>4.366458000000001</v>
+      </c>
+      <c r="N25">
+        <v>-3.983458000000001</v>
+      </c>
+      <c r="O25">
+        <v>-0.91619534</v>
+      </c>
+      <c r="P25">
+        <v>-3.067262660000001</v>
+      </c>
+      <c r="Q25">
+        <v>-2.952262660000001</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2579479510213993</v>
+      </c>
+      <c r="T25">
+        <v>1.279151004593098</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.02017424649452714</v>
+      </c>
+      <c r="W25">
+        <v>0.2339823899371069</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.08771411519359629</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2544358719720121</v>
+      </c>
+      <c r="C26">
+        <v>43.66577241055012</v>
+      </c>
+      <c r="D26">
+        <v>61.60577241055012</v>
+      </c>
+      <c r="E26">
+        <v>19.08</v>
+      </c>
+      <c r="F26">
+        <v>19.08</v>
+      </c>
+      <c r="G26">
+        <v>1.14</v>
+      </c>
+      <c r="H26">
+        <v>79.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.498</v>
+      </c>
+      <c r="K26">
+        <v>0.115</v>
+      </c>
+      <c r="L26">
+        <v>0.383</v>
+      </c>
+      <c r="M26">
+        <v>4.556304</v>
+      </c>
+      <c r="N26">
+        <v>-4.173304</v>
+      </c>
+      <c r="O26">
+        <v>-0.9598599199999999</v>
+      </c>
+      <c r="P26">
+        <v>-3.21344408</v>
+      </c>
+      <c r="Q26">
+        <v>-3.09844408</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2608314766927335</v>
+      </c>
+      <c r="T26">
+        <v>1.29598193886406</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.01933365289058851</v>
+      </c>
+      <c r="W26">
+        <v>0.2341831236897275</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.08405936039386308</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2564358719720121</v>
+      </c>
+      <c r="C27">
+        <v>42.30463621386217</v>
+      </c>
+      <c r="D27">
+        <v>61.03963621386217</v>
+      </c>
+      <c r="E27">
+        <v>19.875</v>
+      </c>
+      <c r="F27">
+        <v>19.875</v>
+      </c>
+      <c r="G27">
+        <v>1.14</v>
+      </c>
+      <c r="H27">
+        <v>79.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.498</v>
+      </c>
+      <c r="K27">
+        <v>0.115</v>
+      </c>
+      <c r="L27">
+        <v>0.383</v>
+      </c>
+      <c r="M27">
+        <v>4.74615</v>
+      </c>
+      <c r="N27">
+        <v>-4.36315</v>
+      </c>
+      <c r="O27">
+        <v>-1.0035245</v>
+      </c>
+      <c r="P27">
+        <v>-3.3596255</v>
+      </c>
+      <c r="Q27">
+        <v>-3.2446255</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2637918963819699</v>
+      </c>
+      <c r="T27">
+        <v>1.313261698048914</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.01856030677496497</v>
+      </c>
+      <c r="W27">
+        <v>0.2343677987421384</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.08069698597810859</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2584358719720121</v>
+      </c>
+      <c r="C28">
+        <v>40.95381046767768</v>
+      </c>
+      <c r="D28">
+        <v>60.48381046767768</v>
+      </c>
+      <c r="E28">
+        <v>20.67</v>
+      </c>
+      <c r="F28">
+        <v>20.67</v>
+      </c>
+      <c r="G28">
+        <v>1.14</v>
+      </c>
+      <c r="H28">
+        <v>79.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.498</v>
+      </c>
+      <c r="K28">
+        <v>0.115</v>
+      </c>
+      <c r="L28">
+        <v>0.383</v>
+      </c>
+      <c r="M28">
+        <v>4.935996</v>
+      </c>
+      <c r="N28">
+        <v>-4.552996</v>
+      </c>
+      <c r="O28">
+        <v>-1.04718908</v>
+      </c>
+      <c r="P28">
+        <v>-3.50580692</v>
+      </c>
+      <c r="Q28">
+        <v>-3.39080692</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2668323274141587</v>
+      </c>
+      <c r="T28">
+        <v>1.331008477752278</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.0178464488220817</v>
+      </c>
+      <c r="W28">
+        <v>0.2345382680212869</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.07759325574818132</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.260435871972012</v>
+      </c>
+      <c r="C29">
+        <v>39.6130160533573</v>
+      </c>
+      <c r="D29">
+        <v>59.93801605335729</v>
+      </c>
+      <c r="E29">
+        <v>21.465</v>
+      </c>
+      <c r="F29">
+        <v>21.465</v>
+      </c>
+      <c r="G29">
+        <v>1.14</v>
+      </c>
+      <c r="H29">
+        <v>79.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.498</v>
+      </c>
+      <c r="K29">
+        <v>0.115</v>
+      </c>
+      <c r="L29">
+        <v>0.383</v>
+      </c>
+      <c r="M29">
+        <v>5.125842</v>
+      </c>
+      <c r="N29">
+        <v>-4.742842</v>
+      </c>
+      <c r="O29">
+        <v>-1.09085366</v>
+      </c>
+      <c r="P29">
+        <v>-3.65198834</v>
+      </c>
+      <c r="Q29">
+        <v>-3.536988340000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2699560579266814</v>
+      </c>
+      <c r="T29">
+        <v>1.349241470598199</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.01718546923607868</v>
+      </c>
+      <c r="W29">
+        <v>0.2346961099464244</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.07471943146121163</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2624358719720121</v>
+      </c>
+      <c r="C30">
+        <v>38.28198383701536</v>
+      </c>
+      <c r="D30">
+        <v>59.40198383701536</v>
+      </c>
+      <c r="E30">
+        <v>22.26</v>
+      </c>
+      <c r="F30">
+        <v>22.26</v>
+      </c>
+      <c r="G30">
+        <v>1.14</v>
+      </c>
+      <c r="H30">
+        <v>79.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.498</v>
+      </c>
+      <c r="K30">
+        <v>0.115</v>
+      </c>
+      <c r="L30">
+        <v>0.383</v>
+      </c>
+      <c r="M30">
+        <v>5.315688000000001</v>
+      </c>
+      <c r="N30">
+        <v>-4.932688000000001</v>
+      </c>
+      <c r="O30">
+        <v>-1.13451824</v>
+      </c>
+      <c r="P30">
+        <v>-3.79816976</v>
+      </c>
+      <c r="Q30">
+        <v>-3.68316976</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2731665587312188</v>
+      </c>
+      <c r="T30">
+        <v>1.367980935467619</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.01657170247764729</v>
+      </c>
+      <c r="W30">
+        <v>0.2348426774483378</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.07205088033759688</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.264435871972012</v>
+      </c>
+      <c r="C31">
+        <v>36.96045422700387</v>
+      </c>
+      <c r="D31">
+        <v>58.87545422700387</v>
+      </c>
+      <c r="E31">
+        <v>23.055</v>
+      </c>
+      <c r="F31">
+        <v>23.055</v>
+      </c>
+      <c r="G31">
+        <v>1.14</v>
+      </c>
+      <c r="H31">
+        <v>79.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.498</v>
+      </c>
+      <c r="K31">
+        <v>0.115</v>
+      </c>
+      <c r="L31">
+        <v>0.383</v>
+      </c>
+      <c r="M31">
+        <v>5.505534</v>
+      </c>
+      <c r="N31">
+        <v>-5.122534</v>
+      </c>
+      <c r="O31">
+        <v>-1.17818282</v>
+      </c>
+      <c r="P31">
+        <v>-3.94435118</v>
+      </c>
+      <c r="Q31">
+        <v>-3.82935118</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2764674961781373</v>
+      </c>
+      <c r="T31">
+        <v>1.387248272586881</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.0160002644611767</v>
+      </c>
+      <c r="W31">
+        <v>0.234979136846671</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.06956636722250742</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2664358719720121</v>
+      </c>
+      <c r="C32">
+        <v>35.64817675472355</v>
+      </c>
+      <c r="D32">
+        <v>58.35817675472354</v>
+      </c>
+      <c r="E32">
+        <v>23.85</v>
+      </c>
+      <c r="F32">
+        <v>23.85</v>
+      </c>
+      <c r="G32">
+        <v>1.14</v>
+      </c>
+      <c r="H32">
+        <v>79.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.498</v>
+      </c>
+      <c r="K32">
+        <v>0.115</v>
+      </c>
+      <c r="L32">
+        <v>0.383</v>
+      </c>
+      <c r="M32">
+        <v>5.69538</v>
+      </c>
+      <c r="N32">
+        <v>-5.31238</v>
+      </c>
+      <c r="O32">
+        <v>-1.2218474</v>
+      </c>
+      <c r="P32">
+        <v>-4.0905326</v>
+      </c>
+      <c r="Q32">
+        <v>-3.9755326</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2798627461235392</v>
+      </c>
+      <c r="T32">
+        <v>1.407066105052408</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.01546692231247081</v>
+      </c>
+      <c r="W32">
+        <v>0.235106498951782</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.06724748831509053</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2684358719720121</v>
+      </c>
+      <c r="C33">
+        <v>34.34490967734082</v>
+      </c>
+      <c r="D33">
+        <v>57.84990967734082</v>
+      </c>
+      <c r="E33">
+        <v>24.645</v>
+      </c>
+      <c r="F33">
+        <v>24.645</v>
+      </c>
+      <c r="G33">
+        <v>1.14</v>
+      </c>
+      <c r="H33">
+        <v>79.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.498</v>
+      </c>
+      <c r="K33">
+        <v>0.115</v>
+      </c>
+      <c r="L33">
+        <v>0.383</v>
+      </c>
+      <c r="M33">
+        <v>5.885226</v>
+      </c>
+      <c r="N33">
+        <v>-5.502226</v>
+      </c>
+      <c r="O33">
+        <v>-1.26551198</v>
+      </c>
+      <c r="P33">
+        <v>-4.236714020000001</v>
+      </c>
+      <c r="Q33">
+        <v>-4.121714020000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2833564091108369</v>
+      </c>
+      <c r="T33">
+        <v>1.427458367444472</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.01496798933464917</v>
+      </c>
+      <c r="W33">
+        <v>0.2352256441468858</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.06507821449847462</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.270435871972012</v>
+      </c>
+      <c r="C34">
+        <v>33.05041960108588</v>
+      </c>
+      <c r="D34">
+        <v>57.35041960108588</v>
+      </c>
+      <c r="E34">
+        <v>25.44</v>
+      </c>
+      <c r="F34">
+        <v>25.44</v>
+      </c>
+      <c r="G34">
+        <v>1.14</v>
+      </c>
+      <c r="H34">
+        <v>79.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.498</v>
+      </c>
+      <c r="K34">
+        <v>0.115</v>
+      </c>
+      <c r="L34">
+        <v>0.383</v>
+      </c>
+      <c r="M34">
+        <v>6.075072</v>
+      </c>
+      <c r="N34">
+        <v>-5.692072</v>
+      </c>
+      <c r="O34">
+        <v>-1.30917656</v>
+      </c>
+      <c r="P34">
+        <v>-4.38289544</v>
+      </c>
+      <c r="Q34">
+        <v>-4.26789544</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2869528268918786</v>
+      </c>
+      <c r="T34">
+        <v>1.448450402259832</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.01450023966794138</v>
+      </c>
+      <c r="W34">
+        <v>0.2353373427672956</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.06304452029539731</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2724358719720121</v>
+      </c>
+      <c r="C35">
+        <v>31.76448112389898</v>
+      </c>
+      <c r="D35">
+        <v>56.85948112389898</v>
+      </c>
+      <c r="E35">
+        <v>26.235</v>
+      </c>
+      <c r="F35">
+        <v>26.235</v>
+      </c>
+      <c r="G35">
+        <v>1.14</v>
+      </c>
+      <c r="H35">
+        <v>79.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.498</v>
+      </c>
+      <c r="K35">
+        <v>0.115</v>
+      </c>
+      <c r="L35">
+        <v>0.383</v>
+      </c>
+      <c r="M35">
+        <v>6.264918000000001</v>
+      </c>
+      <c r="N35">
+        <v>-5.881918000000001</v>
+      </c>
+      <c r="O35">
+        <v>-1.35284114</v>
+      </c>
+      <c r="P35">
+        <v>-4.529076860000001</v>
+      </c>
+      <c r="Q35">
+        <v>-4.414076860000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2906566004275783</v>
+      </c>
+      <c r="T35">
+        <v>1.470069064980128</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.01406083846588255</v>
+      </c>
+      <c r="W35">
+        <v>0.2354422717743473</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.06113408028644585</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2744358719720121</v>
+      </c>
+      <c r="C36">
+        <v>30.48687649627545</v>
+      </c>
+      <c r="D36">
+        <v>56.37687649627545</v>
+      </c>
+      <c r="E36">
+        <v>27.03</v>
+      </c>
+      <c r="F36">
+        <v>27.03</v>
+      </c>
+      <c r="G36">
+        <v>1.14</v>
+      </c>
+      <c r="H36">
+        <v>79.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.498</v>
+      </c>
+      <c r="K36">
+        <v>0.115</v>
+      </c>
+      <c r="L36">
+        <v>0.383</v>
+      </c>
+      <c r="M36">
+        <v>6.454764000000001</v>
+      </c>
+      <c r="N36">
+        <v>-6.071764000000001</v>
+      </c>
+      <c r="O36">
+        <v>-1.39650572</v>
+      </c>
+      <c r="P36">
+        <v>-4.67525828</v>
+      </c>
+      <c r="Q36">
+        <v>-4.56025828</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2944726095249659</v>
+      </c>
+      <c r="T36">
+        <v>1.492342838691948</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.01364728439335659</v>
+      </c>
+      <c r="W36">
+        <v>0.2355410284868664</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.0593360191015504</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2764358719720121</v>
+      </c>
+      <c r="C37">
+        <v>29.21739529923702</v>
+      </c>
+      <c r="D37">
+        <v>55.90239529923702</v>
+      </c>
+      <c r="E37">
+        <v>27.825</v>
+      </c>
+      <c r="F37">
+        <v>27.825</v>
+      </c>
+      <c r="G37">
+        <v>1.14</v>
+      </c>
+      <c r="H37">
+        <v>79.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.498</v>
+      </c>
+      <c r="K37">
+        <v>0.115</v>
+      </c>
+      <c r="L37">
+        <v>0.383</v>
+      </c>
+      <c r="M37">
+        <v>6.644610000000001</v>
+      </c>
+      <c r="N37">
+        <v>-6.261610000000001</v>
+      </c>
+      <c r="O37">
+        <v>-1.4401703</v>
+      </c>
+      <c r="P37">
+        <v>-4.821439700000001</v>
+      </c>
+      <c r="Q37">
+        <v>-4.706439700000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2984060342868884</v>
+      </c>
+      <c r="T37">
+        <v>1.515301959287209</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.01325736198211783</v>
+      </c>
+      <c r="W37">
+        <v>0.2356341419586703</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.0576407042700775</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.278435871972012</v>
+      </c>
+      <c r="C38">
+        <v>27.95583413842914</v>
+      </c>
+      <c r="D38">
+        <v>55.43583413842914</v>
+      </c>
+      <c r="E38">
+        <v>28.62</v>
+      </c>
+      <c r="F38">
+        <v>28.62</v>
+      </c>
+      <c r="G38">
+        <v>1.14</v>
+      </c>
+      <c r="H38">
+        <v>79.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.498</v>
+      </c>
+      <c r="K38">
+        <v>0.115</v>
+      </c>
+      <c r="L38">
+        <v>0.383</v>
+      </c>
+      <c r="M38">
+        <v>6.834455999999999</v>
+      </c>
+      <c r="N38">
+        <v>-6.451455999999999</v>
+      </c>
+      <c r="O38">
+        <v>-1.48383488</v>
+      </c>
+      <c r="P38">
+        <v>-4.96762112</v>
+      </c>
+      <c r="Q38">
+        <v>-4.852621119999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.302462378572621</v>
+      </c>
+      <c r="T38">
+        <v>1.538978552401071</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.01288910192705901</v>
+      </c>
+      <c r="W38">
+        <v>0.2357220824598183</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.05603957359590872</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2804358719720121</v>
+      </c>
+      <c r="C39">
+        <v>26.70199635340977</v>
+      </c>
+      <c r="D39">
+        <v>54.97699635340977</v>
+      </c>
+      <c r="E39">
+        <v>29.415</v>
+      </c>
+      <c r="F39">
+        <v>29.415</v>
+      </c>
+      <c r="G39">
+        <v>1.14</v>
+      </c>
+      <c r="H39">
+        <v>79.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.498</v>
+      </c>
+      <c r="K39">
+        <v>0.115</v>
+      </c>
+      <c r="L39">
+        <v>0.383</v>
+      </c>
+      <c r="M39">
+        <v>7.024302</v>
+      </c>
+      <c r="N39">
+        <v>-6.641302</v>
+      </c>
+      <c r="O39">
+        <v>-1.52749946</v>
+      </c>
+      <c r="P39">
+        <v>-5.11380254</v>
+      </c>
+      <c r="Q39">
+        <v>-4.99880254</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3066474956928214</v>
+      </c>
+      <c r="T39">
+        <v>1.563406783391564</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.01254074782092228</v>
+      </c>
+      <c r="W39">
+        <v>0.2358052694203638</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.054524990525749</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2824358719720121</v>
+      </c>
+      <c r="C40">
+        <v>25.45569174125704</v>
+      </c>
+      <c r="D40">
+        <v>54.52569174125704</v>
+      </c>
+      <c r="E40">
+        <v>30.21</v>
+      </c>
+      <c r="F40">
+        <v>30.21</v>
+      </c>
+      <c r="G40">
+        <v>1.14</v>
+      </c>
+      <c r="H40">
+        <v>79.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.498</v>
+      </c>
+      <c r="K40">
+        <v>0.115</v>
+      </c>
+      <c r="L40">
+        <v>0.383</v>
+      </c>
+      <c r="M40">
+        <v>7.214148000000001</v>
+      </c>
+      <c r="N40">
+        <v>-6.831148000000001</v>
+      </c>
+      <c r="O40">
+        <v>-1.57116404</v>
+      </c>
+      <c r="P40">
+        <v>-5.25998396</v>
+      </c>
+      <c r="Q40">
+        <v>-5.14498396</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3109676165910927</v>
+      </c>
+      <c r="T40">
+        <v>1.588623021833363</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.01221072814142432</v>
+      </c>
+      <c r="W40">
+        <v>0.2358840781198279</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.05309012235401878</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2844358719720121</v>
+      </c>
+      <c r="C41">
+        <v>24.21673629367918</v>
+      </c>
+      <c r="D41">
+        <v>54.08173629367918</v>
+      </c>
+      <c r="E41">
+        <v>31.005</v>
+      </c>
+      <c r="F41">
+        <v>31.005</v>
+      </c>
+      <c r="G41">
+        <v>1.14</v>
+      </c>
+      <c r="H41">
+        <v>79.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.498</v>
+      </c>
+      <c r="K41">
+        <v>0.115</v>
+      </c>
+      <c r="L41">
+        <v>0.383</v>
+      </c>
+      <c r="M41">
+        <v>7.403994000000001</v>
+      </c>
+      <c r="N41">
+        <v>-7.020994000000001</v>
+      </c>
+      <c r="O41">
+        <v>-1.61482862</v>
+      </c>
+      <c r="P41">
+        <v>-5.406165380000001</v>
+      </c>
+      <c r="Q41">
+        <v>-5.291165380000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.315429380797504</v>
+      </c>
+      <c r="T41">
+        <v>1.614666022191288</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.01189763254805447</v>
+      </c>
+      <c r="W41">
+        <v>0.2359588453475246</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.05172883716545418</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.286435871972012</v>
+      </c>
+      <c r="C42">
+        <v>22.98495194686378</v>
+      </c>
+      <c r="D42">
+        <v>53.64495194686378</v>
+      </c>
+      <c r="E42">
+        <v>31.8</v>
+      </c>
+      <c r="F42">
+        <v>31.8</v>
+      </c>
+      <c r="G42">
+        <v>1.14</v>
+      </c>
+      <c r="H42">
+        <v>79.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.498</v>
+      </c>
+      <c r="K42">
+        <v>0.115</v>
+      </c>
+      <c r="L42">
+        <v>0.383</v>
+      </c>
+      <c r="M42">
+        <v>7.59384</v>
+      </c>
+      <c r="N42">
+        <v>-7.21084</v>
+      </c>
+      <c r="O42">
+        <v>-1.6584932</v>
+      </c>
+      <c r="P42">
+        <v>-5.5523468</v>
+      </c>
+      <c r="Q42">
+        <v>-5.4373468</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3200398704774625</v>
+      </c>
+      <c r="T42">
+        <v>1.641577122561143</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.01160019173435311</v>
+      </c>
+      <c r="W42">
+        <v>0.2360298742138365</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.05043561623631787</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.288435871972012</v>
+      </c>
+      <c r="C43">
+        <v>21.76016634335181</v>
+      </c>
+      <c r="D43">
+        <v>53.21516634335182</v>
+      </c>
+      <c r="E43">
+        <v>32.59500000000001</v>
+      </c>
+      <c r="F43">
+        <v>32.59500000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.14</v>
+      </c>
+      <c r="H43">
+        <v>79.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.498</v>
+      </c>
+      <c r="K43">
+        <v>0.115</v>
+      </c>
+      <c r="L43">
+        <v>0.383</v>
+      </c>
+      <c r="M43">
+        <v>7.783686000000002</v>
+      </c>
+      <c r="N43">
+        <v>-7.400686000000002</v>
+      </c>
+      <c r="O43">
+        <v>-1.70215778</v>
+      </c>
+      <c r="P43">
+        <v>-5.698528220000002</v>
+      </c>
+      <c r="Q43">
+        <v>-5.583528220000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3248066479431821</v>
+      </c>
+      <c r="T43">
+        <v>1.669400463621501</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.01131726022863717</v>
+      </c>
+      <c r="W43">
+        <v>0.2360974382574015</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.04920547925494423</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2904358719720121</v>
+      </c>
+      <c r="C44">
+        <v>20.54221260526735</v>
+      </c>
+      <c r="D44">
+        <v>52.79221260526735</v>
+      </c>
+      <c r="E44">
+        <v>33.39</v>
+      </c>
+      <c r="F44">
+        <v>33.39</v>
+      </c>
+      <c r="G44">
+        <v>1.14</v>
+      </c>
+      <c r="H44">
+        <v>79.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.498</v>
+      </c>
+      <c r="K44">
+        <v>0.115</v>
+      </c>
+      <c r="L44">
+        <v>0.383</v>
+      </c>
+      <c r="M44">
+        <v>7.973532000000001</v>
+      </c>
+      <c r="N44">
+        <v>-7.590532000000001</v>
+      </c>
+      <c r="O44">
+        <v>-1.74582236</v>
+      </c>
+      <c r="P44">
+        <v>-5.84470964</v>
+      </c>
+      <c r="Q44">
+        <v>-5.72970964</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3297377970456508</v>
+      </c>
+      <c r="T44">
+        <v>1.698183230235665</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.01104780165176486</v>
+      </c>
+      <c r="W44">
+        <v>0.2361617849655586</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.04803392022506459</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2924358719720121</v>
+      </c>
+      <c r="C45">
+        <v>19.33092911827627</v>
+      </c>
+      <c r="D45">
+        <v>52.37592911827627</v>
+      </c>
+      <c r="E45">
+        <v>34.185</v>
+      </c>
+      <c r="F45">
+        <v>34.185</v>
+      </c>
+      <c r="G45">
+        <v>1.14</v>
+      </c>
+      <c r="H45">
+        <v>79.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.498</v>
+      </c>
+      <c r="K45">
+        <v>0.115</v>
+      </c>
+      <c r="L45">
+        <v>0.383</v>
+      </c>
+      <c r="M45">
+        <v>8.163378000000002</v>
+      </c>
+      <c r="N45">
+        <v>-7.780378000000002</v>
+      </c>
+      <c r="O45">
+        <v>-1.78948694</v>
+      </c>
+      <c r="P45">
+        <v>-5.990891060000001</v>
+      </c>
+      <c r="Q45">
+        <v>-5.875891060000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3348419689236447</v>
+      </c>
+      <c r="T45">
+        <v>1.727975918485413</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.01079087603195638</v>
+      </c>
+      <c r="W45">
+        <v>0.2362231388035688</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.04691685231285381</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2944358719720121</v>
+      </c>
+      <c r="C46">
+        <v>18.1261593256862</v>
+      </c>
+      <c r="D46">
+        <v>51.96615932568619</v>
+      </c>
+      <c r="E46">
+        <v>34.98</v>
+      </c>
+      <c r="F46">
+        <v>34.98</v>
+      </c>
+      <c r="G46">
+        <v>1.14</v>
+      </c>
+      <c r="H46">
+        <v>79.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.498</v>
+      </c>
+      <c r="K46">
+        <v>0.115</v>
+      </c>
+      <c r="L46">
+        <v>0.383</v>
+      </c>
+      <c r="M46">
+        <v>8.353223999999999</v>
+      </c>
+      <c r="N46">
+        <v>-7.970223999999999</v>
+      </c>
+      <c r="O46">
+        <v>-1.83315152</v>
+      </c>
+      <c r="P46">
+        <v>-6.13707248</v>
+      </c>
+      <c r="Q46">
+        <v>-6.022072479999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3401284326544241</v>
+      </c>
+      <c r="T46">
+        <v>1.75883263131551</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.01054562884941192</v>
+      </c>
+      <c r="W46">
+        <v>0.2362817038307604</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.04585056021483447</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2964358719720121</v>
+      </c>
+      <c r="C47">
+        <v>16.92775153213693</v>
+      </c>
+      <c r="D47">
+        <v>51.56275153213693</v>
+      </c>
+      <c r="E47">
+        <v>35.775</v>
+      </c>
+      <c r="F47">
+        <v>35.775</v>
+      </c>
+      <c r="G47">
+        <v>1.14</v>
+      </c>
+      <c r="H47">
+        <v>79.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.498</v>
+      </c>
+      <c r="K47">
+        <v>0.115</v>
+      </c>
+      <c r="L47">
+        <v>0.383</v>
+      </c>
+      <c r="M47">
+        <v>8.54307</v>
+      </c>
+      <c r="N47">
+        <v>-8.160070000000001</v>
+      </c>
+      <c r="O47">
+        <v>-1.8768161</v>
+      </c>
+      <c r="P47">
+        <v>-6.283253900000001</v>
+      </c>
+      <c r="Q47">
+        <v>-6.168253900000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3456071314299591</v>
+      </c>
+      <c r="T47">
+        <v>1.790811406430337</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.01031128154164721</v>
+      </c>
+      <c r="W47">
+        <v>0.2363376659678547</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.04483165887672691</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2984358719720121</v>
+      </c>
+      <c r="C48">
+        <v>15.7355587163638</v>
+      </c>
+      <c r="D48">
+        <v>51.1655587163638</v>
+      </c>
+      <c r="E48">
+        <v>36.57</v>
+      </c>
+      <c r="F48">
+        <v>36.57</v>
+      </c>
+      <c r="G48">
+        <v>1.14</v>
+      </c>
+      <c r="H48">
+        <v>79.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.498</v>
+      </c>
+      <c r="K48">
+        <v>0.115</v>
+      </c>
+      <c r="L48">
+        <v>0.383</v>
+      </c>
+      <c r="M48">
+        <v>8.732916000000001</v>
+      </c>
+      <c r="N48">
+        <v>-8.349916</v>
+      </c>
+      <c r="O48">
+        <v>-1.92048068</v>
+      </c>
+      <c r="P48">
+        <v>-6.429435320000001</v>
+      </c>
+      <c r="Q48">
+        <v>-6.31443532</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3512887449749583</v>
+      </c>
+      <c r="T48">
+        <v>1.823974580623492</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.01008712324726357</v>
+      </c>
+      <c r="W48">
+        <v>0.2363911949685535</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.04385705759679825</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.300435871972012</v>
+      </c>
+      <c r="C49">
+        <v>14.54943835254888</v>
+      </c>
+      <c r="D49">
+        <v>50.77443835254888</v>
+      </c>
+      <c r="E49">
+        <v>37.365</v>
+      </c>
+      <c r="F49">
+        <v>37.365</v>
+      </c>
+      <c r="G49">
+        <v>1.14</v>
+      </c>
+      <c r="H49">
+        <v>79.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.498</v>
+      </c>
+      <c r="K49">
+        <v>0.115</v>
+      </c>
+      <c r="L49">
+        <v>0.383</v>
+      </c>
+      <c r="M49">
+        <v>8.922762000000001</v>
+      </c>
+      <c r="N49">
+        <v>-8.539762</v>
+      </c>
+      <c r="O49">
+        <v>-1.96414526</v>
+      </c>
+      <c r="P49">
+        <v>-6.57561674</v>
+      </c>
+      <c r="Q49">
+        <v>-6.46061674</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3571847590310895</v>
+      </c>
+      <c r="T49">
+        <v>1.858389195352237</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.009872503603704771</v>
+      </c>
+      <c r="W49">
+        <v>0.2364424461394353</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.04292392871175998</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.3024358719720121</v>
+      </c>
+      <c r="C50">
+        <v>13.36925223980364</v>
+      </c>
+      <c r="D50">
+        <v>50.38925223980364</v>
+      </c>
+      <c r="E50">
+        <v>38.16</v>
+      </c>
+      <c r="F50">
+        <v>38.16</v>
+      </c>
+      <c r="G50">
+        <v>1.14</v>
+      </c>
+      <c r="H50">
+        <v>79.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.498</v>
+      </c>
+      <c r="K50">
+        <v>0.115</v>
+      </c>
+      <c r="L50">
+        <v>0.383</v>
+      </c>
+      <c r="M50">
+        <v>9.112608</v>
+      </c>
+      <c r="N50">
+        <v>-8.729607999999999</v>
+      </c>
+      <c r="O50">
+        <v>-2.00780984</v>
+      </c>
+      <c r="P50">
+        <v>-6.721798159999999</v>
+      </c>
+      <c r="Q50">
+        <v>-6.606798159999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3633075428586106</v>
+      </c>
+      <c r="T50">
+        <v>1.894127449109011</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.009666826445294254</v>
+      </c>
+      <c r="W50">
+        <v>0.2364915618448638</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.04202968019693165</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.3044358719720121</v>
+      </c>
+      <c r="C51">
+        <v>12.19486633935485</v>
+      </c>
+      <c r="D51">
+        <v>50.00986633935485</v>
+      </c>
+      <c r="E51">
+        <v>38.955</v>
+      </c>
+      <c r="F51">
+        <v>38.955</v>
+      </c>
+      <c r="G51">
+        <v>1.14</v>
+      </c>
+      <c r="H51">
+        <v>79.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.498</v>
+      </c>
+      <c r="K51">
+        <v>0.115</v>
+      </c>
+      <c r="L51">
+        <v>0.383</v>
+      </c>
+      <c r="M51">
+        <v>9.302454000000001</v>
+      </c>
+      <c r="N51">
+        <v>-8.919454000000002</v>
+      </c>
+      <c r="O51">
+        <v>-2.05147442</v>
+      </c>
+      <c r="P51">
+        <v>-6.867979580000002</v>
+      </c>
+      <c r="Q51">
+        <v>-6.752979580000002</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3696704358558381</v>
+      </c>
+      <c r="T51">
+        <v>1.931267203013109</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.00946954427294131</v>
+      </c>
+      <c r="W51">
+        <v>0.2365386728276216</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.04117193162148391</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.3064358719720121</v>
+      </c>
+      <c r="C52">
+        <v>11.0261506190303</v>
+      </c>
+      <c r="D52">
+        <v>49.6361506190303</v>
+      </c>
+      <c r="E52">
+        <v>39.75</v>
+      </c>
+      <c r="F52">
+        <v>39.75</v>
+      </c>
+      <c r="G52">
+        <v>1.14</v>
+      </c>
+      <c r="H52">
+        <v>79.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.498</v>
+      </c>
+      <c r="K52">
+        <v>0.115</v>
+      </c>
+      <c r="L52">
+        <v>0.383</v>
+      </c>
+      <c r="M52">
+        <v>9.4923</v>
+      </c>
+      <c r="N52">
+        <v>-9.109300000000001</v>
+      </c>
+      <c r="O52">
+        <v>-2.095139</v>
+      </c>
+      <c r="P52">
+        <v>-7.014161000000001</v>
+      </c>
+      <c r="Q52">
+        <v>-6.899161000000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3762878445729549</v>
+      </c>
+      <c r="T52">
+        <v>1.969892547073371</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.009280153387482486</v>
+      </c>
+      <c r="W52">
+        <v>0.2365838993710692</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.04034849298905419</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.3084358719720121</v>
+      </c>
+      <c r="C53">
+        <v>9.862978904665944</v>
+      </c>
+      <c r="D53">
+        <v>49.26797890466595</v>
+      </c>
+      <c r="E53">
+        <v>40.545</v>
+      </c>
+      <c r="F53">
+        <v>40.545</v>
+      </c>
+      <c r="G53">
+        <v>1.14</v>
+      </c>
+      <c r="H53">
+        <v>79.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.498</v>
+      </c>
+      <c r="K53">
+        <v>0.115</v>
+      </c>
+      <c r="L53">
+        <v>0.383</v>
+      </c>
+      <c r="M53">
+        <v>9.682146000000001</v>
+      </c>
+      <c r="N53">
+        <v>-9.299146</v>
+      </c>
+      <c r="O53">
+        <v>-2.13880358</v>
+      </c>
+      <c r="P53">
+        <v>-7.160342420000001</v>
+      </c>
+      <c r="Q53">
+        <v>-7.045342420000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3831753516050561</v>
+      </c>
+      <c r="T53">
+        <v>2.010094435789154</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.009098189595571063</v>
+      </c>
+      <c r="W53">
+        <v>0.2366273523245776</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.03955734606770034</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.3104358719720121</v>
+      </c>
+      <c r="C54">
+        <v>8.705228738077189</v>
+      </c>
+      <c r="D54">
+        <v>48.90522873807719</v>
+      </c>
+      <c r="E54">
+        <v>41.34</v>
+      </c>
+      <c r="F54">
+        <v>41.34</v>
+      </c>
+      <c r="G54">
+        <v>1.14</v>
+      </c>
+      <c r="H54">
+        <v>79.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.498</v>
+      </c>
+      <c r="K54">
+        <v>0.115</v>
+      </c>
+      <c r="L54">
+        <v>0.383</v>
+      </c>
+      <c r="M54">
+        <v>9.871992000000001</v>
+      </c>
+      <c r="N54">
+        <v>-9.488992</v>
+      </c>
+      <c r="O54">
+        <v>-2.18246816</v>
+      </c>
+      <c r="P54">
+        <v>-7.306523840000001</v>
+      </c>
+      <c r="Q54">
+        <v>-7.19152384</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3903498380968281</v>
+      </c>
+      <c r="T54">
+        <v>2.051971403201428</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.008923224411040851</v>
+      </c>
+      <c r="W54">
+        <v>0.2366691340106435</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.03879662787409077</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.3124358719720121</v>
+      </c>
+      <c r="C55">
+        <v>7.552781241258636</v>
+      </c>
+      <c r="D55">
+        <v>48.54778124125864</v>
+      </c>
+      <c r="E55">
+        <v>42.13500000000001</v>
+      </c>
+      <c r="F55">
+        <v>42.13500000000001</v>
+      </c>
+      <c r="G55">
+        <v>1.14</v>
+      </c>
+      <c r="H55">
+        <v>79.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.498</v>
+      </c>
+      <c r="K55">
+        <v>0.115</v>
+      </c>
+      <c r="L55">
+        <v>0.383</v>
+      </c>
+      <c r="M55">
+        <v>10.061838</v>
+      </c>
+      <c r="N55">
+        <v>-9.678838000000002</v>
+      </c>
+      <c r="O55">
+        <v>-2.226132740000001</v>
+      </c>
+      <c r="P55">
+        <v>-7.452705260000002</v>
+      </c>
+      <c r="Q55">
+        <v>-7.337705260000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3978296218861223</v>
+      </c>
+      <c r="T55">
+        <v>2.095630369226991</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.00875486168630423</v>
+      </c>
+      <c r="W55">
+        <v>0.2367093390293106</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.03806461602740963</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.3144358719720121</v>
+      </c>
+      <c r="C56">
+        <v>6.405520986496242</v>
+      </c>
+      <c r="D56">
+        <v>48.19552098649624</v>
+      </c>
+      <c r="E56">
+        <v>42.93</v>
+      </c>
+      <c r="F56">
+        <v>42.93</v>
+      </c>
+      <c r="G56">
+        <v>1.14</v>
+      </c>
+      <c r="H56">
+        <v>79.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.498</v>
+      </c>
+      <c r="K56">
+        <v>0.115</v>
+      </c>
+      <c r="L56">
+        <v>0.383</v>
+      </c>
+      <c r="M56">
+        <v>10.251684</v>
+      </c>
+      <c r="N56">
+        <v>-9.868684000000002</v>
+      </c>
+      <c r="O56">
+        <v>-2.26979732</v>
+      </c>
+      <c r="P56">
+        <v>-7.598886680000001</v>
+      </c>
+      <c r="Q56">
+        <v>-7.483886680000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4056346136662554</v>
+      </c>
+      <c r="T56">
+        <v>2.141187551166707</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.008592734618039338</v>
+      </c>
+      <c r="W56">
+        <v>0.2367480549732122</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.0373597157306057</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.3164358719720122</v>
+      </c>
+      <c r="C57">
+        <v>5.26333587209318</v>
+      </c>
+      <c r="D57">
+        <v>47.84833587209318</v>
+      </c>
+      <c r="E57">
+        <v>43.725</v>
+      </c>
+      <c r="F57">
+        <v>43.725</v>
+      </c>
+      <c r="G57">
+        <v>1.14</v>
+      </c>
+      <c r="H57">
+        <v>79.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.498</v>
+      </c>
+      <c r="K57">
+        <v>0.115</v>
+      </c>
+      <c r="L57">
+        <v>0.383</v>
+      </c>
+      <c r="M57">
+        <v>10.44153</v>
+      </c>
+      <c r="N57">
+        <v>-10.05853</v>
+      </c>
+      <c r="O57">
+        <v>-2.3134619</v>
+      </c>
+      <c r="P57">
+        <v>-7.745068100000001</v>
+      </c>
+      <c r="Q57">
+        <v>-7.630068100000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4137864939699501</v>
+      </c>
+      <c r="T57">
+        <v>2.188769496748191</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.008436503079529532</v>
+      </c>
+      <c r="W57">
+        <v>0.2367853630646084</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.03668044817186744</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3184358719720121</v>
+      </c>
+      <c r="C58">
+        <v>4.126117003429009</v>
+      </c>
+      <c r="D58">
+        <v>47.50611700342901</v>
+      </c>
+      <c r="E58">
+        <v>44.52</v>
+      </c>
+      <c r="F58">
+        <v>44.52</v>
+      </c>
+      <c r="G58">
+        <v>1.14</v>
+      </c>
+      <c r="H58">
+        <v>79.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.498</v>
+      </c>
+      <c r="K58">
+        <v>0.115</v>
+      </c>
+      <c r="L58">
+        <v>0.383</v>
+      </c>
+      <c r="M58">
+        <v>10.631376</v>
+      </c>
+      <c r="N58">
+        <v>-10.248376</v>
+      </c>
+      <c r="O58">
+        <v>-2.35712648</v>
+      </c>
+      <c r="P58">
+        <v>-7.891249520000001</v>
+      </c>
+      <c r="Q58">
+        <v>-7.77624952</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4223089142874489</v>
+      </c>
+      <c r="T58">
+        <v>2.238514258037922</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.008285851238823647</v>
+      </c>
+      <c r="W58">
+        <v>0.2368213387241689</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.03602544016879849</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3204358719720121</v>
+      </c>
+      <c r="C59">
+        <v>2.993758579086311</v>
+      </c>
+      <c r="D59">
+        <v>47.16875857908632</v>
+      </c>
+      <c r="E59">
+        <v>45.315</v>
+      </c>
+      <c r="F59">
+        <v>45.315</v>
+      </c>
+      <c r="G59">
+        <v>1.14</v>
+      </c>
+      <c r="H59">
+        <v>79.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.498</v>
+      </c>
+      <c r="K59">
+        <v>0.115</v>
+      </c>
+      <c r="L59">
+        <v>0.383</v>
+      </c>
+      <c r="M59">
+        <v>10.821222</v>
+      </c>
+      <c r="N59">
+        <v>-10.438222</v>
+      </c>
+      <c r="O59">
+        <v>-2.40079106</v>
+      </c>
+      <c r="P59">
+        <v>-8.037430940000004</v>
+      </c>
+      <c r="Q59">
+        <v>-7.922430940000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4312277262476221</v>
+      </c>
+      <c r="T59">
+        <v>2.290572729155083</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.008140485427616214</v>
+      </c>
+      <c r="W59">
+        <v>0.2368560520798852</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.03539341490267911</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.3224358719720121</v>
+      </c>
+      <c r="C60">
+        <v>1.866157781795479</v>
+      </c>
+      <c r="D60">
+        <v>46.83615778179548</v>
+      </c>
+      <c r="E60">
+        <v>46.11</v>
+      </c>
+      <c r="F60">
+        <v>46.11</v>
+      </c>
+      <c r="G60">
+        <v>1.14</v>
+      </c>
+      <c r="H60">
+        <v>79.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.498</v>
+      </c>
+      <c r="K60">
+        <v>0.115</v>
+      </c>
+      <c r="L60">
+        <v>0.383</v>
+      </c>
+      <c r="M60">
+        <v>11.011068</v>
+      </c>
+      <c r="N60">
+        <v>-10.628068</v>
+      </c>
+      <c r="O60">
+        <v>-2.44445564</v>
+      </c>
+      <c r="P60">
+        <v>-8.18361236</v>
+      </c>
+      <c r="Q60">
+        <v>-8.068612359999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.440571243539232</v>
+      </c>
+      <c r="T60">
+        <v>2.345110175087346</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.008000132230588349</v>
+      </c>
+      <c r="W60">
+        <v>0.2368895684233355</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.03478318361125377</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3244358719720121</v>
+      </c>
+      <c r="C61">
+        <v>0.743214673960729</v>
+      </c>
+      <c r="D61">
+        <v>46.50821467396072</v>
+      </c>
+      <c r="E61">
+        <v>46.90499999999999</v>
+      </c>
+      <c r="F61">
+        <v>46.90499999999999</v>
+      </c>
+      <c r="G61">
+        <v>1.14</v>
+      </c>
+      <c r="H61">
+        <v>79.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.498</v>
+      </c>
+      <c r="K61">
+        <v>0.115</v>
+      </c>
+      <c r="L61">
+        <v>0.383</v>
+      </c>
+      <c r="M61">
+        <v>11.200914</v>
+      </c>
+      <c r="N61">
+        <v>-10.817914</v>
+      </c>
+      <c r="O61">
+        <v>-2.488120219999999</v>
+      </c>
+      <c r="P61">
+        <v>-8.329793779999999</v>
+      </c>
+      <c r="Q61">
+        <v>-8.214793779999999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4503705421621402</v>
+      </c>
+      <c r="T61">
+        <v>2.402307984235818</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.007864536769052955</v>
+      </c>
+      <c r="W61">
+        <v>0.2369219486195502</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.03419363812631726</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3264358719720121</v>
+      </c>
+      <c r="C62">
+        <v>-0.3751679024551038</v>
+      </c>
+      <c r="D62">
+        <v>46.18483209754489</v>
+      </c>
+      <c r="E62">
+        <v>47.7</v>
+      </c>
+      <c r="F62">
+        <v>47.7</v>
+      </c>
+      <c r="G62">
+        <v>1.14</v>
+      </c>
+      <c r="H62">
+        <v>79.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.498</v>
+      </c>
+      <c r="K62">
+        <v>0.115</v>
+      </c>
+      <c r="L62">
+        <v>0.383</v>
+      </c>
+      <c r="M62">
+        <v>11.39076</v>
+      </c>
+      <c r="N62">
+        <v>-11.00776</v>
+      </c>
+      <c r="O62">
+        <v>-2.5317848</v>
+      </c>
+      <c r="P62">
+        <v>-8.475975200000001</v>
+      </c>
+      <c r="Q62">
+        <v>-8.3609752</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4606598057161937</v>
+      </c>
+      <c r="T62">
+        <v>2.462365683841714</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.007733461156235404</v>
+      </c>
+      <c r="W62">
+        <v>0.236953249475891</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.03362374415754521</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3284358719720121</v>
+      </c>
+      <c r="C63">
+        <v>-1.489084421897878</v>
+      </c>
+      <c r="D63">
+        <v>45.86591557810212</v>
+      </c>
+      <c r="E63">
+        <v>48.495</v>
+      </c>
+      <c r="F63">
+        <v>48.495</v>
+      </c>
+      <c r="G63">
+        <v>1.14</v>
+      </c>
+      <c r="H63">
+        <v>79.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.498</v>
+      </c>
+      <c r="K63">
+        <v>0.115</v>
+      </c>
+      <c r="L63">
+        <v>0.383</v>
+      </c>
+      <c r="M63">
+        <v>11.580606</v>
+      </c>
+      <c r="N63">
+        <v>-11.197606</v>
+      </c>
+      <c r="O63">
+        <v>-2.57544938</v>
+      </c>
+      <c r="P63">
+        <v>-8.62215662</v>
+      </c>
+      <c r="Q63">
+        <v>-8.50715662</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4714767238114808</v>
+      </c>
+      <c r="T63">
+        <v>2.525503265478681</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.007606683104493841</v>
+      </c>
+      <c r="W63">
+        <v>0.2369835240746469</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.03307253523692966</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3304358719720121</v>
+      </c>
+      <c r="C64">
+        <v>-2.598626767240802</v>
+      </c>
+      <c r="D64">
+        <v>45.5513732327592</v>
+      </c>
+      <c r="E64">
+        <v>49.29</v>
+      </c>
+      <c r="F64">
+        <v>49.29</v>
+      </c>
+      <c r="G64">
+        <v>1.14</v>
+      </c>
+      <c r="H64">
+        <v>79.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.498</v>
+      </c>
+      <c r="K64">
+        <v>0.115</v>
+      </c>
+      <c r="L64">
+        <v>0.383</v>
+      </c>
+      <c r="M64">
+        <v>11.770452</v>
+      </c>
+      <c r="N64">
+        <v>-11.387452</v>
+      </c>
+      <c r="O64">
+        <v>-2.61911396</v>
+      </c>
+      <c r="P64">
+        <v>-8.76833804</v>
+      </c>
+      <c r="Q64">
+        <v>-8.65333804</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.482862953385467</v>
+      </c>
+      <c r="T64">
+        <v>2.59196387772812</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.007483994667324585</v>
+      </c>
+      <c r="W64">
+        <v>0.2370128220734429</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.03253910724923736</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3324358719720121</v>
+      </c>
+      <c r="C65">
+        <v>-3.703884318042363</v>
+      </c>
+      <c r="D65">
+        <v>45.24111568195764</v>
+      </c>
+      <c r="E65">
+        <v>50.085</v>
+      </c>
+      <c r="F65">
+        <v>50.085</v>
+      </c>
+      <c r="G65">
+        <v>1.14</v>
+      </c>
+      <c r="H65">
+        <v>79.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.498</v>
+      </c>
+      <c r="K65">
+        <v>0.115</v>
+      </c>
+      <c r="L65">
+        <v>0.383</v>
+      </c>
+      <c r="M65">
+        <v>11.960298</v>
+      </c>
+      <c r="N65">
+        <v>-11.577298</v>
+      </c>
+      <c r="O65">
+        <v>-2.662778540000001</v>
+      </c>
+      <c r="P65">
+        <v>-8.914519460000001</v>
+      </c>
+      <c r="Q65">
+        <v>-8.799519460000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.4948646548283175</v>
+      </c>
+      <c r="T65">
+        <v>2.662016955504555</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.007365201101176575</v>
+      </c>
+      <c r="W65">
+        <v>0.237041189977039</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.03202261348337632</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.334435871972012</v>
+      </c>
+      <c r="C66">
+        <v>-4.804944035222022</v>
+      </c>
+      <c r="D66">
+        <v>44.93505596477798</v>
+      </c>
+      <c r="E66">
+        <v>50.88</v>
+      </c>
+      <c r="F66">
+        <v>50.88</v>
+      </c>
+      <c r="G66">
+        <v>1.14</v>
+      </c>
+      <c r="H66">
+        <v>79.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.498</v>
+      </c>
+      <c r="K66">
+        <v>0.115</v>
+      </c>
+      <c r="L66">
+        <v>0.383</v>
+      </c>
+      <c r="M66">
+        <v>12.150144</v>
+      </c>
+      <c r="N66">
+        <v>-11.767144</v>
+      </c>
+      <c r="O66">
+        <v>-2.70644312</v>
+      </c>
+      <c r="P66">
+        <v>-9.060700880000002</v>
+      </c>
+      <c r="Q66">
+        <v>-8.945700880000002</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5075331174624373</v>
+      </c>
+      <c r="T66">
+        <v>2.735961870935237</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.007250119833970692</v>
+      </c>
+      <c r="W66">
+        <v>0.2370686713836478</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.03152226014769854</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3364358719720121</v>
+      </c>
+      <c r="C67">
+        <v>-5.901890542321837</v>
+      </c>
+      <c r="D67">
+        <v>44.63310945767817</v>
+      </c>
+      <c r="E67">
+        <v>51.675</v>
+      </c>
+      <c r="F67">
+        <v>51.675</v>
+      </c>
+      <c r="G67">
+        <v>1.14</v>
+      </c>
+      <c r="H67">
+        <v>79.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.498</v>
+      </c>
+      <c r="K67">
+        <v>0.115</v>
+      </c>
+      <c r="L67">
+        <v>0.383</v>
+      </c>
+      <c r="M67">
+        <v>12.33999</v>
+      </c>
+      <c r="N67">
+        <v>-11.95699</v>
+      </c>
+      <c r="O67">
+        <v>-2.7501077</v>
+      </c>
+      <c r="P67">
+        <v>-9.2068823</v>
+      </c>
+      <c r="Q67">
+        <v>-9.0918823</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5209254922470785</v>
+      </c>
+      <c r="T67">
+        <v>2.814132210104816</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.00713857952883268</v>
+      </c>
+      <c r="W67">
+        <v>0.2370953072085148</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.0310373022992726</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3384358719720121</v>
+      </c>
+      <c r="C68">
+        <v>-6.994806203513747</v>
+      </c>
+      <c r="D68">
+        <v>44.33519379648626</v>
+      </c>
+      <c r="E68">
+        <v>52.47000000000001</v>
+      </c>
+      <c r="F68">
+        <v>52.47000000000001</v>
+      </c>
+      <c r="G68">
+        <v>1.14</v>
+      </c>
+      <c r="H68">
+        <v>79.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.498</v>
+      </c>
+      <c r="K68">
+        <v>0.115</v>
+      </c>
+      <c r="L68">
+        <v>0.383</v>
+      </c>
+      <c r="M68">
+        <v>12.529836</v>
+      </c>
+      <c r="N68">
+        <v>-12.146836</v>
+      </c>
+      <c r="O68">
+        <v>-2.79377228</v>
+      </c>
+      <c r="P68">
+        <v>-9.353063720000002</v>
+      </c>
+      <c r="Q68">
+        <v>-9.238063720000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5351056537837573</v>
+      </c>
+      <c r="T68">
+        <v>2.896900804519663</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.007030419232941276</v>
+      </c>
+      <c r="W68">
+        <v>0.2371211358871737</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.03056704014322298</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3404358719720121</v>
+      </c>
+      <c r="C69">
+        <v>-8.08377119850347</v>
+      </c>
+      <c r="D69">
+        <v>44.04122880149653</v>
+      </c>
+      <c r="E69">
+        <v>53.265</v>
+      </c>
+      <c r="F69">
+        <v>53.265</v>
+      </c>
+      <c r="G69">
+        <v>1.14</v>
+      </c>
+      <c r="H69">
+        <v>79.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.498</v>
+      </c>
+      <c r="K69">
+        <v>0.115</v>
+      </c>
+      <c r="L69">
+        <v>0.383</v>
+      </c>
+      <c r="M69">
+        <v>12.719682</v>
+      </c>
+      <c r="N69">
+        <v>-12.336682</v>
+      </c>
+      <c r="O69">
+        <v>-2.83743686</v>
+      </c>
+      <c r="P69">
+        <v>-9.499245139999999</v>
+      </c>
+      <c r="Q69">
+        <v>-9.384245139999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5501452190499319</v>
+      </c>
+      <c r="T69">
+        <v>2.984685677383895</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.006925487602598869</v>
+      </c>
+      <c r="W69">
+        <v>0.2371461935604994</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.0301108156634734</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3424358719720121</v>
+      </c>
+      <c r="C70">
+        <v>-9.168863594474104</v>
+      </c>
+      <c r="D70">
+        <v>43.7511364055259</v>
+      </c>
+      <c r="E70">
+        <v>54.06</v>
+      </c>
+      <c r="F70">
+        <v>54.06</v>
+      </c>
+      <c r="G70">
+        <v>1.14</v>
+      </c>
+      <c r="H70">
+        <v>79.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.498</v>
+      </c>
+      <c r="K70">
+        <v>0.115</v>
+      </c>
+      <c r="L70">
+        <v>0.383</v>
+      </c>
+      <c r="M70">
+        <v>12.909528</v>
+      </c>
+      <c r="N70">
+        <v>-12.526528</v>
+      </c>
+      <c r="O70">
+        <v>-2.881101440000001</v>
+      </c>
+      <c r="P70">
+        <v>-9.645426560000002</v>
+      </c>
+      <c r="Q70">
+        <v>-9.530426560000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5661247571452421</v>
+      </c>
+      <c r="T70">
+        <v>3.077957104802143</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.006823642196678297</v>
+      </c>
+      <c r="W70">
+        <v>0.2371705142434332</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.02966800955077509</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3444358719720121</v>
+      </c>
+      <c r="C71">
+        <v>-10.25015941520508</v>
+      </c>
+      <c r="D71">
+        <v>43.46484058479493</v>
+      </c>
+      <c r="E71">
+        <v>54.855</v>
+      </c>
+      <c r="F71">
+        <v>54.855</v>
+      </c>
+      <c r="G71">
+        <v>1.14</v>
+      </c>
+      <c r="H71">
+        <v>79.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.498</v>
+      </c>
+      <c r="K71">
+        <v>0.115</v>
+      </c>
+      <c r="L71">
+        <v>0.383</v>
+      </c>
+      <c r="M71">
+        <v>13.099374</v>
+      </c>
+      <c r="N71">
+        <v>-12.716374</v>
+      </c>
+      <c r="O71">
+        <v>-2.92476602</v>
+      </c>
+      <c r="P71">
+        <v>-9.791607980000002</v>
+      </c>
+      <c r="Q71">
+        <v>-9.676607980000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5831352331821855</v>
+      </c>
+      <c r="T71">
+        <v>3.177246043666728</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.006724748831509047</v>
+      </c>
+      <c r="W71">
+        <v>0.2371941299790356</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.02923803839786532</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3464358719720121</v>
+      </c>
+      <c r="C72">
+        <v>-11.32773270749492</v>
+      </c>
+      <c r="D72">
+        <v>43.18226729250509</v>
+      </c>
+      <c r="E72">
+        <v>55.65000000000001</v>
+      </c>
+      <c r="F72">
+        <v>55.65000000000001</v>
+      </c>
+      <c r="G72">
+        <v>1.14</v>
+      </c>
+      <c r="H72">
+        <v>79.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.498</v>
+      </c>
+      <c r="K72">
+        <v>0.115</v>
+      </c>
+      <c r="L72">
+        <v>0.383</v>
+      </c>
+      <c r="M72">
+        <v>13.28922</v>
+      </c>
+      <c r="N72">
+        <v>-12.90622</v>
+      </c>
+      <c r="O72">
+        <v>-2.9684306</v>
+      </c>
+      <c r="P72">
+        <v>-9.937789400000002</v>
+      </c>
+      <c r="Q72">
+        <v>-9.822789400000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6012797409549251</v>
+      </c>
+      <c r="T72">
+        <v>3.283154245122286</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.006628680991058917</v>
+      </c>
+      <c r="W72">
+        <v>0.2372170709793351</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.02882035213503886</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3484358719720121</v>
+      </c>
+      <c r="C73">
+        <v>-12.4016556050099</v>
+      </c>
+      <c r="D73">
+        <v>42.9033443949901</v>
+      </c>
+      <c r="E73">
+        <v>56.445</v>
+      </c>
+      <c r="F73">
+        <v>56.445</v>
+      </c>
+      <c r="G73">
+        <v>1.14</v>
+      </c>
+      <c r="H73">
+        <v>79.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.498</v>
+      </c>
+      <c r="K73">
+        <v>0.115</v>
+      </c>
+      <c r="L73">
+        <v>0.383</v>
+      </c>
+      <c r="M73">
+        <v>13.479066</v>
+      </c>
+      <c r="N73">
+        <v>-13.096066</v>
+      </c>
+      <c r="O73">
+        <v>-3.01209518</v>
+      </c>
+      <c r="P73">
+        <v>-10.08397082</v>
+      </c>
+      <c r="Q73">
+        <v>-9.968970820000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6206755940913016</v>
+      </c>
+      <c r="T73">
+        <v>3.396366460471329</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.006535319286959496</v>
+      </c>
+      <c r="W73">
+        <v>0.2372393657542741</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.02841443168243263</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3504358719720121</v>
+      </c>
+      <c r="C74">
+        <v>-13.47199838967394</v>
+      </c>
+      <c r="D74">
+        <v>42.62800161032606</v>
+      </c>
+      <c r="E74">
+        <v>57.23999999999999</v>
+      </c>
+      <c r="F74">
+        <v>57.23999999999999</v>
+      </c>
+      <c r="G74">
+        <v>1.14</v>
+      </c>
+      <c r="H74">
+        <v>79.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.498</v>
+      </c>
+      <c r="K74">
+        <v>0.115</v>
+      </c>
+      <c r="L74">
+        <v>0.383</v>
+      </c>
+      <c r="M74">
+        <v>13.668912</v>
+      </c>
+      <c r="N74">
+        <v>-13.285912</v>
+      </c>
+      <c r="O74">
+        <v>-3.055759759999999</v>
+      </c>
+      <c r="P74">
+        <v>-10.23015224</v>
+      </c>
+      <c r="Q74">
+        <v>-10.11515224</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6414568653088482</v>
+      </c>
+      <c r="T74">
+        <v>3.51766526263102</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.006444550963529504</v>
+      </c>
+      <c r="W74">
+        <v>0.2372610412299092</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.02801978679795425</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3524358719720121</v>
+      </c>
+      <c r="C75">
+        <v>-14.53882955070981</v>
+      </c>
+      <c r="D75">
+        <v>42.35617044929018</v>
+      </c>
+      <c r="E75">
+        <v>58.035</v>
+      </c>
+      <c r="F75">
+        <v>58.035</v>
+      </c>
+      <c r="G75">
+        <v>1.14</v>
+      </c>
+      <c r="H75">
+        <v>79.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.498</v>
+      </c>
+      <c r="K75">
+        <v>0.115</v>
+      </c>
+      <c r="L75">
+        <v>0.383</v>
+      </c>
+      <c r="M75">
+        <v>13.858758</v>
+      </c>
+      <c r="N75">
+        <v>-13.475758</v>
+      </c>
+      <c r="O75">
+        <v>-3.09942434</v>
+      </c>
+      <c r="P75">
+        <v>-10.37633366</v>
+      </c>
+      <c r="Q75">
+        <v>-10.26133366</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6637774899499165</v>
+      </c>
+      <c r="T75">
+        <v>3.647949161246983</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.006356269443481154</v>
+      </c>
+      <c r="W75">
+        <v>0.2372821228568967</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.02763595410209208</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3544358719720121</v>
+      </c>
+      <c r="C76">
+        <v>-15.60221584143564</v>
+      </c>
+      <c r="D76">
+        <v>42.08778415856435</v>
+      </c>
+      <c r="E76">
+        <v>58.83</v>
+      </c>
+      <c r="F76">
+        <v>58.83</v>
+      </c>
+      <c r="G76">
+        <v>1.14</v>
+      </c>
+      <c r="H76">
+        <v>79.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.498</v>
+      </c>
+      <c r="K76">
+        <v>0.115</v>
+      </c>
+      <c r="L76">
+        <v>0.383</v>
+      </c>
+      <c r="M76">
+        <v>14.048604</v>
+      </c>
+      <c r="N76">
+        <v>-13.665604</v>
+      </c>
+      <c r="O76">
+        <v>-3.14308892</v>
+      </c>
+      <c r="P76">
+        <v>-10.52251508</v>
+      </c>
+      <c r="Q76">
+        <v>-10.40751508</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6878150857172209</v>
+      </c>
+      <c r="T76">
+        <v>3.788254898218021</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.006270373910461138</v>
+      </c>
+      <c r="W76">
+        <v>0.2373026347101819</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.0272624952628745</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3564358719720121</v>
+      </c>
+      <c r="C77">
+        <v>-16.66222233391564</v>
+      </c>
+      <c r="D77">
+        <v>41.82277766608436</v>
+      </c>
+      <c r="E77">
+        <v>59.625</v>
+      </c>
+      <c r="F77">
+        <v>59.625</v>
+      </c>
+      <c r="G77">
+        <v>1.14</v>
+      </c>
+      <c r="H77">
+        <v>79.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.498</v>
+      </c>
+      <c r="K77">
+        <v>0.115</v>
+      </c>
+      <c r="L77">
+        <v>0.383</v>
+      </c>
+      <c r="M77">
+        <v>14.23845</v>
+      </c>
+      <c r="N77">
+        <v>-13.85545</v>
+      </c>
+      <c r="O77">
+        <v>-3.1867535</v>
+      </c>
+      <c r="P77">
+        <v>-10.6686965</v>
+      </c>
+      <c r="Q77">
+        <v>-10.5536965</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7137756891459099</v>
+      </c>
+      <c r="T77">
+        <v>3.939785094146742</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.006186768924988323</v>
+      </c>
+      <c r="W77">
+        <v>0.2373225995807128</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.02689899532603612</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3584358719720121</v>
+      </c>
+      <c r="C78">
+        <v>-17.71891247155918</v>
+      </c>
+      <c r="D78">
+        <v>41.56108752844082</v>
+      </c>
+      <c r="E78">
+        <v>60.42</v>
+      </c>
+      <c r="F78">
+        <v>60.42</v>
+      </c>
+      <c r="G78">
+        <v>1.14</v>
+      </c>
+      <c r="H78">
+        <v>79.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.498</v>
+      </c>
+      <c r="K78">
+        <v>0.115</v>
+      </c>
+      <c r="L78">
+        <v>0.383</v>
+      </c>
+      <c r="M78">
+        <v>14.428296</v>
+      </c>
+      <c r="N78">
+        <v>-14.045296</v>
+      </c>
+      <c r="O78">
+        <v>-3.23041808</v>
+      </c>
+      <c r="P78">
+        <v>-10.81487792</v>
+      </c>
+      <c r="Q78">
+        <v>-10.69987792</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7418996761936563</v>
+      </c>
+      <c r="T78">
+        <v>4.103942806402856</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.006105364070712161</v>
+      </c>
+      <c r="W78">
+        <v>0.2373420390599139</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.0265450611770095</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.360435871972012</v>
+      </c>
+      <c r="C79">
+        <v>-18.77234811975739</v>
+      </c>
+      <c r="D79">
+        <v>41.30265188024261</v>
+      </c>
+      <c r="E79">
+        <v>61.215</v>
+      </c>
+      <c r="F79">
+        <v>61.215</v>
+      </c>
+      <c r="G79">
+        <v>1.14</v>
+      </c>
+      <c r="H79">
+        <v>79.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.498</v>
+      </c>
+      <c r="K79">
+        <v>0.115</v>
+      </c>
+      <c r="L79">
+        <v>0.383</v>
+      </c>
+      <c r="M79">
+        <v>14.618142</v>
+      </c>
+      <c r="N79">
+        <v>-14.235142</v>
+      </c>
+      <c r="O79">
+        <v>-3.27408266</v>
+      </c>
+      <c r="P79">
+        <v>-10.96105934</v>
+      </c>
+      <c r="Q79">
+        <v>-10.84605934</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7724692273325107</v>
+      </c>
+      <c r="T79">
+        <v>4.282375102333415</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.006026073628235378</v>
+      </c>
+      <c r="W79">
+        <v>0.2373609736175774</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.02620032012276241</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3624358719720121</v>
+      </c>
+      <c r="C80">
+        <v>-19.8225896146422</v>
+      </c>
+      <c r="D80">
+        <v>41.04741038535781</v>
+      </c>
+      <c r="E80">
+        <v>62.01000000000001</v>
+      </c>
+      <c r="F80">
+        <v>62.01000000000001</v>
+      </c>
+      <c r="G80">
+        <v>1.14</v>
+      </c>
+      <c r="H80">
+        <v>79.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.498</v>
+      </c>
+      <c r="K80">
+        <v>0.115</v>
+      </c>
+      <c r="L80">
+        <v>0.383</v>
+      </c>
+      <c r="M80">
+        <v>14.807988</v>
+      </c>
+      <c r="N80">
+        <v>-14.424988</v>
+      </c>
+      <c r="O80">
+        <v>-3.317747240000001</v>
+      </c>
+      <c r="P80">
+        <v>-11.10724076</v>
+      </c>
+      <c r="Q80">
+        <v>-10.99224076</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8058178285748978</v>
+      </c>
+      <c r="T80">
+        <v>4.477028516075844</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.005948816274027233</v>
+      </c>
+      <c r="W80">
+        <v>0.2373794226737623</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.02586441858272703</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3644358719720121</v>
+      </c>
+      <c r="C81">
+        <v>-20.86969581004861</v>
+      </c>
+      <c r="D81">
+        <v>40.79530418995139</v>
+      </c>
+      <c r="E81">
+        <v>62.805</v>
+      </c>
+      <c r="F81">
+        <v>62.805</v>
+      </c>
+      <c r="G81">
+        <v>1.14</v>
+      </c>
+      <c r="H81">
+        <v>79.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.498</v>
+      </c>
+      <c r="K81">
+        <v>0.115</v>
+      </c>
+      <c r="L81">
+        <v>0.383</v>
+      </c>
+      <c r="M81">
+        <v>14.997834</v>
+      </c>
+      <c r="N81">
+        <v>-14.614834</v>
+      </c>
+      <c r="O81">
+        <v>-3.36141182</v>
+      </c>
+      <c r="P81">
+        <v>-11.25342218</v>
+      </c>
+      <c r="Q81">
+        <v>-11.13842218</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8423424870784644</v>
+      </c>
+      <c r="T81">
+        <v>4.690220350174694</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.005873514802204104</v>
+      </c>
+      <c r="W81">
+        <v>0.2373974046652337</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.02553702087914822</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3664358719720121</v>
+      </c>
+      <c r="C82">
+        <v>-21.91372412275691</v>
+      </c>
+      <c r="D82">
+        <v>40.54627587724309</v>
+      </c>
+      <c r="E82">
+        <v>63.6</v>
+      </c>
+      <c r="F82">
+        <v>63.6</v>
+      </c>
+      <c r="G82">
+        <v>1.14</v>
+      </c>
+      <c r="H82">
+        <v>79.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.498</v>
+      </c>
+      <c r="K82">
+        <v>0.115</v>
+      </c>
+      <c r="L82">
+        <v>0.383</v>
+      </c>
+      <c r="M82">
+        <v>15.18768</v>
+      </c>
+      <c r="N82">
+        <v>-14.80468</v>
+      </c>
+      <c r="O82">
+        <v>-3.4050764</v>
+      </c>
+      <c r="P82">
+        <v>-11.3996036</v>
+      </c>
+      <c r="Q82">
+        <v>-11.2846036</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.8825196114323877</v>
+      </c>
+      <c r="T82">
+        <v>4.924731367683429</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.005800095867176553</v>
+      </c>
+      <c r="W82">
+        <v>0.2374149371069182</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.02521780811815888</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3684358719720121</v>
+      </c>
+      <c r="C83">
+        <v>-22.95473057608786</v>
+      </c>
+      <c r="D83">
+        <v>40.30026942391215</v>
+      </c>
+      <c r="E83">
+        <v>64.39500000000001</v>
+      </c>
+      <c r="F83">
+        <v>64.39500000000001</v>
+      </c>
+      <c r="G83">
+        <v>1.14</v>
+      </c>
+      <c r="H83">
+        <v>79.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.498</v>
+      </c>
+      <c r="K83">
+        <v>0.115</v>
+      </c>
+      <c r="L83">
+        <v>0.383</v>
+      </c>
+      <c r="M83">
+        <v>15.377526</v>
+      </c>
+      <c r="N83">
+        <v>-14.994526</v>
+      </c>
+      <c r="O83">
+        <v>-3.448740980000001</v>
+      </c>
+      <c r="P83">
+        <v>-11.54578502</v>
+      </c>
+      <c r="Q83">
+        <v>-11.43078502</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9269259067709343</v>
+      </c>
+      <c r="T83">
+        <v>5.183927755456241</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.005728489745359558</v>
+      </c>
+      <c r="W83">
+        <v>0.2374320366488082</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.02490647715373717</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3704358719720121</v>
+      </c>
+      <c r="C84">
+        <v>-23.99276984192044</v>
+      </c>
+      <c r="D84">
+        <v>40.05723015807957</v>
+      </c>
+      <c r="E84">
+        <v>65.19000000000001</v>
+      </c>
+      <c r="F84">
+        <v>65.19000000000001</v>
+      </c>
+      <c r="G84">
+        <v>1.14</v>
+      </c>
+      <c r="H84">
+        <v>79.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.498</v>
+      </c>
+      <c r="K84">
+        <v>0.115</v>
+      </c>
+      <c r="L84">
+        <v>0.383</v>
+      </c>
+      <c r="M84">
+        <v>15.567372</v>
+      </c>
+      <c r="N84">
+        <v>-15.184372</v>
+      </c>
+      <c r="O84">
+        <v>-3.49240556</v>
+      </c>
+      <c r="P84">
+        <v>-11.69196644</v>
+      </c>
+      <c r="Q84">
+        <v>-11.57696644</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.9762662349248752</v>
+      </c>
+      <c r="T84">
+        <v>5.471923741870477</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.005658630114318586</v>
+      </c>
+      <c r="W84">
+        <v>0.2374487191287007</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.02460273962747217</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3724358719720121</v>
+      </c>
+      <c r="C85">
+        <v>-25.02789528119837</v>
+      </c>
+      <c r="D85">
+        <v>39.81710471880163</v>
+      </c>
+      <c r="E85">
+        <v>65.985</v>
+      </c>
+      <c r="F85">
+        <v>65.985</v>
+      </c>
+      <c r="G85">
+        <v>1.14</v>
+      </c>
+      <c r="H85">
+        <v>79.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.498</v>
+      </c>
+      <c r="K85">
+        <v>0.115</v>
+      </c>
+      <c r="L85">
+        <v>0.383</v>
+      </c>
+      <c r="M85">
+        <v>15.757218</v>
+      </c>
+      <c r="N85">
+        <v>-15.374218</v>
+      </c>
+      <c r="O85">
+        <v>-3.53607014</v>
+      </c>
+      <c r="P85">
+        <v>-11.83814786</v>
+      </c>
+      <c r="Q85">
+        <v>-11.72314786</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.031411307567515</v>
+      </c>
+      <c r="T85">
+        <v>5.793801609039329</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.005590453847881015</v>
+      </c>
+      <c r="W85">
+        <v>0.237464999621126</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.02430632107774355</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3744358719720121</v>
+      </c>
+      <c r="C86">
+        <v>-26.0601589829884</v>
+      </c>
+      <c r="D86">
+        <v>39.5798410170116</v>
+      </c>
+      <c r="E86">
+        <v>66.78</v>
+      </c>
+      <c r="F86">
+        <v>66.78</v>
+      </c>
+      <c r="G86">
+        <v>1.14</v>
+      </c>
+      <c r="H86">
+        <v>79.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.498</v>
+      </c>
+      <c r="K86">
+        <v>0.115</v>
+      </c>
+      <c r="L86">
+        <v>0.383</v>
+      </c>
+      <c r="M86">
+        <v>15.947064</v>
+      </c>
+      <c r="N86">
+        <v>-15.564064</v>
+      </c>
+      <c r="O86">
+        <v>-3.57973472</v>
+      </c>
+      <c r="P86">
+        <v>-11.98432928</v>
+      </c>
+      <c r="Q86">
+        <v>-11.86932928</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.093449514290484</v>
+      </c>
+      <c r="T86">
+        <v>6.155914209604283</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.005523900825882432</v>
+      </c>
+      <c r="W86">
+        <v>0.2374808924827793</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.02401696011253229</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3764358719720121</v>
+      </c>
+      <c r="C87">
+        <v>-27.0896118021503</v>
+      </c>
+      <c r="D87">
+        <v>39.3453881978497</v>
+      </c>
+      <c r="E87">
+        <v>67.575</v>
+      </c>
+      <c r="F87">
+        <v>67.575</v>
+      </c>
+      <c r="G87">
+        <v>1.14</v>
+      </c>
+      <c r="H87">
+        <v>79.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.498</v>
+      </c>
+      <c r="K87">
+        <v>0.115</v>
+      </c>
+      <c r="L87">
+        <v>0.383</v>
+      </c>
+      <c r="M87">
+        <v>16.13691</v>
+      </c>
+      <c r="N87">
+        <v>-15.75391</v>
+      </c>
+      <c r="O87">
+        <v>-3.6233993</v>
+      </c>
+      <c r="P87">
+        <v>-12.1305107</v>
+      </c>
+      <c r="Q87">
+        <v>-12.0155107</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.16375948190985</v>
+      </c>
+      <c r="T87">
+        <v>6.56630849024457</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.005458913757342638</v>
+      </c>
+      <c r="W87">
+        <v>0.2374964113947466</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.02373440764062007</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3784358719720121</v>
+      </c>
+      <c r="C88">
+        <v>-28.11630339567603</v>
+      </c>
+      <c r="D88">
+        <v>39.11369660432397</v>
+      </c>
+      <c r="E88">
+        <v>68.37</v>
+      </c>
+      <c r="F88">
+        <v>68.37</v>
+      </c>
+      <c r="G88">
+        <v>1.14</v>
+      </c>
+      <c r="H88">
+        <v>79.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.498</v>
+      </c>
+      <c r="K88">
+        <v>0.115</v>
+      </c>
+      <c r="L88">
+        <v>0.383</v>
+      </c>
+      <c r="M88">
+        <v>16.326756</v>
+      </c>
+      <c r="N88">
+        <v>-15.943756</v>
+      </c>
+      <c r="O88">
+        <v>-3.667063880000001</v>
+      </c>
+      <c r="P88">
+        <v>-12.27669212</v>
+      </c>
+      <c r="Q88">
+        <v>-12.16169212</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.244113730617696</v>
+      </c>
+      <c r="T88">
+        <v>7.035330525262038</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.005395438015978188</v>
+      </c>
+      <c r="W88">
+        <v>0.2375115694017844</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.0234584261564269</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3804358719720121</v>
+      </c>
+      <c r="C89">
+        <v>-29.14028225775249</v>
+      </c>
+      <c r="D89">
+        <v>38.88471774224752</v>
+      </c>
+      <c r="E89">
+        <v>69.16500000000001</v>
+      </c>
+      <c r="F89">
+        <v>69.16500000000001</v>
+      </c>
+      <c r="G89">
+        <v>1.14</v>
+      </c>
+      <c r="H89">
+        <v>79.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.498</v>
+      </c>
+      <c r="K89">
+        <v>0.115</v>
+      </c>
+      <c r="L89">
+        <v>0.383</v>
+      </c>
+      <c r="M89">
+        <v>16.516602</v>
+      </c>
+      <c r="N89">
+        <v>-16.133602</v>
+      </c>
+      <c r="O89">
+        <v>-3.71072846</v>
+      </c>
+      <c r="P89">
+        <v>-12.42287354</v>
+      </c>
+      <c r="Q89">
+        <v>-12.30787354</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.336830171434442</v>
+      </c>
+      <c r="T89">
+        <v>7.576509796436041</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.005333421487058899</v>
+      </c>
+      <c r="W89">
+        <v>0.2375263789488903</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.0231887890741691</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3824358719720121</v>
+      </c>
+      <c r="C90">
+        <v>-30.16159575359971</v>
+      </c>
+      <c r="D90">
+        <v>38.65840424640029</v>
+      </c>
+      <c r="E90">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="F90">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="G90">
+        <v>1.14</v>
+      </c>
+      <c r="H90">
+        <v>79.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.498</v>
+      </c>
+      <c r="K90">
+        <v>0.115</v>
+      </c>
+      <c r="L90">
+        <v>0.383</v>
+      </c>
+      <c r="M90">
+        <v>16.706448</v>
+      </c>
+      <c r="N90">
+        <v>-16.323448</v>
+      </c>
+      <c r="O90">
+        <v>-3.75439304</v>
+      </c>
+      <c r="P90">
+        <v>-12.56905496</v>
+      </c>
+      <c r="Q90">
+        <v>-12.45405496</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.444999352387312</v>
+      </c>
+      <c r="T90">
+        <v>8.207885612805713</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.005272814424705958</v>
+      </c>
+      <c r="W90">
+        <v>0.2375408519153802</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.02292528010741712</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3844358719720121</v>
+      </c>
+      <c r="C91">
+        <v>-31.18029015213442</v>
+      </c>
+      <c r="D91">
+        <v>38.43470984786558</v>
+      </c>
+      <c r="E91">
+        <v>70.755</v>
+      </c>
+      <c r="F91">
+        <v>70.755</v>
+      </c>
+      <c r="G91">
+        <v>1.14</v>
+      </c>
+      <c r="H91">
+        <v>79.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.498</v>
+      </c>
+      <c r="K91">
+        <v>0.115</v>
+      </c>
+      <c r="L91">
+        <v>0.383</v>
+      </c>
+      <c r="M91">
+        <v>16.896294</v>
+      </c>
+      <c r="N91">
+        <v>-16.513294</v>
+      </c>
+      <c r="O91">
+        <v>-3.79805762</v>
+      </c>
+      <c r="P91">
+        <v>-12.71523638</v>
+      </c>
+      <c r="Q91">
+        <v>-12.60023638</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.572835657149795</v>
+      </c>
+      <c r="T91">
+        <v>8.954057032151688</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.005213569318810384</v>
+      </c>
+      <c r="W91">
+        <v>0.2375549996466681</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.02266769269047986</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3864358719720121</v>
+      </c>
+      <c r="C92">
+        <v>-32.19641065750597</v>
+      </c>
+      <c r="D92">
+        <v>38.21358934249402</v>
+      </c>
+      <c r="E92">
+        <v>71.55</v>
+      </c>
+      <c r="F92">
+        <v>71.55</v>
+      </c>
+      <c r="G92">
+        <v>1.14</v>
+      </c>
+      <c r="H92">
+        <v>79.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.498</v>
+      </c>
+      <c r="K92">
+        <v>0.115</v>
+      </c>
+      <c r="L92">
+        <v>0.383</v>
+      </c>
+      <c r="M92">
+        <v>17.08614</v>
+      </c>
+      <c r="N92">
+        <v>-16.70314</v>
+      </c>
+      <c r="O92">
+        <v>-3.8417222</v>
+      </c>
+      <c r="P92">
+        <v>-12.8614178</v>
+      </c>
+      <c r="Q92">
+        <v>-12.7464178</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.726239222864775</v>
+      </c>
+      <c r="T92">
+        <v>9.849462735366856</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.005155640770823603</v>
+      </c>
+      <c r="W92">
+        <v>0.2375688329839273</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.0224158294383634</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3884358719720121</v>
+      </c>
+      <c r="C93">
+        <v>-33.21000143954994</v>
+      </c>
+      <c r="D93">
+        <v>37.99499856045006</v>
+      </c>
+      <c r="E93">
+        <v>72.345</v>
+      </c>
+      <c r="F93">
+        <v>72.345</v>
+      </c>
+      <c r="G93">
+        <v>1.14</v>
+      </c>
+      <c r="H93">
+        <v>79.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.498</v>
+      </c>
+      <c r="K93">
+        <v>0.115</v>
+      </c>
+      <c r="L93">
+        <v>0.383</v>
+      </c>
+      <c r="M93">
+        <v>17.275986</v>
+      </c>
+      <c r="N93">
+        <v>-16.892986</v>
+      </c>
+      <c r="O93">
+        <v>-3.88538678</v>
+      </c>
+      <c r="P93">
+        <v>-13.00759922</v>
+      </c>
+      <c r="Q93">
+        <v>-12.89259922</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.91373246984975</v>
+      </c>
+      <c r="T93">
+        <v>10.94384748374095</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.00509898537773763</v>
+      </c>
+      <c r="W93">
+        <v>0.2375823622917962</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.02216950164233744</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3904358719720121</v>
+      </c>
+      <c r="C94">
+        <v>-34.2211056632025</v>
+      </c>
+      <c r="D94">
+        <v>37.7788943367975</v>
+      </c>
+      <c r="E94">
+        <v>73.14</v>
+      </c>
+      <c r="F94">
+        <v>73.14</v>
+      </c>
+      <c r="G94">
+        <v>1.14</v>
+      </c>
+      <c r="H94">
+        <v>79.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.498</v>
+      </c>
+      <c r="K94">
+        <v>0.115</v>
+      </c>
+      <c r="L94">
+        <v>0.383</v>
+      </c>
+      <c r="M94">
+        <v>17.465832</v>
+      </c>
+      <c r="N94">
+        <v>-17.082832</v>
+      </c>
+      <c r="O94">
+        <v>-3.92905136</v>
+      </c>
+      <c r="P94">
+        <v>-13.15378064</v>
+      </c>
+      <c r="Q94">
+        <v>-13.03878064</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.14809902858097</v>
+      </c>
+      <c r="T94">
+        <v>12.31182841920858</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.005043561623631784</v>
+      </c>
+      <c r="W94">
+        <v>0.2375955974842767</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.02192852879839902</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3924358719720121</v>
+      </c>
+      <c r="C95">
+        <v>-35.22976551691659</v>
+      </c>
+      <c r="D95">
+        <v>37.56523448308341</v>
+      </c>
+      <c r="E95">
+        <v>73.935</v>
+      </c>
+      <c r="F95">
+        <v>73.935</v>
+      </c>
+      <c r="G95">
+        <v>1.14</v>
+      </c>
+      <c r="H95">
+        <v>79.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.498</v>
+      </c>
+      <c r="K95">
+        <v>0.115</v>
+      </c>
+      <c r="L95">
+        <v>0.383</v>
+      </c>
+      <c r="M95">
+        <v>17.655678</v>
+      </c>
+      <c r="N95">
+        <v>-17.272678</v>
+      </c>
+      <c r="O95">
+        <v>-3.972715940000001</v>
+      </c>
+      <c r="P95">
+        <v>-13.29996206</v>
+      </c>
+      <c r="Q95">
+        <v>-13.18496206</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.449427461235394</v>
+      </c>
+      <c r="T95">
+        <v>14.07066105052409</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.004989329778216389</v>
+      </c>
+      <c r="W95">
+        <v>0.2376085480489619</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.02169273816615813</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3944358719720121</v>
+      </c>
+      <c r="C96">
+        <v>-36.23602224011936</v>
+      </c>
+      <c r="D96">
+        <v>37.35397775988064</v>
+      </c>
+      <c r="E96">
+        <v>74.73</v>
+      </c>
+      <c r="F96">
+        <v>74.73</v>
+      </c>
+      <c r="G96">
+        <v>1.14</v>
+      </c>
+      <c r="H96">
+        <v>79.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.498</v>
+      </c>
+      <c r="K96">
+        <v>0.115</v>
+      </c>
+      <c r="L96">
+        <v>0.383</v>
+      </c>
+      <c r="M96">
+        <v>17.845524</v>
+      </c>
+      <c r="N96">
+        <v>-17.462524</v>
+      </c>
+      <c r="O96">
+        <v>-4.01638052</v>
+      </c>
+      <c r="P96">
+        <v>-13.44614348</v>
+      </c>
+      <c r="Q96">
+        <v>-13.33114348</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.851198704774627</v>
+      </c>
+      <c r="T96">
+        <v>16.41577122561144</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.004936251801852386</v>
+      </c>
+      <c r="W96">
+        <v>0.2376212230697176</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.02146196435587988</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3964358719720121</v>
+      </c>
+      <c r="C97">
+        <v>-37.23991614974823</v>
+      </c>
+      <c r="D97">
+        <v>37.14508385025177</v>
+      </c>
+      <c r="E97">
+        <v>75.52500000000001</v>
+      </c>
+      <c r="F97">
+        <v>75.52500000000001</v>
+      </c>
+      <c r="G97">
+        <v>1.14</v>
+      </c>
+      <c r="H97">
+        <v>79.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.498</v>
+      </c>
+      <c r="K97">
+        <v>0.115</v>
+      </c>
+      <c r="L97">
+        <v>0.383</v>
+      </c>
+      <c r="M97">
+        <v>18.03537</v>
+      </c>
+      <c r="N97">
+        <v>-17.65237</v>
+      </c>
+      <c r="O97">
+        <v>-4.060045100000001</v>
+      </c>
+      <c r="P97">
+        <v>-13.5923249</v>
+      </c>
+      <c r="Q97">
+        <v>-13.4773249</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.413678445729555</v>
+      </c>
+      <c r="T97">
+        <v>19.69892547073374</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.004884291256569728</v>
+      </c>
+      <c r="W97">
+        <v>0.2376336312479312</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.02123604894160747</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3984358719720121</v>
+      </c>
+      <c r="C98">
+        <v>-38.24148666590153</v>
+      </c>
+      <c r="D98">
+        <v>36.93851333409846</v>
+      </c>
+      <c r="E98">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="F98">
+        <v>76.31999999999999</v>
+      </c>
+      <c r="G98">
+        <v>1.14</v>
+      </c>
+      <c r="H98">
+        <v>79.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.498</v>
+      </c>
+      <c r="K98">
+        <v>0.115</v>
+      </c>
+      <c r="L98">
+        <v>0.383</v>
+      </c>
+      <c r="M98">
+        <v>18.225216</v>
+      </c>
+      <c r="N98">
+        <v>-17.842216</v>
+      </c>
+      <c r="O98">
+        <v>-4.10370968</v>
+      </c>
+      <c r="P98">
+        <v>-13.73850632</v>
+      </c>
+      <c r="Q98">
+        <v>-13.62350632</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.257398057161934</v>
+      </c>
+      <c r="T98">
+        <v>24.62365683841712</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.004833413222647127</v>
+      </c>
+      <c r="W98">
+        <v>0.2376457809224319</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.02101484009846577</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.4004358719720121</v>
+      </c>
+      <c r="C99">
+        <v>-39.24077233663807</v>
+      </c>
+      <c r="D99">
+        <v>36.73422766336192</v>
+      </c>
+      <c r="E99">
+        <v>77.11499999999999</v>
+      </c>
+      <c r="F99">
+        <v>77.11499999999999</v>
+      </c>
+      <c r="G99">
+        <v>1.14</v>
+      </c>
+      <c r="H99">
+        <v>79.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.498</v>
+      </c>
+      <c r="K99">
+        <v>0.115</v>
+      </c>
+      <c r="L99">
+        <v>0.383</v>
+      </c>
+      <c r="M99">
+        <v>18.415062</v>
+      </c>
+      <c r="N99">
+        <v>-18.032062</v>
+      </c>
+      <c r="O99">
+        <v>-4.147374259999999</v>
+      </c>
+      <c r="P99">
+        <v>-13.88468774</v>
+      </c>
+      <c r="Q99">
+        <v>-13.76968774</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.663597409549245</v>
+      </c>
+      <c r="T99">
+        <v>32.83154245122282</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.004783584220351797</v>
+      </c>
+      <c r="W99">
+        <v>0.23765768008818</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.0207981922623991</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.4024358719720121</v>
+      </c>
+      <c r="C100">
+        <v>-40.2378108619582</v>
+      </c>
+      <c r="D100">
+        <v>36.5321891380418</v>
+      </c>
+      <c r="E100">
+        <v>77.91</v>
+      </c>
+      <c r="F100">
+        <v>77.91</v>
+      </c>
+      <c r="G100">
+        <v>1.14</v>
+      </c>
+      <c r="H100">
+        <v>79.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.498</v>
+      </c>
+      <c r="K100">
+        <v>0.115</v>
+      </c>
+      <c r="L100">
+        <v>0.383</v>
+      </c>
+      <c r="M100">
+        <v>18.604908</v>
+      </c>
+      <c r="N100">
+        <v>-18.221908</v>
+      </c>
+      <c r="O100">
+        <v>-4.19103884</v>
+      </c>
+      <c r="P100">
+        <v>-14.03086916</v>
+      </c>
+      <c r="Q100">
+        <v>-13.91586916</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.475996114323866</v>
+      </c>
+      <c r="T100">
+        <v>49.24731367683423</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.004734772136470655</v>
+      </c>
+      <c r="W100">
+        <v>0.2376693364138108</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.0205859658107419</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.404435871972012</v>
+      </c>
+      <c r="C101">
+        <v>-41.23263911699788</v>
+      </c>
+      <c r="D101">
+        <v>36.33236088300212</v>
+      </c>
+      <c r="E101">
+        <v>78.705</v>
+      </c>
+      <c r="F101">
+        <v>78.705</v>
+      </c>
+      <c r="G101">
+        <v>1.14</v>
+      </c>
+      <c r="H101">
+        <v>79.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.498</v>
+      </c>
+      <c r="K101">
+        <v>0.115</v>
+      </c>
+      <c r="L101">
+        <v>0.383</v>
+      </c>
+      <c r="M101">
+        <v>18.794754</v>
+      </c>
+      <c r="N101">
+        <v>-18.411754</v>
+      </c>
+      <c r="O101">
+        <v>-4.23470342</v>
+      </c>
+      <c r="P101">
+        <v>-14.17705058</v>
+      </c>
+      <c r="Q101">
+        <v>-14.06205058</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>16.91319222864773</v>
+      </c>
+      <c r="T101">
+        <v>98.49462735366846</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.004686946155294185</v>
+      </c>
+      <c r="W101">
+        <v>0.2376807572581158</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.02037802676214862</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_recreation.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_recreation.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1385481776151525</v>
+        <v>0.1382355571711146</v>
       </c>
       <c r="C2">
-        <v>335.7</v>
+        <v>333.4624879583992</v>
       </c>
       <c r="D2">
-        <v>331.01</v>
+        <v>332.1294879583992</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3.357</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.357</v>
       </c>
       <c r="G2">
         <v>4.69</v>
@@ -1439,28 +1439,28 @@
         <v>3.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1688571</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.4311429</v>
       </c>
       <c r="O2">
-        <v>0.9</v>
+        <v>0.8577857250000001</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>2.573357175</v>
       </c>
       <c r="Q2">
-        <v>3.22</v>
+        <v>3.093357175</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1385481776151525</v>
+        <v>0.1392508153243582</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9037408069995096</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>21.31980236543207</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1382355571711146</v>
+        <v>0.1379454367270768</v>
       </c>
       <c r="C3">
-        <v>333.4624879583992</v>
+        <v>331.1511995850092</v>
       </c>
       <c r="D3">
-        <v>332.1294879583992</v>
+        <v>333.1751995850092</v>
       </c>
       <c r="E3">
-        <v>3.357</v>
+        <v>6.714</v>
       </c>
       <c r="F3">
-        <v>3.357</v>
+        <v>6.714</v>
       </c>
       <c r="G3">
         <v>4.69</v>
@@ -1521,45 +1521,45 @@
         <v>3.6</v>
       </c>
       <c r="M3">
-        <v>0.1688571</v>
+        <v>0.3477852</v>
       </c>
       <c r="N3">
-        <v>3.4311429</v>
+        <v>3.2522148</v>
       </c>
       <c r="O3">
-        <v>0.8577857250000001</v>
+        <v>0.8130537</v>
       </c>
       <c r="P3">
-        <v>2.573357175</v>
+        <v>2.4391611</v>
       </c>
       <c r="Q3">
-        <v>3.093357175</v>
+        <v>2.9591611</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1392508153243582</v>
+        <v>0.1399677925786498</v>
       </c>
       <c r="T3">
-        <v>0.9037408069995096</v>
+        <v>0.9106745250216021</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>21.31980236543207</v>
+        <v>10.35121678553314</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1379454367270768</v>
+        <v>0.1377003162830389</v>
       </c>
       <c r="C4">
-        <v>331.1511995850092</v>
+        <v>328.6828586905249</v>
       </c>
       <c r="D4">
-        <v>333.1751995850092</v>
+        <v>334.0638586905249</v>
       </c>
       <c r="E4">
-        <v>6.714</v>
+        <v>10.071</v>
       </c>
       <c r="F4">
-        <v>6.714</v>
+        <v>10.071</v>
       </c>
       <c r="G4">
         <v>4.69</v>
@@ -1603,45 +1603,45 @@
         <v>3.6</v>
       </c>
       <c r="M4">
-        <v>0.3477852</v>
+        <v>0.5468553</v>
       </c>
       <c r="N4">
-        <v>3.2522148</v>
+        <v>3.0531447</v>
       </c>
       <c r="O4">
-        <v>0.8130537</v>
+        <v>0.763286175</v>
       </c>
       <c r="P4">
-        <v>2.4391611</v>
+        <v>2.289858525</v>
       </c>
       <c r="Q4">
-        <v>2.9591611</v>
+        <v>2.809858525</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1399677925786498</v>
+        <v>0.1406995528691122</v>
       </c>
       <c r="T4">
-        <v>0.9106745250216021</v>
+        <v>0.9177512063018817</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.03885</v>
+        <v>0.040725</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>10.35121678553314</v>
+        <v>6.583094284722119</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1377003162830389</v>
+        <v>0.137447695839001</v>
       </c>
       <c r="C5">
-        <v>328.6828586905249</v>
+        <v>326.2466822807618</v>
       </c>
       <c r="D5">
-        <v>334.0638586905249</v>
+        <v>334.9846822807618</v>
       </c>
       <c r="E5">
-        <v>10.071</v>
+        <v>13.428</v>
       </c>
       <c r="F5">
-        <v>10.071</v>
+        <v>13.428</v>
       </c>
       <c r="G5">
         <v>4.69</v>
@@ -1685,45 +1685,45 @@
         <v>3.6</v>
       </c>
       <c r="M5">
-        <v>0.5468553</v>
+        <v>0.7425684</v>
       </c>
       <c r="N5">
-        <v>3.0531447</v>
+        <v>2.8574316</v>
       </c>
       <c r="O5">
-        <v>0.763286175</v>
+        <v>0.7143579</v>
       </c>
       <c r="P5">
-        <v>2.289858525</v>
+        <v>2.1430737</v>
       </c>
       <c r="Q5">
-        <v>2.809858525</v>
+        <v>2.6630737</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1406995528691122</v>
+        <v>0.141446558165626</v>
       </c>
       <c r="T5">
-        <v>0.9177512063018817</v>
+        <v>0.9249753184421674</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>6.583094284722119</v>
+        <v>4.848038241325647</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.137447695839001</v>
+        <v>0.1375025753949631</v>
       </c>
       <c r="C6">
-        <v>326.2466822807618</v>
+        <v>322.6892101507425</v>
       </c>
       <c r="D6">
-        <v>334.9846822807618</v>
+        <v>334.7842101507425</v>
       </c>
       <c r="E6">
-        <v>13.428</v>
+        <v>16.785</v>
       </c>
       <c r="F6">
-        <v>13.428</v>
+        <v>16.785</v>
       </c>
       <c r="G6">
         <v>4.69</v>
@@ -1767,45 +1767,45 @@
         <v>3.6</v>
       </c>
       <c r="M6">
-        <v>0.7425684</v>
+        <v>1.0759185</v>
       </c>
       <c r="N6">
-        <v>2.8574316</v>
+        <v>2.5240815</v>
       </c>
       <c r="O6">
-        <v>0.7143579</v>
+        <v>0.6310203750000001</v>
       </c>
       <c r="P6">
-        <v>2.1430737</v>
+        <v>1.893061125</v>
       </c>
       <c r="Q6">
-        <v>2.6630737</v>
+        <v>2.413061125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.141446558165626</v>
+        <v>0.1422092898894348</v>
       </c>
       <c r="T6">
-        <v>0.9249753184421674</v>
+        <v>0.9323515171538274</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0641</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.041475</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.848038241325647</v>
+        <v>3.345978343155174</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1375025753949631</v>
+        <v>0.1378199549509252</v>
       </c>
       <c r="C7">
-        <v>322.6892101507425</v>
+        <v>318.1775294728674</v>
       </c>
       <c r="D7">
-        <v>334.7842101507425</v>
+        <v>333.6295294728674</v>
       </c>
       <c r="E7">
-        <v>16.785</v>
+        <v>20.142</v>
       </c>
       <c r="F7">
-        <v>16.785</v>
+        <v>20.142</v>
       </c>
       <c r="G7">
         <v>4.69</v>
@@ -1849,45 +1849,45 @@
         <v>3.6</v>
       </c>
       <c r="M7">
-        <v>1.0759185</v>
+        <v>1.5267636</v>
       </c>
       <c r="N7">
-        <v>2.5240815</v>
+        <v>2.0732364</v>
       </c>
       <c r="O7">
-        <v>0.6310203750000001</v>
+        <v>0.5183091</v>
       </c>
       <c r="P7">
-        <v>1.893061125</v>
+        <v>1.5549273</v>
       </c>
       <c r="Q7">
-        <v>2.413061125</v>
+        <v>2.0749273</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1422092898894348</v>
+        <v>0.1429882499477928</v>
       </c>
       <c r="T7">
-        <v>0.9323515171538274</v>
+        <v>0.9398846562636078</v>
       </c>
       <c r="U7">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04807500000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.345978343155174</v>
+        <v>2.357928889580548</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1378199549509252</v>
+        <v>0.1376985845068874</v>
       </c>
       <c r="C8">
-        <v>318.1775294728674</v>
+        <v>315.2611539324665</v>
       </c>
       <c r="D8">
-        <v>333.6295294728674</v>
+        <v>334.0701539324665</v>
       </c>
       <c r="E8">
-        <v>20.142</v>
+        <v>23.499</v>
       </c>
       <c r="F8">
-        <v>20.142</v>
+        <v>23.499</v>
       </c>
       <c r="G8">
         <v>4.69</v>
@@ -1931,28 +1931,28 @@
         <v>3.6</v>
       </c>
       <c r="M8">
-        <v>1.5267636</v>
+        <v>1.7812242</v>
       </c>
       <c r="N8">
-        <v>2.0732364</v>
+        <v>1.8187758</v>
       </c>
       <c r="O8">
-        <v>0.5183091</v>
+        <v>0.4546939500000001</v>
       </c>
       <c r="P8">
-        <v>1.5549273</v>
+        <v>1.36408185</v>
       </c>
       <c r="Q8">
-        <v>2.0749273</v>
+        <v>1.88408185</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1429882499477928</v>
+        <v>0.1437839618353627</v>
       </c>
       <c r="T8">
-        <v>0.9398846562636078</v>
+        <v>0.9475797983649964</v>
       </c>
       <c r="U8">
         <v>0.07580000000000001</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>2.357928889580548</v>
+        <v>2.021081905354756</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1376985845068873</v>
+        <v>0.1422533798268547</v>
       </c>
       <c r="C9">
-        <v>315.2611539324666</v>
+        <v>296.1284374526101</v>
       </c>
       <c r="D9">
-        <v>334.0701539324666</v>
+        <v>318.2944374526101</v>
       </c>
       <c r="E9">
-        <v>23.499</v>
+        <v>26.856</v>
       </c>
       <c r="F9">
-        <v>23.499</v>
+        <v>26.856</v>
       </c>
       <c r="G9">
         <v>4.69</v>
@@ -2013,45 +2013,45 @@
         <v>3.6</v>
       </c>
       <c r="M9">
-        <v>1.7812242</v>
+        <v>3.9424608</v>
       </c>
       <c r="N9">
-        <v>1.8187758</v>
+        <v>-0.3424608</v>
       </c>
       <c r="O9">
-        <v>0.45469395</v>
+        <v>-0.0856152</v>
       </c>
       <c r="P9">
-        <v>1.36408185</v>
+        <v>-0.2568456</v>
       </c>
       <c r="Q9">
-        <v>1.88408185</v>
+        <v>0.2631544</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1437839618353627</v>
+        <v>0.1447721141025084</v>
       </c>
       <c r="T9">
-        <v>0.9475797983649964</v>
+        <v>0.9571359860156766</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V9">
-        <v>0.25</v>
+        <v>0.2282838170515227</v>
       </c>
       <c r="W9">
-        <v>0.05685</v>
+        <v>0.1132879356568365</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.021081905354755</v>
+        <v>0.9131352682060909</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1422533798268547</v>
+        <v>0.1432633798268547</v>
       </c>
       <c r="C10">
-        <v>296.1284374526101</v>
+        <v>289.4729946692975</v>
       </c>
       <c r="D10">
-        <v>318.2944374526101</v>
+        <v>314.9959946692975</v>
       </c>
       <c r="E10">
-        <v>26.856</v>
+        <v>30.213</v>
       </c>
       <c r="F10">
-        <v>26.856</v>
+        <v>30.213</v>
       </c>
       <c r="G10">
         <v>4.69</v>
@@ -2095,37 +2095,37 @@
         <v>3.6</v>
       </c>
       <c r="M10">
-        <v>3.9424608</v>
+        <v>4.4352684</v>
       </c>
       <c r="N10">
-        <v>-0.3424608</v>
+        <v>-0.8352683999999999</v>
       </c>
       <c r="O10">
-        <v>-0.0856152</v>
+        <v>-0.2088171</v>
       </c>
       <c r="P10">
-        <v>-0.2568456</v>
+        <v>-0.6264512999999999</v>
       </c>
       <c r="Q10">
-        <v>0.2631544</v>
+        <v>-0.1064512999999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1447721141025084</v>
+        <v>0.1458597197519866</v>
       </c>
       <c r="T10">
-        <v>0.9571359860156766</v>
+        <v>0.9676539638839809</v>
       </c>
       <c r="U10">
         <v>0.1468</v>
       </c>
       <c r="V10">
-        <v>0.2282838170515227</v>
+        <v>0.2029189484902424</v>
       </c>
       <c r="W10">
-        <v>0.1132879356568365</v>
+        <v>0.1170114983616324</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.9131352682060909</v>
+        <v>0.8116757939609698</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1432633798268547</v>
+        <v>0.1501288925888348</v>
       </c>
       <c r="C11">
-        <v>289.4729946692975</v>
+        <v>265.3872303959372</v>
       </c>
       <c r="D11">
-        <v>314.9959946692975</v>
+        <v>294.2672303959372</v>
       </c>
       <c r="E11">
-        <v>30.213</v>
+        <v>33.56999999999999</v>
       </c>
       <c r="F11">
-        <v>30.213</v>
+        <v>33.56999999999999</v>
       </c>
       <c r="G11">
         <v>4.69</v>
@@ -2177,45 +2177,45 @@
         <v>3.6</v>
       </c>
       <c r="M11">
-        <v>4.4352684</v>
+        <v>6.740855999999999</v>
       </c>
       <c r="N11">
-        <v>-0.8352683999999999</v>
+        <v>-3.140855999999999</v>
       </c>
       <c r="O11">
-        <v>-0.2088171</v>
+        <v>-0.7852139999999997</v>
       </c>
       <c r="P11">
-        <v>-0.6264512999999999</v>
+        <v>-2.355641999999999</v>
       </c>
       <c r="Q11">
-        <v>-0.1064512999999999</v>
+        <v>-1.835641999999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1458597197519866</v>
+        <v>0.1474776197069866</v>
       </c>
       <c r="T11">
-        <v>0.9676539638839809</v>
+        <v>0.983300292981284</v>
       </c>
       <c r="U11">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.2029189484902424</v>
+        <v>0.1335142005703727</v>
       </c>
       <c r="W11">
-        <v>0.1170114983616324</v>
+        <v>0.1739903485254692</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.8116757939609698</v>
+        <v>0.5340568022814908</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1501288925888349</v>
+        <v>0.1557126974902778</v>
       </c>
       <c r="C12">
-        <v>265.3872303959371</v>
+        <v>247.080812895159</v>
       </c>
       <c r="D12">
-        <v>294.2672303959371</v>
+        <v>279.317812895159</v>
       </c>
       <c r="E12">
-        <v>33.57</v>
+        <v>36.927</v>
       </c>
       <c r="F12">
-        <v>33.57</v>
+        <v>36.927</v>
       </c>
       <c r="G12">
         <v>4.69</v>
@@ -2259,45 +2259,45 @@
         <v>3.6</v>
       </c>
       <c r="M12">
-        <v>6.740856</v>
+        <v>8.7073866</v>
       </c>
       <c r="N12">
-        <v>-3.140856</v>
+        <v>-5.1073866</v>
       </c>
       <c r="O12">
-        <v>-0.785214</v>
+        <v>-1.27684665</v>
       </c>
       <c r="P12">
-        <v>-2.355642</v>
+        <v>-3.83053995</v>
       </c>
       <c r="Q12">
-        <v>-1.835642</v>
+        <v>-3.31053995</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1474776197069866</v>
+        <v>0.1488265872334055</v>
       </c>
       <c r="T12">
-        <v>0.983300292981284</v>
+        <v>0.9963458399538873</v>
       </c>
       <c r="U12">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.1335142005703727</v>
+        <v>0.1033605192170978</v>
       </c>
       <c r="W12">
-        <v>0.1739903485254692</v>
+        <v>0.2114275895686083</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y12">
-        <v>0.5340568022814907</v>
+        <v>0.4134420768683912</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1557126974902778</v>
+        <v>0.1576126974902778</v>
       </c>
       <c r="C13">
-        <v>247.080812895159</v>
+        <v>238.9774481583012</v>
       </c>
       <c r="D13">
-        <v>279.317812895159</v>
+        <v>274.5714481583012</v>
       </c>
       <c r="E13">
-        <v>36.927</v>
+        <v>40.284</v>
       </c>
       <c r="F13">
-        <v>36.927</v>
+        <v>40.284</v>
       </c>
       <c r="G13">
         <v>4.69</v>
@@ -2341,37 +2341,37 @@
         <v>3.6</v>
       </c>
       <c r="M13">
-        <v>8.7073866</v>
+        <v>9.498967200000001</v>
       </c>
       <c r="N13">
-        <v>-5.1073866</v>
+        <v>-5.898967200000001</v>
       </c>
       <c r="O13">
-        <v>-1.27684665</v>
+        <v>-1.4747418</v>
       </c>
       <c r="P13">
-        <v>-3.83053995</v>
+        <v>-4.424225400000001</v>
       </c>
       <c r="Q13">
-        <v>-3.31053995</v>
+        <v>-3.904225400000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1488265872334055</v>
+        <v>0.1499973439065124</v>
       </c>
       <c r="T13">
-        <v>0.9963458399538873</v>
+        <v>1.007667951771545</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.1033605192170978</v>
+        <v>0.09474714261567299</v>
       </c>
       <c r="W13">
-        <v>0.2114275895686083</v>
+        <v>0.2134586237712243</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.4134420768683912</v>
+        <v>0.378988570462692</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1576126974902778</v>
+        <v>0.1595126974902779</v>
       </c>
       <c r="C14">
-        <v>238.9774481583012</v>
+        <v>231.0326953126228</v>
       </c>
       <c r="D14">
-        <v>274.5714481583012</v>
+        <v>269.9836953126228</v>
       </c>
       <c r="E14">
-        <v>40.284</v>
+        <v>43.641</v>
       </c>
       <c r="F14">
-        <v>40.284</v>
+        <v>43.641</v>
       </c>
       <c r="G14">
         <v>4.69</v>
@@ -2423,37 +2423,37 @@
         <v>3.6</v>
       </c>
       <c r="M14">
-        <v>9.498967200000001</v>
+        <v>10.2905478</v>
       </c>
       <c r="N14">
-        <v>-5.898967200000001</v>
+        <v>-6.690547800000001</v>
       </c>
       <c r="O14">
-        <v>-1.4747418</v>
+        <v>-1.67263695</v>
       </c>
       <c r="P14">
-        <v>-4.424225400000001</v>
+        <v>-5.017910850000001</v>
       </c>
       <c r="Q14">
-        <v>-3.904225400000001</v>
+        <v>-4.49791085</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1499973439065124</v>
+        <v>0.1511950145261275</v>
       </c>
       <c r="T14">
-        <v>1.007667951771545</v>
+        <v>1.019250342021793</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.09474714261567299</v>
+        <v>0.08745890087600584</v>
       </c>
       <c r="W14">
-        <v>0.2134586237712243</v>
+        <v>0.2151771911734378</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.378988570462692</v>
+        <v>0.3498356035040233</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1595126974902779</v>
+        <v>0.1614126974902779</v>
       </c>
       <c r="C15">
-        <v>231.0326953126228</v>
+        <v>223.2387343885244</v>
       </c>
       <c r="D15">
-        <v>269.9836953126228</v>
+        <v>265.5467343885244</v>
       </c>
       <c r="E15">
-        <v>43.641</v>
+        <v>46.998</v>
       </c>
       <c r="F15">
-        <v>43.641</v>
+        <v>46.998</v>
       </c>
       <c r="G15">
         <v>4.69</v>
@@ -2505,37 +2505,37 @@
         <v>3.6</v>
       </c>
       <c r="M15">
-        <v>10.2905478</v>
+        <v>11.0821284</v>
       </c>
       <c r="N15">
-        <v>-6.690547800000001</v>
+        <v>-7.482128400000002</v>
       </c>
       <c r="O15">
-        <v>-1.67263695</v>
+        <v>-1.870532100000001</v>
       </c>
       <c r="P15">
-        <v>-5.017910850000001</v>
+        <v>-5.611596300000002</v>
       </c>
       <c r="Q15">
-        <v>-4.49791085</v>
+        <v>-5.091596300000003</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1511950145261275</v>
+        <v>0.1524205379508499</v>
       </c>
       <c r="T15">
-        <v>1.019250342021793</v>
+        <v>1.031102090184837</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.08745890087600584</v>
+        <v>0.0812118365277197</v>
       </c>
       <c r="W15">
-        <v>0.2151771911734378</v>
+        <v>0.2166502489467637</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3498356035040233</v>
+        <v>0.3248473461108787</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1614126974902779</v>
+        <v>0.1633126974902779</v>
       </c>
       <c r="C16">
-        <v>223.2387343885244</v>
+        <v>215.5882511640419</v>
       </c>
       <c r="D16">
-        <v>265.5467343885244</v>
+        <v>261.2532511640419</v>
       </c>
       <c r="E16">
-        <v>46.998</v>
+        <v>50.355</v>
       </c>
       <c r="F16">
-        <v>46.998</v>
+        <v>50.355</v>
       </c>
       <c r="G16">
         <v>4.69</v>
@@ -2587,37 +2587,37 @@
         <v>3.6</v>
       </c>
       <c r="M16">
-        <v>11.0821284</v>
+        <v>11.873709</v>
       </c>
       <c r="N16">
-        <v>-7.482128400000002</v>
+        <v>-8.273709000000002</v>
       </c>
       <c r="O16">
-        <v>-1.870532100000001</v>
+        <v>-2.06842725</v>
       </c>
       <c r="P16">
-        <v>-5.611596300000002</v>
+        <v>-6.205281750000001</v>
       </c>
       <c r="Q16">
-        <v>-5.091596300000003</v>
+        <v>-5.685281750000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1524205379508499</v>
+        <v>0.1536748972208599</v>
       </c>
       <c r="T16">
-        <v>1.031102090184837</v>
+        <v>1.043232703010541</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.0812118365277197</v>
+        <v>0.07579771409253838</v>
       </c>
       <c r="W16">
-        <v>0.2166502489467637</v>
+        <v>0.2179268990169795</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3248473461108787</v>
+        <v>0.3031908563701535</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1633126974902778</v>
+        <v>0.1652126974902778</v>
       </c>
       <c r="C17">
-        <v>215.588251164042</v>
+        <v>208.0743969295742</v>
       </c>
       <c r="D17">
-        <v>261.253251164042</v>
+        <v>257.0963969295742</v>
       </c>
       <c r="E17">
-        <v>50.355</v>
+        <v>53.712</v>
       </c>
       <c r="F17">
-        <v>50.355</v>
+        <v>53.712</v>
       </c>
       <c r="G17">
         <v>4.69</v>
@@ -2669,37 +2669,37 @@
         <v>3.6</v>
       </c>
       <c r="M17">
-        <v>11.873709</v>
+        <v>12.6652896</v>
       </c>
       <c r="N17">
-        <v>-8.273709</v>
+        <v>-9.0652896</v>
       </c>
       <c r="O17">
-        <v>-2.06842725</v>
+        <v>-2.2663224</v>
       </c>
       <c r="P17">
-        <v>-6.20528175</v>
+        <v>-6.7989672</v>
       </c>
       <c r="Q17">
-        <v>-5.68528175</v>
+        <v>-6.2789672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1536748972208599</v>
+        <v>0.1549591221877749</v>
       </c>
       <c r="T17">
-        <v>1.043232703010541</v>
+        <v>1.055652139951142</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.0757977140925384</v>
+        <v>0.07106035696175475</v>
       </c>
       <c r="W17">
-        <v>0.2179268990169795</v>
+        <v>0.2190439678284183</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3031908563701535</v>
+        <v>0.284241427847019</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1652126974902778</v>
+        <v>0.1671126974902779</v>
       </c>
       <c r="C18">
-        <v>208.0743969295742</v>
+        <v>200.6907520335992</v>
       </c>
       <c r="D18">
-        <v>257.0963969295742</v>
+        <v>253.0697520335991</v>
       </c>
       <c r="E18">
-        <v>53.712</v>
+        <v>57.069</v>
       </c>
       <c r="F18">
-        <v>53.712</v>
+        <v>57.069</v>
       </c>
       <c r="G18">
         <v>4.69</v>
@@ -2751,37 +2751,37 @@
         <v>3.6</v>
       </c>
       <c r="M18">
-        <v>12.6652896</v>
+        <v>13.4568702</v>
       </c>
       <c r="N18">
-        <v>-9.0652896</v>
+        <v>-9.856870200000001</v>
       </c>
       <c r="O18">
-        <v>-2.2663224</v>
+        <v>-2.46421755</v>
       </c>
       <c r="P18">
-        <v>-6.7989672</v>
+        <v>-7.39265265</v>
       </c>
       <c r="Q18">
-        <v>-6.2789672</v>
+        <v>-6.872652650000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1549591221877749</v>
+        <v>0.1562742923346156</v>
       </c>
       <c r="T18">
-        <v>1.055652139951142</v>
+        <v>1.068370840432482</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.07106035696175475</v>
+        <v>0.06688033596400446</v>
       </c>
       <c r="W18">
-        <v>0.2190439678284183</v>
+        <v>0.2200296167796878</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.284241427847019</v>
+        <v>0.2675213438560178</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1671126974902779</v>
+        <v>0.1690126974902778</v>
       </c>
       <c r="C19">
-        <v>200.6907520335992</v>
+        <v>193.4312928012479</v>
       </c>
       <c r="D19">
-        <v>253.0697520335991</v>
+        <v>249.1672928012479</v>
       </c>
       <c r="E19">
-        <v>57.069</v>
+        <v>60.426</v>
       </c>
       <c r="F19">
-        <v>57.069</v>
+        <v>60.426</v>
       </c>
       <c r="G19">
         <v>4.69</v>
@@ -2833,37 +2833,37 @@
         <v>3.6</v>
       </c>
       <c r="M19">
-        <v>13.4568702</v>
+        <v>14.2484508</v>
       </c>
       <c r="N19">
-        <v>-9.856870200000001</v>
+        <v>-10.6484508</v>
       </c>
       <c r="O19">
-        <v>-2.46421755</v>
+        <v>-2.6621127</v>
       </c>
       <c r="P19">
-        <v>-7.39265265</v>
+        <v>-7.986338100000001</v>
       </c>
       <c r="Q19">
-        <v>-6.872652650000001</v>
+        <v>-7.466338100000002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1562742923346156</v>
+        <v>0.1576215398021109</v>
       </c>
       <c r="T19">
-        <v>1.068370840432482</v>
+        <v>1.081399753120683</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06688033596400446</v>
+        <v>0.06316476174378199</v>
       </c>
       <c r="W19">
-        <v>0.2200296167796878</v>
+        <v>0.2209057491808162</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2675213438560178</v>
+        <v>0.252659046975128</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1690126974902779</v>
+        <v>0.1709126974902779</v>
       </c>
       <c r="C20">
-        <v>193.4312928012478</v>
+        <v>186.2903614671867</v>
       </c>
       <c r="D20">
-        <v>249.1672928012478</v>
+        <v>245.3833614671867</v>
       </c>
       <c r="E20">
-        <v>60.42599999999999</v>
+        <v>63.783</v>
       </c>
       <c r="F20">
-        <v>60.42599999999999</v>
+        <v>63.783</v>
       </c>
       <c r="G20">
         <v>4.69</v>
@@ -2915,37 +2915,37 @@
         <v>3.6</v>
       </c>
       <c r="M20">
-        <v>14.2484508</v>
+        <v>15.0400314</v>
       </c>
       <c r="N20">
-        <v>-10.6484508</v>
+        <v>-11.4400314</v>
       </c>
       <c r="O20">
-        <v>-2.6621127</v>
+        <v>-2.86000785</v>
       </c>
       <c r="P20">
-        <v>-7.986338099999999</v>
+        <v>-8.58002355</v>
       </c>
       <c r="Q20">
-        <v>-7.4663381</v>
+        <v>-8.06002355</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1576215398021109</v>
+        <v>0.159002052639174</v>
       </c>
       <c r="T20">
-        <v>1.081399753120682</v>
+        <v>1.09475036735674</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.06316476174378201</v>
+        <v>0.05984030059937242</v>
       </c>
       <c r="W20">
-        <v>0.2209057491808162</v>
+        <v>0.221689657118668</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.252659046975128</v>
+        <v>0.2393612023974897</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1709126974902779</v>
+        <v>0.1728126974902779</v>
       </c>
       <c r="C21">
-        <v>186.2903614671867</v>
+        <v>179.2626388071681</v>
       </c>
       <c r="D21">
-        <v>245.3833614671867</v>
+        <v>241.7126388071681</v>
       </c>
       <c r="E21">
-        <v>63.783</v>
+        <v>67.14</v>
       </c>
       <c r="F21">
-        <v>63.783</v>
+        <v>67.14</v>
       </c>
       <c r="G21">
         <v>4.69</v>
@@ -2997,37 +2997,37 @@
         <v>3.6</v>
       </c>
       <c r="M21">
-        <v>15.0400314</v>
+        <v>15.831612</v>
       </c>
       <c r="N21">
-        <v>-11.4400314</v>
+        <v>-12.231612</v>
       </c>
       <c r="O21">
-        <v>-2.86000785</v>
+        <v>-3.057903</v>
       </c>
       <c r="P21">
-        <v>-8.58002355</v>
+        <v>-9.173709000000002</v>
       </c>
       <c r="Q21">
-        <v>-8.06002355</v>
+        <v>-8.653709000000003</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.159002052639174</v>
+        <v>0.1604170782971637</v>
       </c>
       <c r="T21">
-        <v>1.09475036735674</v>
+        <v>1.1084347469487</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05984030059937242</v>
+        <v>0.05684828556940379</v>
       </c>
       <c r="W21">
-        <v>0.221689657118668</v>
+        <v>0.2223951742627346</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2393612023974897</v>
+        <v>0.2273931422776152</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1728126974902779</v>
+        <v>0.1747126974902778</v>
       </c>
       <c r="C22">
-        <v>179.2626388071681</v>
+        <v>172.3431191898259</v>
       </c>
       <c r="D22">
-        <v>241.7126388071681</v>
+        <v>238.1501191898259</v>
       </c>
       <c r="E22">
-        <v>67.14</v>
+        <v>70.497</v>
       </c>
       <c r="F22">
-        <v>67.14</v>
+        <v>70.497</v>
       </c>
       <c r="G22">
         <v>4.69</v>
@@ -3079,37 +3079,37 @@
         <v>3.6</v>
       </c>
       <c r="M22">
-        <v>15.831612</v>
+        <v>16.6231926</v>
       </c>
       <c r="N22">
-        <v>-12.231612</v>
+        <v>-13.0231926</v>
       </c>
       <c r="O22">
-        <v>-3.057903</v>
+        <v>-3.25579815</v>
       </c>
       <c r="P22">
-        <v>-9.173709000000002</v>
+        <v>-9.767394449999999</v>
       </c>
       <c r="Q22">
-        <v>-8.653709000000003</v>
+        <v>-9.24739445</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1604170782971637</v>
+        <v>0.1618679273895328</v>
       </c>
       <c r="T22">
-        <v>1.1084347469487</v>
+        <v>1.122465566530329</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05684828556940379</v>
+        <v>0.05414122435181314</v>
       </c>
       <c r="W22">
-        <v>0.2223951742627346</v>
+        <v>0.2230334992978425</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2273931422776152</v>
+        <v>0.2165648974072526</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1747126974902778</v>
+        <v>0.1766126974902779</v>
       </c>
       <c r="C23">
-        <v>172.3431191898259</v>
+        <v>165.527087802645</v>
       </c>
       <c r="D23">
-        <v>238.1501191898259</v>
+        <v>234.691087802645</v>
       </c>
       <c r="E23">
-        <v>70.497</v>
+        <v>73.854</v>
       </c>
       <c r="F23">
-        <v>70.497</v>
+        <v>73.854</v>
       </c>
       <c r="G23">
         <v>4.69</v>
@@ -3161,37 +3161,37 @@
         <v>3.6</v>
       </c>
       <c r="M23">
-        <v>16.6231926</v>
+        <v>17.4147732</v>
       </c>
       <c r="N23">
-        <v>-13.0231926</v>
+        <v>-13.8147732</v>
       </c>
       <c r="O23">
-        <v>-3.25579815</v>
+        <v>-3.4536933</v>
       </c>
       <c r="P23">
-        <v>-9.767394449999999</v>
+        <v>-10.3610799</v>
       </c>
       <c r="Q23">
-        <v>-9.24739445</v>
+        <v>-9.8410799</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1618679273895328</v>
+        <v>0.1633559777406807</v>
       </c>
       <c r="T23">
-        <v>1.122465566530329</v>
+        <v>1.136856150716615</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05414122435181314</v>
+        <v>0.05168025960854891</v>
       </c>
       <c r="W23">
-        <v>0.2230334992978425</v>
+        <v>0.2236137947843042</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2165648974072526</v>
+        <v>0.2067210384341956</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1766126974902779</v>
+        <v>0.1785126974902778</v>
       </c>
       <c r="C24">
-        <v>165.527087802645</v>
+        <v>158.8100998342165</v>
       </c>
       <c r="D24">
-        <v>234.691087802645</v>
+        <v>231.3310998342165</v>
       </c>
       <c r="E24">
-        <v>73.854</v>
+        <v>77.211</v>
       </c>
       <c r="F24">
-        <v>73.854</v>
+        <v>77.211</v>
       </c>
       <c r="G24">
         <v>4.69</v>
@@ -3243,37 +3243,37 @@
         <v>3.6</v>
       </c>
       <c r="M24">
-        <v>17.4147732</v>
+        <v>18.2063538</v>
       </c>
       <c r="N24">
-        <v>-13.8147732</v>
+        <v>-14.6063538</v>
       </c>
       <c r="O24">
-        <v>-3.4536933</v>
+        <v>-3.65158845</v>
       </c>
       <c r="P24">
-        <v>-10.3610799</v>
+        <v>-10.95476535</v>
       </c>
       <c r="Q24">
-        <v>-9.8410799</v>
+        <v>-10.43476535</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1633559777406807</v>
+        <v>0.1648826787502999</v>
       </c>
       <c r="T24">
-        <v>1.136856150716615</v>
+        <v>1.151620516310337</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.05168025960854891</v>
+        <v>0.04943329179948157</v>
       </c>
       <c r="W24">
-        <v>0.2236137947843042</v>
+        <v>0.2241436297936823</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2067210384341956</v>
+        <v>0.1977331671979262</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1785126974902778</v>
+        <v>0.1804126974902779</v>
       </c>
       <c r="C25">
-        <v>158.8100998342165</v>
+        <v>152.1879614194934</v>
       </c>
       <c r="D25">
-        <v>231.3310998342165</v>
+        <v>228.0659614194934</v>
       </c>
       <c r="E25">
-        <v>77.211</v>
+        <v>80.568</v>
       </c>
       <c r="F25">
-        <v>77.211</v>
+        <v>80.568</v>
       </c>
       <c r="G25">
         <v>4.69</v>
@@ -3325,37 +3325,37 @@
         <v>3.6</v>
       </c>
       <c r="M25">
-        <v>18.2063538</v>
+        <v>18.9979344</v>
       </c>
       <c r="N25">
-        <v>-14.6063538</v>
+        <v>-15.3979344</v>
       </c>
       <c r="O25">
-        <v>-3.65158845</v>
+        <v>-3.849483600000001</v>
       </c>
       <c r="P25">
-        <v>-10.95476535</v>
+        <v>-11.5484508</v>
       </c>
       <c r="Q25">
-        <v>-10.43476535</v>
+        <v>-11.0284508</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1648826787502999</v>
+        <v>0.1664495561022775</v>
       </c>
       <c r="T25">
-        <v>1.151620516310337</v>
+        <v>1.166773417840737</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04943329179948157</v>
+        <v>0.0473735713078365</v>
       </c>
       <c r="W25">
-        <v>0.2241436297936823</v>
+        <v>0.2246293118856122</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.1977331671979262</v>
+        <v>0.1894942852313459</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1804126974902779</v>
+        <v>0.1823126974902778</v>
       </c>
       <c r="C26">
-        <v>152.1879614194934</v>
+        <v>145.6567121762836</v>
       </c>
       <c r="D26">
-        <v>228.0659614194934</v>
+        <v>224.8917121762836</v>
       </c>
       <c r="E26">
-        <v>80.568</v>
+        <v>83.925</v>
       </c>
       <c r="F26">
-        <v>80.568</v>
+        <v>83.925</v>
       </c>
       <c r="G26">
         <v>4.69</v>
@@ -3407,37 +3407,37 @@
         <v>3.6</v>
       </c>
       <c r="M26">
-        <v>18.9979344</v>
+        <v>19.789515</v>
       </c>
       <c r="N26">
-        <v>-15.3979344</v>
+        <v>-16.189515</v>
       </c>
       <c r="O26">
-        <v>-3.849483600000001</v>
+        <v>-4.04737875</v>
       </c>
       <c r="P26">
-        <v>-11.5484508</v>
+        <v>-12.14213625</v>
       </c>
       <c r="Q26">
-        <v>-11.0284508</v>
+        <v>-11.62213625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1664495561022775</v>
+        <v>0.1680582168503079</v>
       </c>
       <c r="T26">
-        <v>1.166773417840737</v>
+        <v>1.18233039674528</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.0473735713078365</v>
+        <v>0.04547862845552304</v>
       </c>
       <c r="W26">
-        <v>0.2246293118856122</v>
+        <v>0.2250761394101877</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1894942852313459</v>
+        <v>0.1819145138220922</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1823126974902778</v>
+        <v>0.1842126974902779</v>
       </c>
       <c r="C27">
-        <v>145.6567121762836</v>
+        <v>139.2126091800794</v>
       </c>
       <c r="D27">
-        <v>224.8917121762836</v>
+        <v>221.8046091800794</v>
       </c>
       <c r="E27">
-        <v>83.925</v>
+        <v>87.282</v>
       </c>
       <c r="F27">
-        <v>83.925</v>
+        <v>87.282</v>
       </c>
       <c r="G27">
         <v>4.69</v>
@@ -3489,37 +3489,37 @@
         <v>3.6</v>
       </c>
       <c r="M27">
-        <v>19.789515</v>
+        <v>20.5810956</v>
       </c>
       <c r="N27">
-        <v>-16.189515</v>
+        <v>-16.9810956</v>
       </c>
       <c r="O27">
-        <v>-4.04737875</v>
+        <v>-4.2452739</v>
       </c>
       <c r="P27">
-        <v>-12.14213625</v>
+        <v>-12.7358217</v>
       </c>
       <c r="Q27">
-        <v>-11.62213625</v>
+        <v>-12.2158217</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1680582168503079</v>
+        <v>0.1697103549158526</v>
       </c>
       <c r="T27">
-        <v>1.18233039674528</v>
+        <v>1.198307834539135</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04547862845552304</v>
+        <v>0.04372945043800292</v>
       </c>
       <c r="W27">
-        <v>0.2250761394101877</v>
+        <v>0.2254885955867189</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1819145138220922</v>
+        <v>0.1749178017520118</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1842126974902779</v>
+        <v>0.1861126974902778</v>
       </c>
       <c r="C28">
-        <v>139.2126091800794</v>
+        <v>132.8521122408851</v>
       </c>
       <c r="D28">
-        <v>221.8046091800794</v>
+        <v>218.8011122408851</v>
       </c>
       <c r="E28">
-        <v>87.282</v>
+        <v>90.639</v>
       </c>
       <c r="F28">
-        <v>87.282</v>
+        <v>90.639</v>
       </c>
       <c r="G28">
         <v>4.69</v>
@@ -3571,37 +3571,37 @@
         <v>3.6</v>
       </c>
       <c r="M28">
-        <v>20.5810956</v>
+        <v>21.3726762</v>
       </c>
       <c r="N28">
-        <v>-16.9810956</v>
+        <v>-17.7726762</v>
       </c>
       <c r="O28">
-        <v>-4.2452739</v>
+        <v>-4.44316905</v>
       </c>
       <c r="P28">
-        <v>-12.7358217</v>
+        <v>-13.32950715</v>
       </c>
       <c r="Q28">
-        <v>-12.2158217</v>
+        <v>-12.80950715</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1697103549158526</v>
+        <v>0.1714077570379876</v>
       </c>
       <c r="T28">
-        <v>1.198307834539135</v>
+        <v>1.21472301035474</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04372945043800292</v>
+        <v>0.04210984116252133</v>
       </c>
       <c r="W28">
-        <v>0.2254885955867189</v>
+        <v>0.2258704994538775</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1749178017520118</v>
+        <v>0.1684393646500854</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1861126974902778</v>
+        <v>0.1880126974902779</v>
       </c>
       <c r="C29">
-        <v>132.8521122408851</v>
+        <v>126.571870360278</v>
       </c>
       <c r="D29">
-        <v>218.8011122408851</v>
+        <v>215.877870360278</v>
       </c>
       <c r="E29">
-        <v>90.639</v>
+        <v>93.99600000000001</v>
       </c>
       <c r="F29">
-        <v>90.639</v>
+        <v>93.99600000000001</v>
       </c>
       <c r="G29">
         <v>4.69</v>
@@ -3653,37 +3653,37 @@
         <v>3.6</v>
       </c>
       <c r="M29">
-        <v>21.3726762</v>
+        <v>22.1642568</v>
       </c>
       <c r="N29">
-        <v>-17.7726762</v>
+        <v>-18.5642568</v>
       </c>
       <c r="O29">
-        <v>-4.44316905</v>
+        <v>-4.641064200000001</v>
       </c>
       <c r="P29">
-        <v>-13.32950715</v>
+        <v>-13.9231926</v>
       </c>
       <c r="Q29">
-        <v>-12.80950715</v>
+        <v>-13.4031926</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1714077570379876</v>
+        <v>0.1731523092190707</v>
       </c>
       <c r="T29">
-        <v>1.21472301035474</v>
+        <v>1.231594163276333</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04210984116252133</v>
+        <v>0.04060591826385985</v>
       </c>
       <c r="W29">
-        <v>0.2258704994538775</v>
+        <v>0.2262251244733819</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1684393646500854</v>
+        <v>0.1624236730554395</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1880126974902779</v>
+        <v>0.1899126974902779</v>
       </c>
       <c r="C30">
-        <v>126.571870360278</v>
+        <v>120.368709259781</v>
       </c>
       <c r="D30">
-        <v>215.877870360278</v>
+        <v>213.031709259781</v>
       </c>
       <c r="E30">
-        <v>93.99600000000001</v>
+        <v>97.35300000000001</v>
       </c>
       <c r="F30">
-        <v>93.99600000000001</v>
+        <v>97.35300000000001</v>
       </c>
       <c r="G30">
         <v>4.69</v>
@@ -3735,37 +3735,37 @@
         <v>3.6</v>
       </c>
       <c r="M30">
-        <v>22.1642568</v>
+        <v>22.9558374</v>
       </c>
       <c r="N30">
-        <v>-18.5642568</v>
+        <v>-19.3558374</v>
       </c>
       <c r="O30">
-        <v>-4.641064200000001</v>
+        <v>-4.838959350000001</v>
       </c>
       <c r="P30">
-        <v>-13.9231926</v>
+        <v>-14.51687805</v>
       </c>
       <c r="Q30">
-        <v>-13.4031926</v>
+        <v>-13.99687805</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1731523092190707</v>
+        <v>0.174946003715114</v>
       </c>
       <c r="T30">
-        <v>1.231594163276333</v>
+        <v>1.248940559942197</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.04060591826385985</v>
+        <v>0.03920571418579571</v>
       </c>
       <c r="W30">
-        <v>0.2262251244733819</v>
+        <v>0.2265552925949894</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1624236730554395</v>
+        <v>0.156822856743183</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1899126974902778</v>
+        <v>0.1918126974902779</v>
       </c>
       <c r="C31">
-        <v>120.368709259781</v>
+        <v>114.2396198829613</v>
       </c>
       <c r="D31">
-        <v>213.031709259781</v>
+        <v>210.2596198829613</v>
       </c>
       <c r="E31">
-        <v>97.35299999999999</v>
+        <v>100.71</v>
       </c>
       <c r="F31">
-        <v>97.35299999999999</v>
+        <v>100.71</v>
       </c>
       <c r="G31">
         <v>4.69</v>
@@ -3817,37 +3817,37 @@
         <v>3.6</v>
       </c>
       <c r="M31">
-        <v>22.9558374</v>
+        <v>23.747418</v>
       </c>
       <c r="N31">
-        <v>-19.3558374</v>
+        <v>-20.147418</v>
       </c>
       <c r="O31">
-        <v>-4.83895935</v>
+        <v>-5.0368545</v>
       </c>
       <c r="P31">
-        <v>-14.51687805</v>
+        <v>-15.1105635</v>
       </c>
       <c r="Q31">
-        <v>-13.99687805</v>
+        <v>-14.5905635</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.174946003715114</v>
+        <v>0.1767909466253299</v>
       </c>
       <c r="T31">
-        <v>1.248940559942197</v>
+        <v>1.266782567941371</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03920571418579572</v>
+        <v>0.0378988570462692</v>
       </c>
       <c r="W31">
-        <v>0.2265552925949894</v>
+        <v>0.2268634495084897</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.156822856743183</v>
+        <v>0.1515954281850769</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1918126974902779</v>
+        <v>0.1937126974902778</v>
       </c>
       <c r="C32">
-        <v>114.2396198829613</v>
+        <v>108.1817477837023</v>
       </c>
       <c r="D32">
-        <v>210.2596198829613</v>
+        <v>207.5587477837023</v>
       </c>
       <c r="E32">
-        <v>100.71</v>
+        <v>104.067</v>
       </c>
       <c r="F32">
-        <v>100.71</v>
+        <v>104.067</v>
       </c>
       <c r="G32">
         <v>4.69</v>
@@ -3899,37 +3899,37 @@
         <v>3.6</v>
       </c>
       <c r="M32">
-        <v>23.747418</v>
+        <v>24.5389986</v>
       </c>
       <c r="N32">
-        <v>-20.147418</v>
+        <v>-20.9389986</v>
       </c>
       <c r="O32">
-        <v>-5.0368545</v>
+        <v>-5.234749649999999</v>
       </c>
       <c r="P32">
-        <v>-15.1105635</v>
+        <v>-15.70424895</v>
       </c>
       <c r="Q32">
-        <v>-14.5905635</v>
+        <v>-15.18424895</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1767909466253299</v>
+        <v>0.178689366141639</v>
       </c>
       <c r="T32">
-        <v>1.266782567941371</v>
+        <v>1.285141735592695</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0378988570462692</v>
+        <v>0.0366763132705831</v>
       </c>
       <c r="W32">
-        <v>0.2268634495084897</v>
+        <v>0.2271517253307965</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1515954281850769</v>
+        <v>0.1467052530823324</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1937126974902778</v>
+        <v>0.1956126974902778</v>
       </c>
       <c r="C33">
-        <v>108.1817477837023</v>
+        <v>102.1923833219742</v>
       </c>
       <c r="D33">
-        <v>207.5587477837023</v>
+        <v>204.9263833219742</v>
       </c>
       <c r="E33">
-        <v>104.067</v>
+        <v>107.424</v>
       </c>
       <c r="F33">
-        <v>104.067</v>
+        <v>107.424</v>
       </c>
       <c r="G33">
         <v>4.69</v>
@@ -3981,37 +3981,37 @@
         <v>3.6</v>
       </c>
       <c r="M33">
-        <v>24.5389986</v>
+        <v>25.3305792</v>
       </c>
       <c r="N33">
-        <v>-20.9389986</v>
+        <v>-21.7305792</v>
       </c>
       <c r="O33">
-        <v>-5.234749649999999</v>
+        <v>-5.432644799999999</v>
       </c>
       <c r="P33">
-        <v>-15.70424895</v>
+        <v>-16.2979344</v>
       </c>
       <c r="Q33">
-        <v>-15.18424895</v>
+        <v>-15.7779344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.178689366141639</v>
+        <v>0.1806436215260749</v>
       </c>
       <c r="T33">
-        <v>1.285141735592695</v>
+        <v>1.304040878763176</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0366763132705831</v>
+        <v>0.03553017848087738</v>
       </c>
       <c r="W33">
-        <v>0.2271517253307965</v>
+        <v>0.2274219839142091</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1467052530823324</v>
+        <v>0.1421207139235096</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1956126974902778</v>
+        <v>0.1975126974902779</v>
       </c>
       <c r="C34">
-        <v>102.1923833219742</v>
+        <v>96.26895259631451</v>
       </c>
       <c r="D34">
-        <v>204.9263833219742</v>
+        <v>202.3599525963145</v>
       </c>
       <c r="E34">
-        <v>107.424</v>
+        <v>110.781</v>
       </c>
       <c r="F34">
-        <v>107.424</v>
+        <v>110.781</v>
       </c>
       <c r="G34">
         <v>4.69</v>
@@ -4063,37 +4063,37 @@
         <v>3.6</v>
       </c>
       <c r="M34">
-        <v>25.3305792</v>
+        <v>26.1221598</v>
       </c>
       <c r="N34">
-        <v>-21.7305792</v>
+        <v>-22.5221598</v>
       </c>
       <c r="O34">
-        <v>-5.432644799999999</v>
+        <v>-5.63053995</v>
       </c>
       <c r="P34">
-        <v>-16.2979344</v>
+        <v>-16.89161985</v>
       </c>
       <c r="Q34">
-        <v>-15.7779344</v>
+        <v>-16.37161985</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1806436215260749</v>
+        <v>0.1826562128921357</v>
       </c>
       <c r="T34">
-        <v>1.304040878763176</v>
+        <v>1.323504175461134</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03553017848087738</v>
+        <v>0.03445350640569927</v>
       </c>
       <c r="W34">
-        <v>0.2274219839142091</v>
+        <v>0.2276758631895361</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1421207139235096</v>
+        <v>0.1378140256227971</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1975126974902779</v>
+        <v>0.1994126974902778</v>
       </c>
       <c r="C35">
-        <v>96.26895259631451</v>
+        <v>90.40900904923356</v>
       </c>
       <c r="D35">
-        <v>202.3599525963145</v>
+        <v>199.8570090492336</v>
       </c>
       <c r="E35">
-        <v>110.781</v>
+        <v>114.138</v>
       </c>
       <c r="F35">
-        <v>110.781</v>
+        <v>114.138</v>
       </c>
       <c r="G35">
         <v>4.69</v>
@@ -4145,37 +4145,37 @@
         <v>3.6</v>
       </c>
       <c r="M35">
-        <v>26.1221598</v>
+        <v>26.9137404</v>
       </c>
       <c r="N35">
-        <v>-22.5221598</v>
+        <v>-23.3137404</v>
       </c>
       <c r="O35">
-        <v>-5.63053995</v>
+        <v>-5.8284351</v>
       </c>
       <c r="P35">
-        <v>-16.89161985</v>
+        <v>-17.4853053</v>
       </c>
       <c r="Q35">
-        <v>-16.37161985</v>
+        <v>-16.9653053</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1826562128921357</v>
+        <v>0.1847297918753499</v>
       </c>
       <c r="T35">
-        <v>1.323504175461134</v>
+        <v>1.343557269028727</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03445350640569927</v>
+        <v>0.03344016798200223</v>
       </c>
       <c r="W35">
-        <v>0.2276758631895361</v>
+        <v>0.2279148083898439</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1378140256227971</v>
+        <v>0.133760671928009</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1994126974902778</v>
+        <v>0.2013126974902779</v>
       </c>
       <c r="C36">
-        <v>90.40900904923356</v>
+        <v>84.61022568799203</v>
       </c>
       <c r="D36">
-        <v>199.8570090492336</v>
+        <v>197.415225687992</v>
       </c>
       <c r="E36">
-        <v>114.138</v>
+        <v>117.495</v>
       </c>
       <c r="F36">
-        <v>114.138</v>
+        <v>117.495</v>
       </c>
       <c r="G36">
         <v>4.69</v>
@@ -4227,37 +4227,37 @@
         <v>3.6</v>
       </c>
       <c r="M36">
-        <v>26.9137404</v>
+        <v>27.705321</v>
       </c>
       <c r="N36">
-        <v>-23.3137404</v>
+        <v>-24.105321</v>
       </c>
       <c r="O36">
-        <v>-5.8284351</v>
+        <v>-6.02633025</v>
       </c>
       <c r="P36">
-        <v>-17.4853053</v>
+        <v>-18.07899075</v>
       </c>
       <c r="Q36">
-        <v>-16.9653053</v>
+        <v>-17.55899075</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1847297918753499</v>
+        <v>0.1868671732888168</v>
       </c>
       <c r="T36">
-        <v>1.343557269028727</v>
+        <v>1.364227380859938</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03344016798200223</v>
+        <v>0.03248473461108788</v>
       </c>
       <c r="W36">
-        <v>0.2279148083898439</v>
+        <v>0.2281400995787055</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.133760671928009</v>
+        <v>0.1299389384443516</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2013126974902779</v>
+        <v>0.2032126974902778</v>
       </c>
       <c r="C37">
-        <v>84.61022568799203</v>
+        <v>78.87038786875991</v>
       </c>
       <c r="D37">
-        <v>197.415225687992</v>
+        <v>195.0323878687599</v>
       </c>
       <c r="E37">
-        <v>117.495</v>
+        <v>120.852</v>
       </c>
       <c r="F37">
-        <v>117.495</v>
+        <v>120.852</v>
       </c>
       <c r="G37">
         <v>4.69</v>
@@ -4309,37 +4309,37 @@
         <v>3.6</v>
       </c>
       <c r="M37">
-        <v>27.705321</v>
+        <v>28.4969016</v>
       </c>
       <c r="N37">
-        <v>-24.105321</v>
+        <v>-24.8969016</v>
       </c>
       <c r="O37">
-        <v>-6.02633025</v>
+        <v>-6.2242254</v>
       </c>
       <c r="P37">
-        <v>-18.07899075</v>
+        <v>-18.6726762</v>
       </c>
       <c r="Q37">
-        <v>-17.55899075</v>
+        <v>-18.1526762</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1868671732888168</v>
+        <v>0.1890713478714546</v>
       </c>
       <c r="T37">
-        <v>1.364227380859938</v>
+        <v>1.385543433685875</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03248473461108788</v>
+        <v>0.031582380871891</v>
       </c>
       <c r="W37">
-        <v>0.2281400995787055</v>
+        <v>0.2283528745904081</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1299389384443516</v>
+        <v>0.126329523487564</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2032126974902778</v>
+        <v>0.2051126974902779</v>
       </c>
       <c r="C38">
-        <v>78.87038786875992</v>
+        <v>73.18738659712081</v>
       </c>
       <c r="D38">
-        <v>195.0323878687599</v>
+        <v>192.7063865971208</v>
       </c>
       <c r="E38">
-        <v>120.852</v>
+        <v>124.209</v>
       </c>
       <c r="F38">
-        <v>120.852</v>
+        <v>124.209</v>
       </c>
       <c r="G38">
         <v>4.69</v>
@@ -4391,37 +4391,37 @@
         <v>3.6</v>
       </c>
       <c r="M38">
-        <v>28.4969016</v>
+        <v>29.2884822</v>
       </c>
       <c r="N38">
-        <v>-24.8969016</v>
+        <v>-25.6884822</v>
       </c>
       <c r="O38">
-        <v>-6.224225399999999</v>
+        <v>-6.422120549999999</v>
       </c>
       <c r="P38">
-        <v>-18.6726762</v>
+        <v>-19.26636165</v>
       </c>
       <c r="Q38">
-        <v>-18.1526762</v>
+        <v>-18.74636165</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1890713478714546</v>
+        <v>0.1913454962503666</v>
       </c>
       <c r="T38">
-        <v>1.385543433685875</v>
+        <v>1.407536186601523</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.031582380871891</v>
+        <v>0.03072880301048854</v>
       </c>
       <c r="W38">
-        <v>0.2283528745904081</v>
+        <v>0.2285541482501268</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1263295234875641</v>
+        <v>0.1229152120419542</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2051126974902779</v>
+        <v>0.2070126974902778</v>
       </c>
       <c r="C39">
-        <v>73.18738659712081</v>
+        <v>67.55921230232551</v>
       </c>
       <c r="D39">
-        <v>192.7063865971208</v>
+        <v>190.4352123023255</v>
       </c>
       <c r="E39">
-        <v>124.209</v>
+        <v>127.566</v>
       </c>
       <c r="F39">
-        <v>124.209</v>
+        <v>127.566</v>
       </c>
       <c r="G39">
         <v>4.69</v>
@@ -4473,37 +4473,37 @@
         <v>3.6</v>
       </c>
       <c r="M39">
-        <v>29.2884822</v>
+        <v>30.0800628</v>
       </c>
       <c r="N39">
-        <v>-25.6884822</v>
+        <v>-26.4800628</v>
       </c>
       <c r="O39">
-        <v>-6.422120549999999</v>
+        <v>-6.6200157</v>
       </c>
       <c r="P39">
-        <v>-19.26636165</v>
+        <v>-19.8600471</v>
       </c>
       <c r="Q39">
-        <v>-18.74636165</v>
+        <v>-19.3400471</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1913454962503666</v>
+        <v>0.1936930042544047</v>
       </c>
       <c r="T39">
-        <v>1.407536186601523</v>
+        <v>1.430238383159613</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03072880301048854</v>
+        <v>0.02992015029968621</v>
       </c>
       <c r="W39">
-        <v>0.2285541482501268</v>
+        <v>0.228744828559334</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1229152120419542</v>
+        <v>0.1196806011987449</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2070126974902778</v>
+        <v>0.2089126974902779</v>
       </c>
       <c r="C40">
-        <v>67.55921230232551</v>
+        <v>61.98394904666455</v>
       </c>
       <c r="D40">
-        <v>190.4352123023255</v>
+        <v>188.2169490466646</v>
       </c>
       <c r="E40">
-        <v>127.566</v>
+        <v>130.923</v>
       </c>
       <c r="F40">
-        <v>127.566</v>
+        <v>130.923</v>
       </c>
       <c r="G40">
         <v>4.69</v>
@@ -4555,37 +4555,37 @@
         <v>3.6</v>
       </c>
       <c r="M40">
-        <v>30.0800628</v>
+        <v>30.8716434</v>
       </c>
       <c r="N40">
-        <v>-26.4800628</v>
+        <v>-27.2716434</v>
       </c>
       <c r="O40">
-        <v>-6.6200157</v>
+        <v>-6.81791085</v>
       </c>
       <c r="P40">
-        <v>-19.8600471</v>
+        <v>-20.45373255</v>
       </c>
       <c r="Q40">
-        <v>-19.3400471</v>
+        <v>-19.93373255</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1936930042544047</v>
+        <v>0.1961174797339851</v>
       </c>
       <c r="T40">
-        <v>1.430238383159613</v>
+        <v>1.453684914031081</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02992015029968621</v>
+        <v>0.02915296695866862</v>
       </c>
       <c r="W40">
-        <v>0.228744828559334</v>
+        <v>0.2289257303911459</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1196806011987449</v>
+        <v>0.1166118678346745</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2089126974902779</v>
+        <v>0.2108126974902778</v>
       </c>
       <c r="C41">
-        <v>61.98394904666455</v>
+        <v>56.45976913489002</v>
       </c>
       <c r="D41">
-        <v>188.2169490466646</v>
+        <v>186.04976913489</v>
       </c>
       <c r="E41">
-        <v>130.923</v>
+        <v>134.28</v>
       </c>
       <c r="F41">
-        <v>130.923</v>
+        <v>134.28</v>
       </c>
       <c r="G41">
         <v>4.69</v>
@@ -4637,37 +4637,37 @@
         <v>3.6</v>
       </c>
       <c r="M41">
-        <v>30.8716434</v>
+        <v>31.663224</v>
       </c>
       <c r="N41">
-        <v>-27.2716434</v>
+        <v>-28.063224</v>
       </c>
       <c r="O41">
-        <v>-6.81791085</v>
+        <v>-7.015806</v>
       </c>
       <c r="P41">
-        <v>-20.45373255</v>
+        <v>-21.047418</v>
       </c>
       <c r="Q41">
-        <v>-19.93373255</v>
+        <v>-20.527418</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1961174797339851</v>
+        <v>0.1986227710628849</v>
       </c>
       <c r="T41">
-        <v>1.453684914031081</v>
+        <v>1.4779129959316</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02915296695866862</v>
+        <v>0.0284241427847019</v>
       </c>
       <c r="W41">
-        <v>0.2289257303911459</v>
+        <v>0.2290975871313673</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1166118678346745</v>
+        <v>0.1136965711388076</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2108126974902778</v>
+        <v>0.2127126974902779</v>
       </c>
       <c r="C42">
-        <v>56.45976913489002</v>
+        <v>50.98492809180888</v>
       </c>
       <c r="D42">
-        <v>186.04976913489</v>
+        <v>183.9319280918089</v>
       </c>
       <c r="E42">
-        <v>134.28</v>
+        <v>137.637</v>
       </c>
       <c r="F42">
-        <v>134.28</v>
+        <v>137.637</v>
       </c>
       <c r="G42">
         <v>4.69</v>
@@ -4719,37 +4719,37 @@
         <v>3.6</v>
       </c>
       <c r="M42">
-        <v>31.663224</v>
+        <v>32.4548046</v>
       </c>
       <c r="N42">
-        <v>-28.063224</v>
+        <v>-28.8548046</v>
       </c>
       <c r="O42">
-        <v>-7.015806</v>
+        <v>-7.21370115</v>
       </c>
       <c r="P42">
-        <v>-21.047418</v>
+        <v>-21.64110345</v>
       </c>
       <c r="Q42">
-        <v>-20.527418</v>
+        <v>-21.12110345</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1986227710628849</v>
+        <v>0.2012129875215778</v>
       </c>
       <c r="T42">
-        <v>1.4779129959316</v>
+        <v>1.502962368743999</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0284241427847019</v>
+        <v>0.02773087100946527</v>
       </c>
       <c r="W42">
-        <v>0.2290975871313673</v>
+        <v>0.2292610606159681</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1136965711388076</v>
+        <v>0.1109234840378611</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2127126974902779</v>
+        <v>0.2146126974902779</v>
       </c>
       <c r="C43">
-        <v>50.98492809180888</v>
+        <v>45.55775997904257</v>
       </c>
       <c r="D43">
-        <v>183.9319280918089</v>
+        <v>181.8617599790426</v>
       </c>
       <c r="E43">
-        <v>137.637</v>
+        <v>140.994</v>
       </c>
       <c r="F43">
-        <v>137.637</v>
+        <v>140.994</v>
       </c>
       <c r="G43">
         <v>4.69</v>
@@ -4801,37 +4801,37 @@
         <v>3.6</v>
       </c>
       <c r="M43">
-        <v>32.4548046</v>
+        <v>33.2463852</v>
       </c>
       <c r="N43">
-        <v>-28.8548046</v>
+        <v>-29.6463852</v>
       </c>
       <c r="O43">
-        <v>-7.21370115</v>
+        <v>-7.411596299999999</v>
       </c>
       <c r="P43">
-        <v>-21.64110345</v>
+        <v>-22.2347889</v>
       </c>
       <c r="Q43">
-        <v>-21.12110345</v>
+        <v>-21.7147889</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2012129875215778</v>
+        <v>0.2038925217891913</v>
       </c>
       <c r="T43">
-        <v>1.502962368743999</v>
+        <v>1.528875513032689</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02773087100946527</v>
+        <v>0.02707061217590657</v>
       </c>
       <c r="W43">
-        <v>0.2292610606159681</v>
+        <v>0.2294167496489213</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1109234840378611</v>
+        <v>0.1082824487036264</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2146126974902779</v>
+        <v>0.2165126974902779</v>
       </c>
       <c r="C44">
-        <v>45.55775997904254</v>
+        <v>40.17667302452733</v>
       </c>
       <c r="D44">
-        <v>181.8617599790425</v>
+        <v>179.8376730245273</v>
       </c>
       <c r="E44">
-        <v>140.994</v>
+        <v>144.351</v>
       </c>
       <c r="F44">
-        <v>140.994</v>
+        <v>144.351</v>
       </c>
       <c r="G44">
         <v>4.69</v>
@@ -4883,37 +4883,37 @@
         <v>3.6</v>
       </c>
       <c r="M44">
-        <v>33.2463852</v>
+        <v>34.0379658</v>
       </c>
       <c r="N44">
-        <v>-29.6463852</v>
+        <v>-30.4379658</v>
       </c>
       <c r="O44">
-        <v>-7.411596299999999</v>
+        <v>-7.60949145</v>
       </c>
       <c r="P44">
-        <v>-22.2347889</v>
+        <v>-22.82847435</v>
       </c>
       <c r="Q44">
-        <v>-21.7147889</v>
+        <v>-22.30847435</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2038925217891913</v>
+        <v>0.2066660748030367</v>
       </c>
       <c r="T44">
-        <v>1.528875513032689</v>
+        <v>1.555697890454315</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02707061217590657</v>
+        <v>0.02644106305553665</v>
       </c>
       <c r="W44">
-        <v>0.2294167496489213</v>
+        <v>0.2295651973315045</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1082824487036264</v>
+        <v>0.1057642522221466</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2165126974902779</v>
+        <v>0.2184126974902779</v>
       </c>
       <c r="C45">
-        <v>40.17667302452733</v>
+        <v>34.84014554065931</v>
       </c>
       <c r="D45">
-        <v>179.8376730245273</v>
+        <v>177.8581455406593</v>
       </c>
       <c r="E45">
-        <v>144.351</v>
+        <v>147.708</v>
       </c>
       <c r="F45">
-        <v>144.351</v>
+        <v>147.708</v>
       </c>
       <c r="G45">
         <v>4.69</v>
@@ -4965,37 +4965,37 @@
         <v>3.6</v>
       </c>
       <c r="M45">
-        <v>34.0379658</v>
+        <v>34.8295464</v>
       </c>
       <c r="N45">
-        <v>-30.4379658</v>
+        <v>-31.2295464</v>
       </c>
       <c r="O45">
-        <v>-7.60949145</v>
+        <v>-7.807386599999999</v>
       </c>
       <c r="P45">
-        <v>-22.82847435</v>
+        <v>-23.4221598</v>
       </c>
       <c r="Q45">
-        <v>-22.30847435</v>
+        <v>-22.9021598</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2066660748030367</v>
+        <v>0.2095386832816624</v>
       </c>
       <c r="T45">
-        <v>1.555697890454315</v>
+        <v>1.583478209926714</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02644106305553665</v>
+        <v>0.02584012980427446</v>
       </c>
       <c r="W45">
-        <v>0.2295651973315045</v>
+        <v>0.2297068973921521</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1057642522221466</v>
+        <v>0.1033605192170979</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2184126974902779</v>
+        <v>0.2203126974902778</v>
       </c>
       <c r="C46">
-        <v>34.84014554065931</v>
+        <v>29.54672210908592</v>
       </c>
       <c r="D46">
-        <v>177.8581455406593</v>
+        <v>175.9217221090859</v>
       </c>
       <c r="E46">
-        <v>147.708</v>
+        <v>151.065</v>
       </c>
       <c r="F46">
-        <v>147.708</v>
+        <v>151.065</v>
       </c>
       <c r="G46">
         <v>4.69</v>
@@ -5047,37 +5047,37 @@
         <v>3.6</v>
       </c>
       <c r="M46">
-        <v>34.8295464</v>
+        <v>35.621127</v>
       </c>
       <c r="N46">
-        <v>-31.2295464</v>
+        <v>-32.021127</v>
       </c>
       <c r="O46">
-        <v>-7.807386599999999</v>
+        <v>-8.00528175</v>
       </c>
       <c r="P46">
-        <v>-23.4221598</v>
+        <v>-24.01584525</v>
       </c>
       <c r="Q46">
-        <v>-22.9021598</v>
+        <v>-23.49584525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2095386832816624</v>
+        <v>0.2125157502504199</v>
       </c>
       <c r="T46">
-        <v>1.583478209926714</v>
+        <v>1.612268722834472</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02584012980427446</v>
+        <v>0.0252659046975128</v>
       </c>
       <c r="W46">
-        <v>0.2297068973921521</v>
+        <v>0.2298422996723265</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1033605192170979</v>
+        <v>0.1010636187900512</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2203126974902778</v>
+        <v>0.2222126974902779</v>
       </c>
       <c r="C47">
-        <v>29.54672210908592</v>
+        <v>24.29501001204042</v>
       </c>
       <c r="D47">
-        <v>175.9217221090859</v>
+        <v>174.0270100120404</v>
       </c>
       <c r="E47">
-        <v>151.065</v>
+        <v>154.422</v>
       </c>
       <c r="F47">
-        <v>151.065</v>
+        <v>154.422</v>
       </c>
       <c r="G47">
         <v>4.69</v>
@@ -5129,37 +5129,37 @@
         <v>3.6</v>
       </c>
       <c r="M47">
-        <v>35.621127</v>
+        <v>36.4127076</v>
       </c>
       <c r="N47">
-        <v>-32.021127</v>
+        <v>-32.8127076</v>
       </c>
       <c r="O47">
-        <v>-8.00528175</v>
+        <v>-8.203176899999999</v>
       </c>
       <c r="P47">
-        <v>-24.01584525</v>
+        <v>-24.6095307</v>
       </c>
       <c r="Q47">
-        <v>-23.49584525</v>
+        <v>-24.0895307</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2125157502504199</v>
+        <v>0.215603078958761</v>
       </c>
       <c r="T47">
-        <v>1.612268722834472</v>
+        <v>1.642125551035111</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.0252659046975128</v>
+        <v>0.02471664589974078</v>
       </c>
       <c r="W47">
-        <v>0.2298422996723265</v>
+        <v>0.2299718148968411</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1010636187900512</v>
+        <v>0.09886658359896316</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2222126974902779</v>
+        <v>0.2241126974902778</v>
       </c>
       <c r="C48">
-        <v>24.29501001204042</v>
+        <v>19.08367589183058</v>
       </c>
       <c r="D48">
-        <v>174.0270100120404</v>
+        <v>172.1726758918306</v>
       </c>
       <c r="E48">
-        <v>154.422</v>
+        <v>157.779</v>
       </c>
       <c r="F48">
-        <v>154.422</v>
+        <v>157.779</v>
       </c>
       <c r="G48">
         <v>4.69</v>
@@ -5211,37 +5211,37 @@
         <v>3.6</v>
       </c>
       <c r="M48">
-        <v>36.4127076</v>
+        <v>37.2042882</v>
       </c>
       <c r="N48">
-        <v>-32.8127076</v>
+        <v>-33.6042882</v>
       </c>
       <c r="O48">
-        <v>-8.203176899999999</v>
+        <v>-8.40107205</v>
       </c>
       <c r="P48">
-        <v>-24.6095307</v>
+        <v>-25.20321615</v>
       </c>
       <c r="Q48">
-        <v>-24.0895307</v>
+        <v>-24.68321615</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.215603078958761</v>
+        <v>0.2188069106372282</v>
       </c>
       <c r="T48">
-        <v>1.642125551035111</v>
+        <v>1.673109051998037</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02471664589974078</v>
+        <v>0.02419075981676757</v>
       </c>
       <c r="W48">
-        <v>0.2299718148968411</v>
+        <v>0.2300958188352062</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.09886658359896316</v>
+        <v>0.09676303926707031</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2241126974902778</v>
+        <v>0.2260126974902779</v>
       </c>
       <c r="C49">
-        <v>19.08367589183058</v>
+        <v>13.91144262164369</v>
       </c>
       <c r="D49">
-        <v>172.1726758918306</v>
+        <v>170.3574426216437</v>
       </c>
       <c r="E49">
-        <v>157.779</v>
+        <v>161.136</v>
       </c>
       <c r="F49">
-        <v>157.779</v>
+        <v>161.136</v>
       </c>
       <c r="G49">
         <v>4.69</v>
@@ -5293,37 +5293,37 @@
         <v>3.6</v>
       </c>
       <c r="M49">
-        <v>37.2042882</v>
+        <v>37.9958688</v>
       </c>
       <c r="N49">
-        <v>-33.6042882</v>
+        <v>-34.3958688</v>
       </c>
       <c r="O49">
-        <v>-8.40107205</v>
+        <v>-8.598967200000001</v>
       </c>
       <c r="P49">
-        <v>-25.20321615</v>
+        <v>-25.7969016</v>
       </c>
       <c r="Q49">
-        <v>-24.68321615</v>
+        <v>-25.2769016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2188069106372282</v>
+        <v>0.222133966611021</v>
       </c>
       <c r="T49">
-        <v>1.673109051998037</v>
+        <v>1.705284226074923</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02419075981676757</v>
+        <v>0.02368678565391825</v>
       </c>
       <c r="W49">
-        <v>0.2300958188352062</v>
+        <v>0.2302146559428061</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.09676303926707031</v>
+        <v>0.09474714261567307</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2260126974902779</v>
+        <v>0.2279126974902779</v>
       </c>
       <c r="C50">
-        <v>13.91144262164369</v>
+        <v>8.777086372234407</v>
       </c>
       <c r="D50">
-        <v>170.3574426216437</v>
+        <v>168.5800863722344</v>
       </c>
       <c r="E50">
-        <v>161.136</v>
+        <v>164.493</v>
       </c>
       <c r="F50">
-        <v>161.136</v>
+        <v>164.493</v>
       </c>
       <c r="G50">
         <v>4.69</v>
@@ -5375,37 +5375,37 @@
         <v>3.6</v>
       </c>
       <c r="M50">
-        <v>37.9958688</v>
+        <v>38.7874494</v>
       </c>
       <c r="N50">
-        <v>-34.3958688</v>
+        <v>-35.1874494</v>
       </c>
       <c r="O50">
-        <v>-8.598967200000001</v>
+        <v>-8.79686235</v>
       </c>
       <c r="P50">
-        <v>-25.7969016</v>
+        <v>-26.39058705</v>
       </c>
       <c r="Q50">
-        <v>-25.2769016</v>
+        <v>-25.87058705</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.222133966611021</v>
+        <v>0.2255914953680999</v>
       </c>
       <c r="T50">
-        <v>1.705284226074923</v>
+        <v>1.738721171684235</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02368678565391825</v>
+        <v>0.02320338186506278</v>
       </c>
       <c r="W50">
-        <v>0.2302146559428061</v>
+        <v>0.2303286425562182</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.09474714261567307</v>
+        <v>0.09281352746025118</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2279126974902779</v>
+        <v>0.2298126974902778</v>
       </c>
       <c r="C51">
-        <v>8.777086372234407</v>
+        <v>3.679433860338236</v>
       </c>
       <c r="D51">
-        <v>168.5800863722344</v>
+        <v>166.8394338603382</v>
       </c>
       <c r="E51">
-        <v>164.493</v>
+        <v>167.85</v>
       </c>
       <c r="F51">
-        <v>164.493</v>
+        <v>167.85</v>
       </c>
       <c r="G51">
         <v>4.69</v>
@@ -5457,37 +5457,37 @@
         <v>3.6</v>
       </c>
       <c r="M51">
-        <v>38.7874494</v>
+        <v>39.57903</v>
       </c>
       <c r="N51">
-        <v>-35.1874494</v>
+        <v>-35.97903</v>
       </c>
       <c r="O51">
-        <v>-8.79686235</v>
+        <v>-8.9947575</v>
       </c>
       <c r="P51">
-        <v>-26.39058705</v>
+        <v>-26.9842725</v>
       </c>
       <c r="Q51">
-        <v>-25.87058705</v>
+        <v>-26.4642725</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2255914953680999</v>
+        <v>0.2291873252754618</v>
       </c>
       <c r="T51">
-        <v>1.738721171684235</v>
+        <v>1.773495595117919</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02320338186506278</v>
+        <v>0.02273931422776152</v>
       </c>
       <c r="W51">
-        <v>0.2303286425562182</v>
+        <v>0.2304380697050938</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.09281352746025118</v>
+        <v>0.09095725691104606</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2298126974902778</v>
+        <v>0.2317126974902778</v>
       </c>
       <c r="C52">
-        <v>3.679433860338236</v>
+        <v>-1.382640234190546</v>
       </c>
       <c r="D52">
-        <v>166.8394338603382</v>
+        <v>165.1343597658094</v>
       </c>
       <c r="E52">
-        <v>167.85</v>
+        <v>171.207</v>
       </c>
       <c r="F52">
-        <v>167.85</v>
+        <v>171.207</v>
       </c>
       <c r="G52">
         <v>4.69</v>
@@ -5539,37 +5539,37 @@
         <v>3.6</v>
       </c>
       <c r="M52">
-        <v>39.57903</v>
+        <v>40.3706106</v>
       </c>
       <c r="N52">
-        <v>-35.97903</v>
+        <v>-36.7706106</v>
       </c>
       <c r="O52">
-        <v>-8.9947575</v>
+        <v>-9.192652649999999</v>
       </c>
       <c r="P52">
-        <v>-26.9842725</v>
+        <v>-27.57795795</v>
       </c>
       <c r="Q52">
-        <v>-26.4642725</v>
+        <v>-27.05795795</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2291873252754618</v>
+        <v>0.2329299237504713</v>
       </c>
       <c r="T52">
-        <v>1.773495595117919</v>
+        <v>1.809689382773387</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02273931422776152</v>
+        <v>0.02229344532133483</v>
       </c>
       <c r="W52">
-        <v>0.2304380697050938</v>
+        <v>0.2305432055932293</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.09095725691104606</v>
+        <v>0.08917378128533937</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2317126974902778</v>
+        <v>0.2336126974902779</v>
       </c>
       <c r="C53">
-        <v>-1.382640234190546</v>
+        <v>-6.410215694464142</v>
       </c>
       <c r="D53">
-        <v>165.1343597658094</v>
+        <v>163.4637843055359</v>
       </c>
       <c r="E53">
-        <v>171.207</v>
+        <v>174.564</v>
       </c>
       <c r="F53">
-        <v>171.207</v>
+        <v>174.564</v>
       </c>
       <c r="G53">
         <v>4.69</v>
@@ -5621,37 +5621,37 @@
         <v>3.6</v>
       </c>
       <c r="M53">
-        <v>40.3706106</v>
+        <v>41.1621912</v>
       </c>
       <c r="N53">
-        <v>-36.7706106</v>
+        <v>-37.5621912</v>
       </c>
       <c r="O53">
-        <v>-9.192652649999999</v>
+        <v>-9.3905478</v>
       </c>
       <c r="P53">
-        <v>-27.57795795</v>
+        <v>-28.1716434</v>
       </c>
       <c r="Q53">
-        <v>-27.05795795</v>
+        <v>-27.6516434</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2329299237504713</v>
+        <v>0.2368284638286061</v>
       </c>
       <c r="T53">
-        <v>1.809689382773387</v>
+        <v>1.8473912449145</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02229344532133483</v>
+        <v>0.02186472521900146</v>
       </c>
       <c r="W53">
-        <v>0.2305432055932293</v>
+        <v>0.2306442977933595</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.08917378128533937</v>
+        <v>0.08745890087600583</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2336126974902779</v>
+        <v>0.2355126974902778</v>
       </c>
       <c r="C54">
-        <v>-6.410215694464142</v>
+        <v>-11.40432904686074</v>
       </c>
       <c r="D54">
-        <v>163.4637843055359</v>
+        <v>161.8266709531393</v>
       </c>
       <c r="E54">
-        <v>174.564</v>
+        <v>177.921</v>
       </c>
       <c r="F54">
-        <v>174.564</v>
+        <v>177.921</v>
       </c>
       <c r="G54">
         <v>4.69</v>
@@ -5703,37 +5703,37 @@
         <v>3.6</v>
       </c>
       <c r="M54">
-        <v>41.1621912</v>
+        <v>41.9537718</v>
       </c>
       <c r="N54">
-        <v>-37.5621912</v>
+        <v>-38.3537718</v>
       </c>
       <c r="O54">
-        <v>-9.3905478</v>
+        <v>-9.588442949999999</v>
       </c>
       <c r="P54">
-        <v>-28.1716434</v>
+        <v>-28.76532885</v>
       </c>
       <c r="Q54">
-        <v>-27.6516434</v>
+        <v>-28.24532885</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2368284638286061</v>
+        <v>0.2408928992292147</v>
       </c>
       <c r="T54">
-        <v>1.8473912449145</v>
+        <v>1.886697441614808</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02186472521900146</v>
+        <v>0.02145218323373728</v>
       </c>
       <c r="W54">
-        <v>0.2306442977933595</v>
+        <v>0.2307415751934848</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.08745890087600583</v>
+        <v>0.08580873293494917</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2355126974902778</v>
+        <v>0.2374126974902779</v>
       </c>
       <c r="C55">
-        <v>-11.40432904686074</v>
+        <v>-16.36597570565831</v>
       </c>
       <c r="D55">
-        <v>161.8266709531393</v>
+        <v>160.2220242943417</v>
       </c>
       <c r="E55">
-        <v>177.921</v>
+        <v>181.278</v>
       </c>
       <c r="F55">
-        <v>177.921</v>
+        <v>181.278</v>
       </c>
       <c r="G55">
         <v>4.69</v>
@@ -5785,37 +5785,37 @@
         <v>3.6</v>
       </c>
       <c r="M55">
-        <v>41.9537718</v>
+        <v>42.7453524</v>
       </c>
       <c r="N55">
-        <v>-38.3537718</v>
+        <v>-39.1453524</v>
       </c>
       <c r="O55">
-        <v>-9.588442949999999</v>
+        <v>-9.7863381</v>
       </c>
       <c r="P55">
-        <v>-28.76532885</v>
+        <v>-29.3590143</v>
       </c>
       <c r="Q55">
-        <v>-28.24532885</v>
+        <v>-28.8390143</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2408928992292147</v>
+        <v>0.2451340492124585</v>
       </c>
       <c r="T55">
-        <v>1.886697441614808</v>
+        <v>1.927712603389043</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02145218323373728</v>
+        <v>0.02105492058126067</v>
       </c>
       <c r="W55">
-        <v>0.2307415751934848</v>
+        <v>0.2308352497269388</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.08580873293494917</v>
+        <v>0.08421968232504273</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2374126974902779</v>
+        <v>0.2393126974902779</v>
       </c>
       <c r="C56">
-        <v>-16.36597570565831</v>
+        <v>-21.29611199132535</v>
       </c>
       <c r="D56">
-        <v>160.2220242943417</v>
+        <v>158.6488880086747</v>
       </c>
       <c r="E56">
-        <v>181.278</v>
+        <v>184.635</v>
       </c>
       <c r="F56">
-        <v>181.278</v>
+        <v>184.635</v>
       </c>
       <c r="G56">
         <v>4.69</v>
@@ -5867,37 +5867,37 @@
         <v>3.6</v>
       </c>
       <c r="M56">
-        <v>42.7453524</v>
+        <v>43.536933</v>
       </c>
       <c r="N56">
-        <v>-39.1453524</v>
+        <v>-39.936933</v>
       </c>
       <c r="O56">
-        <v>-9.7863381</v>
+        <v>-9.984233250000001</v>
       </c>
       <c r="P56">
-        <v>-29.3590143</v>
+        <v>-29.95269975</v>
       </c>
       <c r="Q56">
-        <v>-28.8390143</v>
+        <v>-29.43269975</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2451340492124585</v>
+        <v>0.2495636947505132</v>
       </c>
       <c r="T56">
-        <v>1.927712603389043</v>
+        <v>1.970550661242133</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02105492058126067</v>
+        <v>0.02067210384341956</v>
       </c>
       <c r="W56">
-        <v>0.2308352497269388</v>
+        <v>0.2309255179137217</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.08421968232504273</v>
+        <v>0.08268841537367833</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2393126974902779</v>
+        <v>0.2412126974902778</v>
       </c>
       <c r="C57">
-        <v>-21.29611199132535</v>
+        <v>-26.19565703106858</v>
       </c>
       <c r="D57">
-        <v>158.6488880086747</v>
+        <v>157.1063429689314</v>
       </c>
       <c r="E57">
-        <v>184.635</v>
+        <v>187.992</v>
       </c>
       <c r="F57">
-        <v>184.635</v>
+        <v>187.992</v>
       </c>
       <c r="G57">
         <v>4.69</v>
@@ -5949,37 +5949,37 @@
         <v>3.6</v>
       </c>
       <c r="M57">
-        <v>43.536933</v>
+        <v>44.32851360000001</v>
       </c>
       <c r="N57">
-        <v>-39.936933</v>
+        <v>-40.72851360000001</v>
       </c>
       <c r="O57">
-        <v>-9.984233250000001</v>
+        <v>-10.1821284</v>
       </c>
       <c r="P57">
-        <v>-29.95269975</v>
+        <v>-30.5463852</v>
       </c>
       <c r="Q57">
-        <v>-29.43269975</v>
+        <v>-30.0263852</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2495636947505132</v>
+        <v>0.2541946878130248</v>
       </c>
       <c r="T57">
-        <v>1.970550661242133</v>
+        <v>2.01533590354309</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02067210384341956</v>
+        <v>0.02030295913192992</v>
       </c>
       <c r="W57">
-        <v>0.2309255179137217</v>
+        <v>0.2310125622366909</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.08268841537367833</v>
+        <v>0.08121183652771968</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2412126974902778</v>
+        <v>0.2431126974902779</v>
       </c>
       <c r="C58">
-        <v>-26.19565703106858</v>
+        <v>-31.06549454957485</v>
       </c>
       <c r="D58">
-        <v>157.1063429689314</v>
+        <v>155.5935054504252</v>
       </c>
       <c r="E58">
-        <v>187.992</v>
+        <v>191.349</v>
       </c>
       <c r="F58">
-        <v>187.992</v>
+        <v>191.349</v>
       </c>
       <c r="G58">
         <v>4.69</v>
@@ -6031,37 +6031,37 @@
         <v>3.6</v>
       </c>
       <c r="M58">
-        <v>44.32851360000001</v>
+        <v>45.1200942</v>
       </c>
       <c r="N58">
-        <v>-40.72851360000001</v>
+        <v>-41.5200942</v>
       </c>
       <c r="O58">
-        <v>-10.1821284</v>
+        <v>-10.38002355</v>
       </c>
       <c r="P58">
-        <v>-30.5463852</v>
+        <v>-31.14007065</v>
       </c>
       <c r="Q58">
-        <v>-30.0263852</v>
+        <v>-30.62007065</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2541946878130248</v>
+        <v>0.2590410759016998</v>
       </c>
       <c r="T58">
-        <v>2.01533590354309</v>
+        <v>2.062204180369674</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02030295913192992</v>
+        <v>0.01994676686645747</v>
       </c>
       <c r="W58">
-        <v>0.2310125622366909</v>
+        <v>0.2310965523728893</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.08121183652771968</v>
+        <v>0.07978706746582986</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2431126974902779</v>
+        <v>0.2450126974902779</v>
       </c>
       <c r="C59">
-        <v>-31.06549454957485</v>
+        <v>-35.90647455727611</v>
       </c>
       <c r="D59">
-        <v>155.5935054504252</v>
+        <v>154.1095254427239</v>
       </c>
       <c r="E59">
-        <v>191.349</v>
+        <v>194.706</v>
       </c>
       <c r="F59">
-        <v>191.349</v>
+        <v>194.706</v>
       </c>
       <c r="G59">
         <v>4.69</v>
@@ -6113,37 +6113,37 @@
         <v>3.6</v>
       </c>
       <c r="M59">
-        <v>45.1200942</v>
+        <v>45.91167480000001</v>
       </c>
       <c r="N59">
-        <v>-41.5200942</v>
+        <v>-42.31167480000001</v>
       </c>
       <c r="O59">
-        <v>-10.38002355</v>
+        <v>-10.5779187</v>
       </c>
       <c r="P59">
-        <v>-31.14007065</v>
+        <v>-31.7337561</v>
       </c>
       <c r="Q59">
-        <v>-30.62007065</v>
+        <v>-31.2137561</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2590410759016998</v>
+        <v>0.2641182443755499</v>
       </c>
       <c r="T59">
-        <v>2.062204180369674</v>
+        <v>2.111304279902285</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01994676686645747</v>
+        <v>0.01960285709289786</v>
       </c>
       <c r="W59">
-        <v>0.2310965523728893</v>
+        <v>0.2311776462974947</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.07978706746582986</v>
+        <v>0.07841142837159143</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2450126974902778</v>
+        <v>0.2469126974902778</v>
       </c>
       <c r="C60">
-        <v>-35.90647455727603</v>
+        <v>-40.71941494291644</v>
       </c>
       <c r="D60">
-        <v>154.109525442724</v>
+        <v>152.6535850570835</v>
       </c>
       <c r="E60">
-        <v>194.706</v>
+        <v>198.063</v>
       </c>
       <c r="F60">
-        <v>194.706</v>
+        <v>198.063</v>
       </c>
       <c r="G60">
         <v>4.69</v>
@@ -6195,37 +6195,37 @@
         <v>3.6</v>
       </c>
       <c r="M60">
-        <v>45.9116748</v>
+        <v>46.7032554</v>
       </c>
       <c r="N60">
-        <v>-42.3116748</v>
+        <v>-43.10325539999999</v>
       </c>
       <c r="O60">
-        <v>-10.5779187</v>
+        <v>-10.77581385</v>
       </c>
       <c r="P60">
-        <v>-31.7337561</v>
+        <v>-32.32744155</v>
       </c>
       <c r="Q60">
-        <v>-31.2137561</v>
+        <v>-31.80744155</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2641182443755498</v>
+        <v>0.2694430796042218</v>
       </c>
       <c r="T60">
-        <v>2.111304279902285</v>
+        <v>2.162799506241365</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01960285709289786</v>
+        <v>0.019270605277764</v>
       </c>
       <c r="W60">
-        <v>0.2311776462974947</v>
+        <v>0.2312559912755033</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.07841142837159143</v>
+        <v>0.07708242111105601</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2469126974902778</v>
+        <v>0.2488126974902778</v>
       </c>
       <c r="C61">
-        <v>-40.71941494291644</v>
+        <v>-45.50510297669007</v>
       </c>
       <c r="D61">
-        <v>152.6535850570835</v>
+        <v>151.2248970233099</v>
       </c>
       <c r="E61">
-        <v>198.063</v>
+        <v>201.42</v>
       </c>
       <c r="F61">
-        <v>198.063</v>
+        <v>201.42</v>
       </c>
       <c r="G61">
         <v>4.69</v>
@@ -6277,37 +6277,37 @@
         <v>3.6</v>
       </c>
       <c r="M61">
-        <v>46.7032554</v>
+        <v>47.494836</v>
       </c>
       <c r="N61">
-        <v>-43.10325539999999</v>
+        <v>-43.894836</v>
       </c>
       <c r="O61">
-        <v>-10.77581385</v>
+        <v>-10.973709</v>
       </c>
       <c r="P61">
-        <v>-32.32744155</v>
+        <v>-32.921127</v>
       </c>
       <c r="Q61">
-        <v>-31.80744155</v>
+        <v>-32.401127</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2694430796042218</v>
+        <v>0.2750341565943273</v>
       </c>
       <c r="T61">
-        <v>2.162799506241365</v>
+        <v>2.216869493897399</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.019270605277764</v>
+        <v>0.0189494285231346</v>
       </c>
       <c r="W61">
-        <v>0.2312559912755033</v>
+        <v>0.2313317247542448</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.07708242111105601</v>
+        <v>0.07579771409253844</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2488126974902778</v>
+        <v>0.2507126974902778</v>
       </c>
       <c r="C62">
-        <v>-45.50510297669007</v>
+        <v>-50.26429672975368</v>
       </c>
       <c r="D62">
-        <v>151.2248970233099</v>
+        <v>149.8227032702463</v>
       </c>
       <c r="E62">
-        <v>201.42</v>
+        <v>204.777</v>
       </c>
       <c r="F62">
-        <v>201.42</v>
+        <v>204.777</v>
       </c>
       <c r="G62">
         <v>4.69</v>
@@ -6359,37 +6359,37 @@
         <v>3.6</v>
       </c>
       <c r="M62">
-        <v>47.494836</v>
+        <v>48.2864166</v>
       </c>
       <c r="N62">
-        <v>-43.894836</v>
+        <v>-44.68641659999999</v>
       </c>
       <c r="O62">
-        <v>-10.973709</v>
+        <v>-11.17160415</v>
       </c>
       <c r="P62">
-        <v>-32.921127</v>
+        <v>-33.51481244999999</v>
       </c>
       <c r="Q62">
-        <v>-32.401127</v>
+        <v>-32.99481244999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2750341565943273</v>
+        <v>0.2809119554813613</v>
       </c>
       <c r="T62">
-        <v>2.216869493897399</v>
+        <v>2.27371230143323</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0189494285231346</v>
+        <v>0.01863878215390289</v>
       </c>
       <c r="W62">
-        <v>0.2313317247542448</v>
+        <v>0.2314049751681097</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.07579771409253844</v>
+        <v>0.07455512861561153</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2507126974902778</v>
+        <v>0.2526126974902778</v>
       </c>
       <c r="C63">
-        <v>-50.26429672975368</v>
+        <v>-54.99772641549313</v>
       </c>
       <c r="D63">
-        <v>149.8227032702463</v>
+        <v>148.4462735845069</v>
       </c>
       <c r="E63">
-        <v>204.777</v>
+        <v>208.134</v>
       </c>
       <c r="F63">
-        <v>204.777</v>
+        <v>208.134</v>
       </c>
       <c r="G63">
         <v>4.69</v>
@@ -6441,37 +6441,37 @@
         <v>3.6</v>
       </c>
       <c r="M63">
-        <v>48.2864166</v>
+        <v>49.0779972</v>
       </c>
       <c r="N63">
-        <v>-44.68641659999999</v>
+        <v>-45.4779972</v>
       </c>
       <c r="O63">
-        <v>-11.17160415</v>
+        <v>-11.3694993</v>
       </c>
       <c r="P63">
-        <v>-33.51481244999999</v>
+        <v>-34.1084979</v>
       </c>
       <c r="Q63">
-        <v>-32.99481244999999</v>
+        <v>-33.58849789999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2809119554813613</v>
+        <v>0.2870991122045551</v>
       </c>
       <c r="T63">
-        <v>2.27371230143323</v>
+        <v>2.333546835681473</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01863878215390289</v>
+        <v>0.01833815663529155</v>
       </c>
       <c r="W63">
-        <v>0.2314049751681097</v>
+        <v>0.2314758626653982</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.07455512861561153</v>
+        <v>0.07335262654116625</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2526126974902778</v>
+        <v>0.2545126974902778</v>
       </c>
       <c r="C64">
-        <v>-54.99772641549313</v>
+        <v>-59.70609565752835</v>
       </c>
       <c r="D64">
-        <v>148.4462735845069</v>
+        <v>147.0949043424716</v>
       </c>
       <c r="E64">
-        <v>208.134</v>
+        <v>211.491</v>
       </c>
       <c r="F64">
-        <v>208.134</v>
+        <v>211.491</v>
       </c>
       <c r="G64">
         <v>4.69</v>
@@ -6523,37 +6523,37 @@
         <v>3.6</v>
       </c>
       <c r="M64">
-        <v>49.0779972</v>
+        <v>49.8695778</v>
       </c>
       <c r="N64">
-        <v>-45.4779972</v>
+        <v>-46.2695778</v>
       </c>
       <c r="O64">
-        <v>-11.3694993</v>
+        <v>-11.56739445</v>
       </c>
       <c r="P64">
-        <v>-34.1084979</v>
+        <v>-34.70218335</v>
       </c>
       <c r="Q64">
-        <v>-33.58849789999999</v>
+        <v>-34.18218335</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2870991122045551</v>
+        <v>0.2936207098317052</v>
       </c>
       <c r="T64">
-        <v>2.333546835681473</v>
+        <v>2.396615669078269</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01833815663529155</v>
+        <v>0.01804707478393771</v>
       </c>
       <c r="W64">
-        <v>0.2314758626653982</v>
+        <v>0.2315444997659475</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.07335262654116625</v>
+        <v>0.07218829913575087</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2545126974902778</v>
+        <v>0.2564126974902778</v>
       </c>
       <c r="C65">
-        <v>-59.70609565752835</v>
+        <v>-64.39008268908469</v>
       </c>
       <c r="D65">
-        <v>147.0949043424716</v>
+        <v>145.7679173109153</v>
       </c>
       <c r="E65">
-        <v>211.491</v>
+        <v>214.848</v>
       </c>
       <c r="F65">
-        <v>211.491</v>
+        <v>214.848</v>
       </c>
       <c r="G65">
         <v>4.69</v>
@@ -6605,37 +6605,37 @@
         <v>3.6</v>
       </c>
       <c r="M65">
-        <v>49.8695778</v>
+        <v>50.6611584</v>
       </c>
       <c r="N65">
-        <v>-46.2695778</v>
+        <v>-47.0611584</v>
       </c>
       <c r="O65">
-        <v>-11.56739445</v>
+        <v>-11.7652896</v>
       </c>
       <c r="P65">
-        <v>-34.70218335</v>
+        <v>-35.29586879999999</v>
       </c>
       <c r="Q65">
-        <v>-34.18218335</v>
+        <v>-34.77586879999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2936207098317052</v>
+        <v>0.3005046184381415</v>
       </c>
       <c r="T65">
-        <v>2.396615669078269</v>
+        <v>2.463188326552666</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01804707478393771</v>
+        <v>0.01776508924043869</v>
       </c>
       <c r="W65">
-        <v>0.2315444997659475</v>
+        <v>0.2316109919571046</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.07218829913575087</v>
+        <v>0.07106035696175483</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2564126974902778</v>
+        <v>0.2583126974902779</v>
       </c>
       <c r="C66">
-        <v>-64.39008268908469</v>
+        <v>-69.050341488025</v>
       </c>
       <c r="D66">
-        <v>145.7679173109153</v>
+        <v>144.464658511975</v>
       </c>
       <c r="E66">
-        <v>214.848</v>
+        <v>218.205</v>
       </c>
       <c r="F66">
-        <v>214.848</v>
+        <v>218.205</v>
       </c>
       <c r="G66">
         <v>4.69</v>
@@ -6687,37 +6687,37 @@
         <v>3.6</v>
       </c>
       <c r="M66">
-        <v>50.6611584</v>
+        <v>51.45273900000001</v>
       </c>
       <c r="N66">
-        <v>-47.0611584</v>
+        <v>-47.85273900000001</v>
       </c>
       <c r="O66">
-        <v>-11.7652896</v>
+        <v>-11.96318475</v>
       </c>
       <c r="P66">
-        <v>-35.29586879999999</v>
+        <v>-35.88955425</v>
       </c>
       <c r="Q66">
-        <v>-34.77586879999999</v>
+        <v>-35.36955425</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3005046184381415</v>
+        <v>0.3077818932506598</v>
       </c>
       <c r="T66">
-        <v>2.463188326552666</v>
+        <v>2.533565135882742</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01776508924043869</v>
+        <v>0.01749178017520116</v>
       </c>
       <c r="W66">
-        <v>0.2316109919571046</v>
+        <v>0.2316754382346876</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.07106035696175483</v>
+        <v>0.06996712070080469</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2583126974902779</v>
+        <v>0.2602126974902779</v>
       </c>
       <c r="C67">
-        <v>-69.050341488025</v>
+        <v>-73.68750285153379</v>
       </c>
       <c r="D67">
-        <v>144.464658511975</v>
+        <v>143.1844971484662</v>
       </c>
       <c r="E67">
-        <v>218.205</v>
+        <v>221.562</v>
       </c>
       <c r="F67">
-        <v>218.205</v>
+        <v>221.562</v>
       </c>
       <c r="G67">
         <v>4.69</v>
@@ -6769,37 +6769,37 @@
         <v>3.6</v>
       </c>
       <c r="M67">
-        <v>51.45273900000001</v>
+        <v>52.2443196</v>
       </c>
       <c r="N67">
-        <v>-47.85273900000001</v>
+        <v>-48.6443196</v>
       </c>
       <c r="O67">
-        <v>-11.96318475</v>
+        <v>-12.1610799</v>
       </c>
       <c r="P67">
-        <v>-35.88955425</v>
+        <v>-36.4832397</v>
       </c>
       <c r="Q67">
-        <v>-35.36955425</v>
+        <v>-35.9632397</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3077818932506598</v>
+        <v>0.3154872430521498</v>
       </c>
       <c r="T67">
-        <v>2.533565135882742</v>
+        <v>2.608081757526352</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01749178017520116</v>
+        <v>0.01722675320284963</v>
       </c>
       <c r="W67">
-        <v>0.2316754382346876</v>
+        <v>0.2317379315947681</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.06996712070080469</v>
+        <v>0.06890701281139855</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2602126974902779</v>
+        <v>0.2621126974902779</v>
       </c>
       <c r="C68">
-        <v>-73.68750285153379</v>
+        <v>-78.30217541416417</v>
       </c>
       <c r="D68">
-        <v>143.1844971484662</v>
+        <v>141.9268245858358</v>
       </c>
       <c r="E68">
-        <v>221.562</v>
+        <v>224.919</v>
       </c>
       <c r="F68">
-        <v>221.562</v>
+        <v>224.919</v>
       </c>
       <c r="G68">
         <v>4.69</v>
@@ -6851,37 +6851,37 @@
         <v>3.6</v>
       </c>
       <c r="M68">
-        <v>52.2443196</v>
+        <v>53.03590020000001</v>
       </c>
       <c r="N68">
-        <v>-48.6443196</v>
+        <v>-49.43590020000001</v>
       </c>
       <c r="O68">
-        <v>-12.1610799</v>
+        <v>-12.35897505</v>
       </c>
       <c r="P68">
-        <v>-36.4832397</v>
+        <v>-37.07692515000001</v>
       </c>
       <c r="Q68">
-        <v>-35.9632397</v>
+        <v>-36.55692515</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3154872430521498</v>
+        <v>0.3236595837506999</v>
       </c>
       <c r="T68">
-        <v>2.608081757526352</v>
+        <v>2.687114538057454</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01722675320284963</v>
+        <v>0.01696963748340412</v>
       </c>
       <c r="W68">
-        <v>0.2317379315947681</v>
+        <v>0.2317985594814133</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.06890701281139855</v>
+        <v>0.06787854993361653</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2621126974902779</v>
+        <v>0.2640126974902778</v>
       </c>
       <c r="C69">
-        <v>-78.30217541416417</v>
+        <v>-82.89494661269904</v>
       </c>
       <c r="D69">
-        <v>141.9268245858358</v>
+        <v>140.691053387301</v>
       </c>
       <c r="E69">
-        <v>224.919</v>
+        <v>228.276</v>
       </c>
       <c r="F69">
-        <v>224.919</v>
+        <v>228.276</v>
       </c>
       <c r="G69">
         <v>4.69</v>
@@ -6933,37 +6933,37 @@
         <v>3.6</v>
       </c>
       <c r="M69">
-        <v>53.03590020000001</v>
+        <v>53.8274808</v>
       </c>
       <c r="N69">
-        <v>-49.43590020000001</v>
+        <v>-50.2274808</v>
       </c>
       <c r="O69">
-        <v>-12.35897505</v>
+        <v>-12.5568702</v>
       </c>
       <c r="P69">
-        <v>-37.07692515000001</v>
+        <v>-37.6706106</v>
       </c>
       <c r="Q69">
-        <v>-36.55692515</v>
+        <v>-37.1506106</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3236595837506999</v>
+        <v>0.3323426957429092</v>
       </c>
       <c r="T69">
-        <v>2.687114538057454</v>
+        <v>2.77108686737175</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01696963748340412</v>
+        <v>0.01672008399100111</v>
       </c>
       <c r="W69">
-        <v>0.2317985594814133</v>
+        <v>0.231857404194922</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.06787854993361653</v>
+        <v>0.06688033596400444</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2640126974902778</v>
+        <v>0.2659126974902778</v>
       </c>
       <c r="C70">
-        <v>-82.89494661269904</v>
+        <v>-87.4663836010408</v>
       </c>
       <c r="D70">
-        <v>140.691053387301</v>
+        <v>139.4766163989592</v>
       </c>
       <c r="E70">
-        <v>228.276</v>
+        <v>231.633</v>
       </c>
       <c r="F70">
-        <v>228.276</v>
+        <v>231.633</v>
       </c>
       <c r="G70">
         <v>4.69</v>
@@ -7015,37 +7015,37 @@
         <v>3.6</v>
       </c>
       <c r="M70">
-        <v>53.8274808</v>
+        <v>54.61906140000001</v>
       </c>
       <c r="N70">
-        <v>-50.2274808</v>
+        <v>-51.01906140000001</v>
       </c>
       <c r="O70">
-        <v>-12.5568702</v>
+        <v>-12.75476535</v>
       </c>
       <c r="P70">
-        <v>-37.6706106</v>
+        <v>-38.26429605000001</v>
       </c>
       <c r="Q70">
-        <v>-37.1506106</v>
+        <v>-37.74429605</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3323426957429092</v>
+        <v>0.3415860085088095</v>
       </c>
       <c r="T70">
-        <v>2.77108686737175</v>
+        <v>2.860476766319226</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01672008399100111</v>
+        <v>0.01647776393316052</v>
       </c>
       <c r="W70">
-        <v>0.231857404194922</v>
+        <v>0.2319145432645608</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.06688033596400444</v>
+        <v>0.06591105573264211</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2659126974902778</v>
+        <v>0.2678126974902778</v>
       </c>
       <c r="C71">
-        <v>-87.4663836010408</v>
+        <v>-92.01703411812267</v>
       </c>
       <c r="D71">
-        <v>139.4766163989592</v>
+        <v>138.2829658818773</v>
       </c>
       <c r="E71">
-        <v>231.633</v>
+        <v>234.99</v>
       </c>
       <c r="F71">
-        <v>231.633</v>
+        <v>234.99</v>
       </c>
       <c r="G71">
         <v>4.69</v>
@@ -7097,37 +7097,37 @@
         <v>3.6</v>
       </c>
       <c r="M71">
-        <v>54.61906140000001</v>
+        <v>55.410642</v>
       </c>
       <c r="N71">
-        <v>-51.01906140000001</v>
+        <v>-51.810642</v>
       </c>
       <c r="O71">
-        <v>-12.75476535</v>
+        <v>-12.9526605</v>
       </c>
       <c r="P71">
-        <v>-38.26429605000001</v>
+        <v>-38.8579815</v>
       </c>
       <c r="Q71">
-        <v>-37.74429605</v>
+        <v>-38.3379815</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3415860085088095</v>
+        <v>0.3514455421257698</v>
       </c>
       <c r="T71">
-        <v>2.860476766319226</v>
+        <v>2.955825991863199</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01647776393316052</v>
+        <v>0.01624236730554394</v>
       </c>
       <c r="W71">
-        <v>0.2319145432645608</v>
+        <v>0.2319700497893527</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.06591105573264211</v>
+        <v>0.06496946922217584</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2678126974902778</v>
+        <v>0.2697126974902779</v>
       </c>
       <c r="C72">
-        <v>-92.01703411812267</v>
+        <v>-96.54742731163276</v>
       </c>
       <c r="D72">
-        <v>138.2829658818773</v>
+        <v>137.1095726883673</v>
       </c>
       <c r="E72">
-        <v>234.99</v>
+        <v>238.347</v>
       </c>
       <c r="F72">
-        <v>234.99</v>
+        <v>238.347</v>
       </c>
       <c r="G72">
         <v>4.69</v>
@@ -7179,37 +7179,37 @@
         <v>3.6</v>
       </c>
       <c r="M72">
-        <v>55.410642</v>
+        <v>56.20222260000001</v>
       </c>
       <c r="N72">
-        <v>-51.810642</v>
+        <v>-52.6022226</v>
       </c>
       <c r="O72">
-        <v>-12.9526605</v>
+        <v>-13.15055565</v>
       </c>
       <c r="P72">
-        <v>-38.8579815</v>
+        <v>-39.45166695</v>
       </c>
       <c r="Q72">
-        <v>-38.3379815</v>
+        <v>-38.93166695</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3514455421257698</v>
+        <v>0.3619850435783826</v>
       </c>
       <c r="T72">
-        <v>2.955825991863199</v>
+        <v>3.057751026065379</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01624236730554394</v>
+        <v>0.01601360156884614</v>
       </c>
       <c r="W72">
-        <v>0.2319700497893527</v>
+        <v>0.2320239927500661</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.06496946922217584</v>
+        <v>0.06405440627538461</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2697126974902779</v>
+        <v>0.2716126974902778</v>
       </c>
       <c r="C73">
-        <v>-96.54742731163273</v>
+        <v>-101.0580745201521</v>
       </c>
       <c r="D73">
-        <v>137.1095726883673</v>
+        <v>135.9559254798478</v>
       </c>
       <c r="E73">
-        <v>238.347</v>
+        <v>241.704</v>
       </c>
       <c r="F73">
-        <v>238.347</v>
+        <v>241.704</v>
       </c>
       <c r="G73">
         <v>4.69</v>
@@ -7261,37 +7261,37 @@
         <v>3.6</v>
       </c>
       <c r="M73">
-        <v>56.2022226</v>
+        <v>56.9938032</v>
       </c>
       <c r="N73">
-        <v>-52.6022226</v>
+        <v>-53.39380319999999</v>
       </c>
       <c r="O73">
-        <v>-13.15055565</v>
+        <v>-13.3484508</v>
       </c>
       <c r="P73">
-        <v>-39.45166695</v>
+        <v>-40.0453524</v>
       </c>
       <c r="Q73">
-        <v>-38.93166694999999</v>
+        <v>-39.5253524</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3619850435783825</v>
+        <v>0.3732773665633247</v>
       </c>
       <c r="T73">
-        <v>3.057751026065378</v>
+        <v>3.166956419853427</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01601360156884614</v>
+        <v>0.0157911904359455</v>
       </c>
       <c r="W73">
-        <v>0.2320239927500661</v>
+        <v>0.2320764372952041</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.06405440627538461</v>
+        <v>0.06316476174378205</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2716126974902778</v>
+        <v>0.2735126974902778</v>
       </c>
       <c r="C74">
-        <v>-101.0580745201521</v>
+        <v>-105.5494700161378</v>
       </c>
       <c r="D74">
-        <v>135.9559254798478</v>
+        <v>134.8215299838622</v>
       </c>
       <c r="E74">
-        <v>241.704</v>
+        <v>245.061</v>
       </c>
       <c r="F74">
-        <v>241.704</v>
+        <v>245.061</v>
       </c>
       <c r="G74">
         <v>4.69</v>
@@ -7343,37 +7343,37 @@
         <v>3.6</v>
       </c>
       <c r="M74">
-        <v>56.9938032</v>
+        <v>57.7853838</v>
       </c>
       <c r="N74">
-        <v>-53.39380319999999</v>
+        <v>-54.1853838</v>
       </c>
       <c r="O74">
-        <v>-13.3484508</v>
+        <v>-13.54634595</v>
       </c>
       <c r="P74">
-        <v>-40.0453524</v>
+        <v>-40.63903784999999</v>
       </c>
       <c r="Q74">
-        <v>-39.5253524</v>
+        <v>-40.11903784999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3732773665633247</v>
+        <v>0.3854061579175219</v>
       </c>
       <c r="T74">
-        <v>3.166956419853427</v>
+        <v>3.284251102070221</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0157911904359455</v>
+        <v>0.01557487275874077</v>
       </c>
       <c r="W74">
-        <v>0.2320764372952041</v>
+        <v>0.2321274450034889</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.06316476174378205</v>
+        <v>0.06229949103496313</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2735126974902778</v>
+        <v>0.2754126974902778</v>
       </c>
       <c r="C75">
-        <v>-105.5494700161378</v>
+        <v>-110.0220917120162</v>
       </c>
       <c r="D75">
-        <v>134.8215299838622</v>
+        <v>133.7059082879837</v>
       </c>
       <c r="E75">
-        <v>245.061</v>
+        <v>248.418</v>
       </c>
       <c r="F75">
-        <v>245.061</v>
+        <v>248.418</v>
       </c>
       <c r="G75">
         <v>4.69</v>
@@ -7425,37 +7425,37 @@
         <v>3.6</v>
       </c>
       <c r="M75">
-        <v>57.7853838</v>
+        <v>58.57696439999999</v>
       </c>
       <c r="N75">
-        <v>-54.1853838</v>
+        <v>-54.97696439999999</v>
       </c>
       <c r="O75">
-        <v>-13.54634595</v>
+        <v>-13.7442411</v>
       </c>
       <c r="P75">
-        <v>-40.63903784999999</v>
+        <v>-41.2327233</v>
       </c>
       <c r="Q75">
-        <v>-40.11903784999999</v>
+        <v>-40.71272329999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3854061579175219</v>
+        <v>0.398467933222042</v>
       </c>
       <c r="T75">
-        <v>3.284251102070221</v>
+        <v>3.410568452149845</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01557487275874077</v>
+        <v>0.01536440150524427</v>
       </c>
       <c r="W75">
-        <v>0.2321274450034889</v>
+        <v>0.2321770741250634</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.06229949103496313</v>
+        <v>0.06145760602097716</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2754126974902778</v>
+        <v>0.2773126974902779</v>
       </c>
       <c r="C76">
-        <v>-110.0220917120162</v>
+        <v>-114.4764018315091</v>
       </c>
       <c r="D76">
-        <v>133.7059082879837</v>
+        <v>132.6085981684909</v>
       </c>
       <c r="E76">
-        <v>248.418</v>
+        <v>251.775</v>
       </c>
       <c r="F76">
-        <v>248.418</v>
+        <v>251.775</v>
       </c>
       <c r="G76">
         <v>4.69</v>
@@ -7507,37 +7507,37 @@
         <v>3.6</v>
       </c>
       <c r="M76">
-        <v>58.57696439999999</v>
+        <v>59.368545</v>
       </c>
       <c r="N76">
-        <v>-54.97696439999999</v>
+        <v>-55.768545</v>
       </c>
       <c r="O76">
-        <v>-13.7442411</v>
+        <v>-13.94213625</v>
       </c>
       <c r="P76">
-        <v>-41.2327233</v>
+        <v>-41.82640875</v>
       </c>
       <c r="Q76">
-        <v>-40.71272329999999</v>
+        <v>-41.30640875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.398467933222042</v>
+        <v>0.4125746505509237</v>
       </c>
       <c r="T76">
-        <v>3.410568452149845</v>
+        <v>3.546991190235839</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01536440150524427</v>
+        <v>0.01515954281850768</v>
       </c>
       <c r="W76">
-        <v>0.2321770741250634</v>
+        <v>0.2322253798033959</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.06145760602097716</v>
+        <v>0.06063817127403071</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2773126974902779</v>
+        <v>0.2792126974902779</v>
       </c>
       <c r="C77">
-        <v>-114.4764018315091</v>
+        <v>-118.91284754817</v>
       </c>
       <c r="D77">
-        <v>132.6085981684909</v>
+        <v>131.52915245183</v>
       </c>
       <c r="E77">
-        <v>251.775</v>
+        <v>255.132</v>
       </c>
       <c r="F77">
-        <v>251.775</v>
+        <v>255.132</v>
       </c>
       <c r="G77">
         <v>4.69</v>
@@ -7589,37 +7589,37 @@
         <v>3.6</v>
       </c>
       <c r="M77">
-        <v>59.368545</v>
+        <v>60.1601256</v>
       </c>
       <c r="N77">
-        <v>-55.768545</v>
+        <v>-56.5601256</v>
       </c>
       <c r="O77">
-        <v>-13.94213625</v>
+        <v>-14.1400314</v>
       </c>
       <c r="P77">
-        <v>-41.82640875</v>
+        <v>-42.4200942</v>
       </c>
       <c r="Q77">
-        <v>-41.30640875</v>
+        <v>-41.9000942</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4125746505509237</v>
+        <v>0.4278569276572123</v>
       </c>
       <c r="T77">
-        <v>3.546991190235839</v>
+        <v>3.694782489829</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01515954281850768</v>
+        <v>0.0149600751498431</v>
       </c>
       <c r="W77">
-        <v>0.2322253798033959</v>
+        <v>0.232272414279667</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.06063817127403071</v>
+        <v>0.0598403005993724</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2792126974902779</v>
+        <v>0.2811126974902778</v>
       </c>
       <c r="C78">
-        <v>-118.91284754817</v>
+        <v>-123.3318615929871</v>
       </c>
       <c r="D78">
-        <v>131.52915245183</v>
+        <v>130.4671384070129</v>
       </c>
       <c r="E78">
-        <v>255.132</v>
+        <v>258.489</v>
       </c>
       <c r="F78">
-        <v>255.132</v>
+        <v>258.489</v>
       </c>
       <c r="G78">
         <v>4.69</v>
@@ -7671,37 +7671,37 @@
         <v>3.6</v>
       </c>
       <c r="M78">
-        <v>60.1601256</v>
+        <v>60.9517062</v>
       </c>
       <c r="N78">
-        <v>-56.5601256</v>
+        <v>-57.3517062</v>
       </c>
       <c r="O78">
-        <v>-14.1400314</v>
+        <v>-14.33792655</v>
       </c>
       <c r="P78">
-        <v>-42.4200942</v>
+        <v>-43.01377965</v>
       </c>
       <c r="Q78">
-        <v>-41.9000942</v>
+        <v>-42.49377964999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4278569276572123</v>
+        <v>0.4444680984249171</v>
       </c>
       <c r="T78">
-        <v>3.694782489829</v>
+        <v>3.855425206778086</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0149600751498431</v>
+        <v>0.0147657884595854</v>
       </c>
       <c r="W78">
-        <v>0.232272414279667</v>
+        <v>0.2323182270812298</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.0598403005993724</v>
+        <v>0.0590631538383416</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2811126974902778</v>
+        <v>0.2830126974902779</v>
       </c>
       <c r="C79">
-        <v>-123.3318615929871</v>
+        <v>-127.7338628327858</v>
       </c>
       <c r="D79">
-        <v>130.4671384070129</v>
+        <v>129.4221371672142</v>
       </c>
       <c r="E79">
-        <v>258.489</v>
+        <v>261.846</v>
       </c>
       <c r="F79">
-        <v>258.489</v>
+        <v>261.846</v>
       </c>
       <c r="G79">
         <v>4.69</v>
@@ -7753,37 +7753,37 @@
         <v>3.6</v>
       </c>
       <c r="M79">
-        <v>60.9517062</v>
+        <v>61.7432868</v>
       </c>
       <c r="N79">
-        <v>-57.3517062</v>
+        <v>-58.1432868</v>
       </c>
       <c r="O79">
-        <v>-14.33792655</v>
+        <v>-14.5358217</v>
       </c>
       <c r="P79">
-        <v>-43.01377965</v>
+        <v>-43.6074651</v>
       </c>
       <c r="Q79">
-        <v>-42.49377964999999</v>
+        <v>-43.0874651</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4444680984249171</v>
+        <v>0.4625893756260498</v>
       </c>
       <c r="T79">
-        <v>3.855425206778086</v>
+        <v>4.030671807086182</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0147657884595854</v>
+        <v>0.01457648347933431</v>
       </c>
       <c r="W79">
-        <v>0.2323182270812298</v>
+        <v>0.232362865195573</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0590631538383416</v>
+        <v>0.05830593391733729</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2830126974902779</v>
+        <v>0.2849126974902778</v>
       </c>
       <c r="C80">
-        <v>-127.7338628327858</v>
+        <v>-132.1192568210544</v>
       </c>
       <c r="D80">
-        <v>129.4221371672142</v>
+        <v>128.3937431789456</v>
       </c>
       <c r="E80">
-        <v>261.846</v>
+        <v>265.203</v>
       </c>
       <c r="F80">
-        <v>261.846</v>
+        <v>265.203</v>
       </c>
       <c r="G80">
         <v>4.69</v>
@@ -7835,37 +7835,37 @@
         <v>3.6</v>
       </c>
       <c r="M80">
-        <v>61.7432868</v>
+        <v>62.5348674</v>
       </c>
       <c r="N80">
-        <v>-58.1432868</v>
+        <v>-58.93486739999999</v>
       </c>
       <c r="O80">
-        <v>-14.5358217</v>
+        <v>-14.73371685</v>
       </c>
       <c r="P80">
-        <v>-43.6074651</v>
+        <v>-44.20115054999999</v>
       </c>
       <c r="Q80">
-        <v>-43.0874651</v>
+        <v>-43.68115054999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4625893756260498</v>
+        <v>0.4824364887510997</v>
       </c>
       <c r="T80">
-        <v>4.030671807086182</v>
+        <v>4.222608559804571</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01457648347933431</v>
+        <v>0.01439197103022881</v>
       </c>
       <c r="W80">
-        <v>0.232362865195573</v>
+        <v>0.232406373231072</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05830593391733729</v>
+        <v>0.05756788412091529</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2849126974902778</v>
+        <v>0.2868126974902778</v>
       </c>
       <c r="C81">
-        <v>-132.1192568210544</v>
+        <v>-136.4884363227167</v>
       </c>
       <c r="D81">
-        <v>128.3937431789456</v>
+        <v>127.3815636772833</v>
       </c>
       <c r="E81">
-        <v>265.203</v>
+        <v>268.56</v>
       </c>
       <c r="F81">
-        <v>265.203</v>
+        <v>268.56</v>
       </c>
       <c r="G81">
         <v>4.69</v>
@@ -7917,37 +7917,37 @@
         <v>3.6</v>
       </c>
       <c r="M81">
-        <v>62.5348674</v>
+        <v>63.32644800000001</v>
       </c>
       <c r="N81">
-        <v>-58.93486739999999</v>
+        <v>-59.726448</v>
       </c>
       <c r="O81">
-        <v>-14.73371685</v>
+        <v>-14.931612</v>
       </c>
       <c r="P81">
-        <v>-44.20115054999999</v>
+        <v>-44.794836</v>
       </c>
       <c r="Q81">
-        <v>-43.68115054999999</v>
+        <v>-44.274836</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4824364887510997</v>
+        <v>0.5042683131886546</v>
       </c>
       <c r="T81">
-        <v>4.222608559804571</v>
+        <v>4.433738987794799</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01439197103022881</v>
+        <v>0.01421207139235095</v>
       </c>
       <c r="W81">
-        <v>0.232406373231072</v>
+        <v>0.2324487935656837</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05756788412091529</v>
+        <v>0.0568482855694038</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2868126974902778</v>
+        <v>0.2887126974902778</v>
       </c>
       <c r="C82">
-        <v>-136.4884363227167</v>
+        <v>-140.8417818142756</v>
       </c>
       <c r="D82">
-        <v>127.3815636772833</v>
+        <v>126.3852181857244</v>
       </c>
       <c r="E82">
-        <v>268.56</v>
+        <v>271.917</v>
       </c>
       <c r="F82">
-        <v>268.56</v>
+        <v>271.917</v>
       </c>
       <c r="G82">
         <v>4.69</v>
@@ -7999,37 +7999,37 @@
         <v>3.6</v>
       </c>
       <c r="M82">
-        <v>63.32644800000001</v>
+        <v>64.11802860000002</v>
       </c>
       <c r="N82">
-        <v>-59.726448</v>
+        <v>-60.51802860000002</v>
       </c>
       <c r="O82">
-        <v>-14.931612</v>
+        <v>-15.12950715</v>
       </c>
       <c r="P82">
-        <v>-44.794836</v>
+        <v>-45.38852145000001</v>
       </c>
       <c r="Q82">
-        <v>-44.274836</v>
+        <v>-44.86852145000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5042683131886546</v>
+        <v>0.5283982244091102</v>
       </c>
       <c r="T82">
-        <v>4.433738987794799</v>
+        <v>4.667093671362947</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01421207139235095</v>
+        <v>0.01403661372084044</v>
       </c>
       <c r="W82">
-        <v>0.2324487935656837</v>
+        <v>0.2324901664846258</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0568482855694038</v>
+        <v>0.05614645488336178</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2887126974902778</v>
+        <v>0.2906126974902778</v>
       </c>
       <c r="C83">
-        <v>-140.8417818142756</v>
+        <v>-145.1796619606675</v>
       </c>
       <c r="D83">
-        <v>126.3852181857244</v>
+        <v>125.4043380393324</v>
       </c>
       <c r="E83">
-        <v>271.917</v>
+        <v>275.274</v>
       </c>
       <c r="F83">
-        <v>271.917</v>
+        <v>275.274</v>
       </c>
       <c r="G83">
         <v>4.69</v>
@@ -8081,37 +8081,37 @@
         <v>3.6</v>
       </c>
       <c r="M83">
-        <v>64.11802860000002</v>
+        <v>64.90960920000001</v>
       </c>
       <c r="N83">
-        <v>-60.51802860000002</v>
+        <v>-61.3096092</v>
       </c>
       <c r="O83">
-        <v>-15.12950715</v>
+        <v>-15.3274023</v>
       </c>
       <c r="P83">
-        <v>-45.38852145000001</v>
+        <v>-45.9822069</v>
       </c>
       <c r="Q83">
-        <v>-44.86852145000001</v>
+        <v>-45.4622069</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5283982244091102</v>
+        <v>0.555209236876283</v>
       </c>
       <c r="T83">
-        <v>4.667093671362947</v>
+        <v>4.926376653105333</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01403661372084044</v>
+        <v>0.01386543550473263</v>
       </c>
       <c r="W83">
-        <v>0.2324901664846258</v>
+        <v>0.2325305303079841</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05614645488336178</v>
+        <v>0.0554617420189305</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2906126974902778</v>
+        <v>0.2925126974902779</v>
       </c>
       <c r="C84">
-        <v>-145.1796619606675</v>
+        <v>-149.5024340700829</v>
       </c>
       <c r="D84">
-        <v>125.4043380393324</v>
+        <v>124.4385659299171</v>
       </c>
       <c r="E84">
-        <v>275.274</v>
+        <v>278.631</v>
       </c>
       <c r="F84">
-        <v>275.274</v>
+        <v>278.631</v>
       </c>
       <c r="G84">
         <v>4.69</v>
@@ -8163,37 +8163,37 @@
         <v>3.6</v>
       </c>
       <c r="M84">
-        <v>64.90960920000001</v>
+        <v>65.70118980000001</v>
       </c>
       <c r="N84">
-        <v>-61.3096092</v>
+        <v>-62.10118980000001</v>
       </c>
       <c r="O84">
-        <v>-15.3274023</v>
+        <v>-15.52529745</v>
       </c>
       <c r="P84">
-        <v>-45.9822069</v>
+        <v>-46.57589235</v>
       </c>
       <c r="Q84">
-        <v>-45.4622069</v>
+        <v>-46.05589235</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.555209236876283</v>
+        <v>0.5851744861042997</v>
       </c>
       <c r="T84">
-        <v>4.926376653105333</v>
+        <v>5.216163515052706</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01386543550473263</v>
+        <v>0.01369838206491658</v>
       </c>
       <c r="W84">
-        <v>0.2325305303079841</v>
+        <v>0.2325699215090927</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.0554617420189305</v>
+        <v>0.05479352825966632</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2925126974902779</v>
+        <v>0.2944126974902779</v>
       </c>
       <c r="C85">
-        <v>-149.5024340700829</v>
+        <v>-153.81044452793</v>
       </c>
       <c r="D85">
-        <v>124.4385659299171</v>
+        <v>123.48755547207</v>
       </c>
       <c r="E85">
-        <v>278.631</v>
+        <v>281.988</v>
       </c>
       <c r="F85">
-        <v>278.631</v>
+        <v>281.988</v>
       </c>
       <c r="G85">
         <v>4.69</v>
@@ -8245,37 +8245,37 @@
         <v>3.6</v>
       </c>
       <c r="M85">
-        <v>65.70118980000001</v>
+        <v>66.4927704</v>
       </c>
       <c r="N85">
-        <v>-62.10118980000001</v>
+        <v>-62.8927704</v>
       </c>
       <c r="O85">
-        <v>-15.52529745</v>
+        <v>-15.7231926</v>
       </c>
       <c r="P85">
-        <v>-46.57589235</v>
+        <v>-47.1695778</v>
       </c>
       <c r="Q85">
-        <v>-46.05589235</v>
+        <v>-46.6495778</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5851744861042997</v>
+        <v>0.6188853914858186</v>
       </c>
       <c r="T85">
-        <v>5.216163515052706</v>
+        <v>5.542173734743502</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01369838206491658</v>
+        <v>0.01353530608795329</v>
       </c>
       <c r="W85">
-        <v>0.2325699215090927</v>
+        <v>0.2326083748244606</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05479352825966632</v>
+        <v>0.05414122435181312</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2944126974902779</v>
+        <v>0.2963126974902778</v>
       </c>
       <c r="C86">
-        <v>-153.81044452793</v>
+        <v>-158.1040292110519</v>
       </c>
       <c r="D86">
-        <v>123.48755547207</v>
+        <v>122.5509707889481</v>
       </c>
       <c r="E86">
-        <v>281.988</v>
+        <v>285.345</v>
       </c>
       <c r="F86">
-        <v>281.988</v>
+        <v>285.345</v>
       </c>
       <c r="G86">
         <v>4.69</v>
@@ -8327,37 +8327,37 @@
         <v>3.6</v>
       </c>
       <c r="M86">
-        <v>66.4927704</v>
+        <v>67.284351</v>
       </c>
       <c r="N86">
-        <v>-62.8927704</v>
+        <v>-63.684351</v>
       </c>
       <c r="O86">
-        <v>-15.7231926</v>
+        <v>-15.92108775</v>
       </c>
       <c r="P86">
-        <v>-47.1695778</v>
+        <v>-47.76326325</v>
       </c>
       <c r="Q86">
-        <v>-46.6495778</v>
+        <v>-47.24326325</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6188853914858182</v>
+        <v>0.6570910842515394</v>
       </c>
       <c r="T86">
-        <v>5.542173734743498</v>
+        <v>5.911651983726397</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01353530608795329</v>
+        <v>0.01337606719280089</v>
       </c>
       <c r="W86">
-        <v>0.2326083748244606</v>
+        <v>0.2326459233559376</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.05414122435181312</v>
+        <v>0.05350426877120362</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2963126974902778</v>
+        <v>0.2982126974902778</v>
       </c>
       <c r="C87">
-        <v>-158.1040292110519</v>
+        <v>-162.3835138832343</v>
       </c>
       <c r="D87">
-        <v>122.5509707889481</v>
+        <v>121.6284861167657</v>
       </c>
       <c r="E87">
-        <v>285.345</v>
+        <v>288.702</v>
       </c>
       <c r="F87">
-        <v>285.345</v>
+        <v>288.702</v>
       </c>
       <c r="G87">
         <v>4.69</v>
@@ -8409,37 +8409,37 @@
         <v>3.6</v>
       </c>
       <c r="M87">
-        <v>67.284351</v>
+        <v>68.0759316</v>
       </c>
       <c r="N87">
-        <v>-63.684351</v>
+        <v>-64.47593160000001</v>
       </c>
       <c r="O87">
-        <v>-15.92108775</v>
+        <v>-16.1189829</v>
       </c>
       <c r="P87">
-        <v>-47.76326325</v>
+        <v>-48.3569487</v>
       </c>
       <c r="Q87">
-        <v>-47.24326325</v>
+        <v>-47.8369487</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6570910842515394</v>
+        <v>0.7007547331266494</v>
       </c>
       <c r="T87">
-        <v>5.911651983726397</v>
+        <v>6.333912839706855</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01337606719280089</v>
+        <v>0.01322053152776832</v>
       </c>
       <c r="W87">
-        <v>0.2326459233559376</v>
+        <v>0.2326825986657522</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.05350426877120362</v>
+        <v>0.05288212611107324</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2982126974902778</v>
+        <v>0.3001126974902778</v>
       </c>
       <c r="C88">
-        <v>-162.3835138832343</v>
+        <v>-166.6492145729853</v>
       </c>
       <c r="D88">
-        <v>121.6284861167657</v>
+        <v>120.7197854270147</v>
       </c>
       <c r="E88">
-        <v>288.702</v>
+        <v>292.059</v>
       </c>
       <c r="F88">
-        <v>288.702</v>
+        <v>292.059</v>
       </c>
       <c r="G88">
         <v>4.69</v>
@@ -8491,37 +8491,37 @@
         <v>3.6</v>
       </c>
       <c r="M88">
-        <v>68.0759316</v>
+        <v>68.86751219999999</v>
       </c>
       <c r="N88">
-        <v>-64.47593160000001</v>
+        <v>-65.2675122</v>
       </c>
       <c r="O88">
-        <v>-16.1189829</v>
+        <v>-16.31687805</v>
       </c>
       <c r="P88">
-        <v>-48.3569487</v>
+        <v>-48.95063415</v>
       </c>
       <c r="Q88">
-        <v>-47.8369487</v>
+        <v>-48.43063415</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7007547331266494</v>
+        <v>0.7511358664440839</v>
       </c>
       <c r="T88">
-        <v>6.333912839706855</v>
+        <v>6.821136904299689</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01322053152776832</v>
+        <v>0.01306857139526524</v>
       </c>
       <c r="W88">
-        <v>0.2326825986657522</v>
+        <v>0.2327184308649964</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.05288212611107324</v>
+        <v>0.05227428558106084</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3001126974902778</v>
+        <v>0.3020126974902778</v>
       </c>
       <c r="C89">
-        <v>-166.6492145729853</v>
+        <v>-170.9014379345052</v>
       </c>
       <c r="D89">
-        <v>120.7197854270147</v>
+        <v>119.8245620654948</v>
       </c>
       <c r="E89">
-        <v>292.059</v>
+        <v>295.416</v>
       </c>
       <c r="F89">
-        <v>292.059</v>
+        <v>295.416</v>
       </c>
       <c r="G89">
         <v>4.69</v>
@@ -8573,37 +8573,37 @@
         <v>3.6</v>
       </c>
       <c r="M89">
-        <v>68.86751219999999</v>
+        <v>69.6590928</v>
       </c>
       <c r="N89">
-        <v>-65.2675122</v>
+        <v>-66.0590928</v>
       </c>
       <c r="O89">
-        <v>-16.31687805</v>
+        <v>-16.5147732</v>
       </c>
       <c r="P89">
-        <v>-48.95063415</v>
+        <v>-49.5443196</v>
       </c>
       <c r="Q89">
-        <v>-48.43063415</v>
+        <v>-49.0243196</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7511358664440839</v>
+        <v>0.8099138553144245</v>
       </c>
       <c r="T89">
-        <v>6.821136904299689</v>
+        <v>7.389564979657999</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01306857139526524</v>
+        <v>0.01292006490213723</v>
       </c>
       <c r="W89">
-        <v>0.2327184308649964</v>
+        <v>0.232753448696076</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05227428558106084</v>
+        <v>0.05168025960854883</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3020126974902778</v>
+        <v>0.3039126974902778</v>
       </c>
       <c r="C90">
-        <v>-170.9014379345052</v>
+        <v>-175.1404815927139</v>
       </c>
       <c r="D90">
-        <v>119.8245620654948</v>
+        <v>118.9425184072861</v>
       </c>
       <c r="E90">
-        <v>295.416</v>
+        <v>298.773</v>
       </c>
       <c r="F90">
-        <v>295.416</v>
+        <v>298.773</v>
       </c>
       <c r="G90">
         <v>4.69</v>
@@ -8655,37 +8655,37 @@
         <v>3.6</v>
       </c>
       <c r="M90">
-        <v>69.6590928</v>
+        <v>70.4506734</v>
       </c>
       <c r="N90">
-        <v>-66.0590928</v>
+        <v>-66.85067340000001</v>
       </c>
       <c r="O90">
-        <v>-16.5147732</v>
+        <v>-16.71266835</v>
       </c>
       <c r="P90">
-        <v>-49.5443196</v>
+        <v>-50.13800505</v>
       </c>
       <c r="Q90">
-        <v>-49.0243196</v>
+        <v>-49.61800505</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8099138553144245</v>
+        <v>0.8793787512520993</v>
       </c>
       <c r="T90">
-        <v>7.389564979657999</v>
+        <v>8.061343614172362</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01292006490213723</v>
+        <v>0.01277489563357389</v>
       </c>
       <c r="W90">
-        <v>0.232753448696076</v>
+        <v>0.2327876796096033</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.05168025960854883</v>
+        <v>0.05109958253429547</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3039126974902778</v>
+        <v>0.3058126974902778</v>
       </c>
       <c r="C91">
-        <v>-175.1404815927139</v>
+        <v>-179.3666344731508</v>
       </c>
       <c r="D91">
-        <v>118.9425184072861</v>
+        <v>118.0733655268492</v>
       </c>
       <c r="E91">
-        <v>298.773</v>
+        <v>302.13</v>
       </c>
       <c r="F91">
-        <v>298.773</v>
+        <v>302.13</v>
       </c>
       <c r="G91">
         <v>4.69</v>
@@ -8737,37 +8737,37 @@
         <v>3.6</v>
       </c>
       <c r="M91">
-        <v>70.4506734</v>
+        <v>71.242254</v>
       </c>
       <c r="N91">
-        <v>-66.85067340000001</v>
+        <v>-67.64225400000001</v>
       </c>
       <c r="O91">
-        <v>-16.71266835</v>
+        <v>-16.9105635</v>
       </c>
       <c r="P91">
-        <v>-50.13800505</v>
+        <v>-50.73169050000001</v>
       </c>
       <c r="Q91">
-        <v>-49.61800505</v>
+        <v>-50.2116905</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8793787512520993</v>
+        <v>0.9627366263773093</v>
       </c>
       <c r="T91">
-        <v>8.061343614172362</v>
+        <v>8.867477975589598</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01277489563357389</v>
+        <v>0.0126329523487564</v>
       </c>
       <c r="W91">
-        <v>0.2327876796096033</v>
+        <v>0.2328211498361633</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05109958253429547</v>
+        <v>0.05053180939502555</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3058126974902778</v>
+        <v>0.3077126974902779</v>
       </c>
       <c r="C92">
-        <v>-179.3666344731508</v>
+        <v>-183.5801771175155</v>
       </c>
       <c r="D92">
-        <v>118.0733655268492</v>
+        <v>117.2168228824845</v>
       </c>
       <c r="E92">
-        <v>302.13</v>
+        <v>305.487</v>
       </c>
       <c r="F92">
-        <v>302.13</v>
+        <v>305.487</v>
       </c>
       <c r="G92">
         <v>4.69</v>
@@ -8819,37 +8819,37 @@
         <v>3.6</v>
       </c>
       <c r="M92">
-        <v>71.242254</v>
+        <v>72.03383460000001</v>
       </c>
       <c r="N92">
-        <v>-67.64225400000001</v>
+        <v>-68.43383460000001</v>
       </c>
       <c r="O92">
-        <v>-16.9105635</v>
+        <v>-17.10845865</v>
       </c>
       <c r="P92">
-        <v>-50.73169050000001</v>
+        <v>-51.32537595000001</v>
       </c>
       <c r="Q92">
-        <v>-50.2116905</v>
+        <v>-50.80537595000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9627366263773093</v>
+        <v>1.064618473752566</v>
       </c>
       <c r="T92">
-        <v>8.867477975589598</v>
+        <v>9.852753306210666</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0126329523487564</v>
+        <v>0.01249412869657226</v>
       </c>
       <c r="W92">
-        <v>0.2328211498361633</v>
+        <v>0.2328538844533483</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.05053180939502555</v>
+        <v>0.04997651478628895</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3077126974902779</v>
+        <v>0.3096126974902779</v>
       </c>
       <c r="C93">
-        <v>-183.5801771175155</v>
+        <v>-187.7813819855732</v>
       </c>
       <c r="D93">
-        <v>117.2168228824845</v>
+        <v>116.3726180144268</v>
       </c>
       <c r="E93">
-        <v>305.487</v>
+        <v>308.844</v>
       </c>
       <c r="F93">
-        <v>305.487</v>
+        <v>308.844</v>
       </c>
       <c r="G93">
         <v>4.69</v>
@@ -8901,37 +8901,37 @@
         <v>3.6</v>
       </c>
       <c r="M93">
-        <v>72.03383460000001</v>
+        <v>72.82541519999999</v>
       </c>
       <c r="N93">
-        <v>-68.43383460000001</v>
+        <v>-69.2254152</v>
       </c>
       <c r="O93">
-        <v>-17.10845865</v>
+        <v>-17.3063538</v>
       </c>
       <c r="P93">
-        <v>-51.32537595000001</v>
+        <v>-51.9190614</v>
       </c>
       <c r="Q93">
-        <v>-50.80537595000001</v>
+        <v>-51.3990614</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.064618473752566</v>
+        <v>1.191970782971637</v>
       </c>
       <c r="T93">
-        <v>9.852753306210666</v>
+        <v>11.084347469487</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01249412869657226</v>
+        <v>0.01235832294987039</v>
       </c>
       <c r="W93">
-        <v>0.2328538844533483</v>
+        <v>0.2328859074484206</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04997651478628895</v>
+        <v>0.04943329179948153</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3096126974902779</v>
+        <v>0.3115126974902779</v>
       </c>
       <c r="C94">
-        <v>-187.7813819855732</v>
+        <v>-191.9705137441073</v>
       </c>
       <c r="D94">
-        <v>116.3726180144268</v>
+        <v>115.5404862558927</v>
       </c>
       <c r="E94">
-        <v>308.844</v>
+        <v>312.201</v>
       </c>
       <c r="F94">
-        <v>308.844</v>
+        <v>312.201</v>
       </c>
       <c r="G94">
         <v>4.69</v>
@@ -8983,37 +8983,37 @@
         <v>3.6</v>
       </c>
       <c r="M94">
-        <v>72.82541519999999</v>
+        <v>73.61699580000001</v>
       </c>
       <c r="N94">
-        <v>-69.2254152</v>
+        <v>-70.01699580000002</v>
       </c>
       <c r="O94">
-        <v>-17.3063538</v>
+        <v>-17.50424895</v>
       </c>
       <c r="P94">
-        <v>-51.9190614</v>
+        <v>-52.51274685000001</v>
       </c>
       <c r="Q94">
-        <v>-51.3990614</v>
+        <v>-51.99274685000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.191970782971637</v>
+        <v>1.3557094662533</v>
       </c>
       <c r="T94">
-        <v>11.084347469487</v>
+        <v>12.66782567941372</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01235832294987039</v>
+        <v>0.01222543775686103</v>
       </c>
       <c r="W94">
-        <v>0.2328859074484206</v>
+        <v>0.2329172417769322</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04943329179948153</v>
+        <v>0.0489017510274441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3115126974902779</v>
+        <v>0.3134126974902778</v>
       </c>
       <c r="C95">
-        <v>-191.9705137441073</v>
+        <v>-196.1478295435628</v>
       </c>
       <c r="D95">
-        <v>115.5404862558927</v>
+        <v>114.7201704564372</v>
       </c>
       <c r="E95">
-        <v>312.201</v>
+        <v>315.558</v>
       </c>
       <c r="F95">
-        <v>312.201</v>
+        <v>315.558</v>
       </c>
       <c r="G95">
         <v>4.69</v>
@@ -9065,37 +9065,37 @@
         <v>3.6</v>
       </c>
       <c r="M95">
-        <v>73.61699580000001</v>
+        <v>74.4085764</v>
       </c>
       <c r="N95">
-        <v>-70.01699580000002</v>
+        <v>-70.80857640000001</v>
       </c>
       <c r="O95">
-        <v>-17.50424895</v>
+        <v>-17.7021441</v>
       </c>
       <c r="P95">
-        <v>-52.51274685000001</v>
+        <v>-53.10643230000001</v>
       </c>
       <c r="Q95">
-        <v>-51.99274685000001</v>
+        <v>-52.58643230000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.3557094662533</v>
+        <v>1.57402771062885</v>
       </c>
       <c r="T95">
-        <v>12.66782567941372</v>
+        <v>14.77912995931601</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01222543775686103</v>
+        <v>0.01209537990838379</v>
       </c>
       <c r="W95">
-        <v>0.2329172417769322</v>
+        <v>0.2329479094176031</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.0489017510274441</v>
+        <v>0.0483815196335351</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3134126974902778</v>
+        <v>0.3153126974902778</v>
       </c>
       <c r="C96">
-        <v>-196.1478295435628</v>
+        <v>-200.3135792829887</v>
       </c>
       <c r="D96">
-        <v>114.7201704564372</v>
+        <v>113.9114207170113</v>
       </c>
       <c r="E96">
-        <v>315.558</v>
+        <v>318.915</v>
       </c>
       <c r="F96">
-        <v>315.558</v>
+        <v>318.915</v>
       </c>
       <c r="G96">
         <v>4.69</v>
@@ -9147,37 +9147,37 @@
         <v>3.6</v>
       </c>
       <c r="M96">
-        <v>74.4085764</v>
+        <v>75.200157</v>
       </c>
       <c r="N96">
-        <v>-70.80857640000001</v>
+        <v>-71.60015700000001</v>
       </c>
       <c r="O96">
-        <v>-17.7021441</v>
+        <v>-17.90003925</v>
       </c>
       <c r="P96">
-        <v>-53.10643230000001</v>
+        <v>-53.70011775</v>
       </c>
       <c r="Q96">
-        <v>-52.58643230000001</v>
+        <v>-53.18011775</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.57402771062885</v>
+        <v>1.879673252754621</v>
       </c>
       <c r="T96">
-        <v>14.77912995931601</v>
+        <v>17.73495595117922</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01209537990838379</v>
+        <v>0.01196806011987448</v>
       </c>
       <c r="W96">
-        <v>0.2329479094176031</v>
+        <v>0.2329779314237336</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0483815196335351</v>
+        <v>0.0478722404794979</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3153126974902778</v>
+        <v>0.3172126974902779</v>
       </c>
       <c r="C97">
-        <v>-200.3135792829887</v>
+        <v>-204.4680058638511</v>
       </c>
       <c r="D97">
-        <v>113.9114207170113</v>
+        <v>113.1139941361489</v>
       </c>
       <c r="E97">
-        <v>318.915</v>
+        <v>322.272</v>
       </c>
       <c r="F97">
-        <v>318.915</v>
+        <v>322.272</v>
       </c>
       <c r="G97">
         <v>4.69</v>
@@ -9229,37 +9229,37 @@
         <v>3.6</v>
       </c>
       <c r="M97">
-        <v>75.200157</v>
+        <v>75.99173760000001</v>
       </c>
       <c r="N97">
-        <v>-71.60015700000001</v>
+        <v>-72.39173760000001</v>
       </c>
       <c r="O97">
-        <v>-17.90003925</v>
+        <v>-18.0979344</v>
       </c>
       <c r="P97">
-        <v>-53.70011775</v>
+        <v>-54.29380320000001</v>
       </c>
       <c r="Q97">
-        <v>-53.18011775</v>
+        <v>-53.77380320000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.879673252754621</v>
+        <v>2.338141565943277</v>
       </c>
       <c r="T97">
-        <v>17.73495595117922</v>
+        <v>22.16869493897403</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01196806011987448</v>
+        <v>0.01184339282695912</v>
       </c>
       <c r="W97">
-        <v>0.2329779314237336</v>
+        <v>0.2330073279714031</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0478722404794979</v>
+        <v>0.04737357130783637</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3172126974902779</v>
+        <v>0.3191126974902779</v>
       </c>
       <c r="C98">
-        <v>-204.4680058638511</v>
+        <v>-208.6113454332607</v>
       </c>
       <c r="D98">
-        <v>113.1139941361489</v>
+        <v>112.3276545667393</v>
       </c>
       <c r="E98">
-        <v>322.272</v>
+        <v>325.629</v>
       </c>
       <c r="F98">
-        <v>322.272</v>
+        <v>325.629</v>
       </c>
       <c r="G98">
         <v>4.69</v>
@@ -9311,37 +9311,37 @@
         <v>3.6</v>
       </c>
       <c r="M98">
-        <v>75.99173760000001</v>
+        <v>76.7833182</v>
       </c>
       <c r="N98">
-        <v>-72.39173760000001</v>
+        <v>-73.1833182</v>
       </c>
       <c r="O98">
-        <v>-18.0979344</v>
+        <v>-18.29582955</v>
       </c>
       <c r="P98">
-        <v>-54.29380320000001</v>
+        <v>-54.88748865</v>
       </c>
       <c r="Q98">
-        <v>-53.77380320000001</v>
+        <v>-54.36748865</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.338141565943271</v>
+        <v>3.102255421257695</v>
       </c>
       <c r="T98">
-        <v>22.16869493897397</v>
+        <v>29.55825991863197</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01184339282695912</v>
+        <v>0.01172129599369151</v>
       </c>
       <c r="W98">
-        <v>0.2330073279714031</v>
+        <v>0.2330361184046875</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04737357130783637</v>
+        <v>0.04688518397476593</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3191126974902779</v>
+        <v>0.3210126974902778</v>
       </c>
       <c r="C99">
-        <v>-208.6113454332607</v>
+        <v>-212.7438276171245</v>
       </c>
       <c r="D99">
-        <v>112.3276545667393</v>
+        <v>111.5521723828755</v>
       </c>
       <c r="E99">
-        <v>325.629</v>
+        <v>328.986</v>
       </c>
       <c r="F99">
-        <v>325.629</v>
+        <v>328.986</v>
       </c>
       <c r="G99">
         <v>4.69</v>
@@ -9393,37 +9393,37 @@
         <v>3.6</v>
       </c>
       <c r="M99">
-        <v>76.7833182</v>
+        <v>77.5748988</v>
       </c>
       <c r="N99">
-        <v>-73.1833182</v>
+        <v>-73.97489880000001</v>
       </c>
       <c r="O99">
-        <v>-18.29582955</v>
+        <v>-18.4937247</v>
       </c>
       <c r="P99">
-        <v>-54.88748865</v>
+        <v>-55.4811741</v>
       </c>
       <c r="Q99">
-        <v>-54.36748865</v>
+        <v>-54.9611741</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.102255421257695</v>
+        <v>4.630483131886542</v>
       </c>
       <c r="T99">
-        <v>29.55825991863197</v>
+        <v>44.33738987794795</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01172129599369151</v>
+        <v>0.01160169093253139</v>
       </c>
       <c r="W99">
-        <v>0.2330361184046875</v>
+        <v>0.2330643212781091</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04688518397476593</v>
+        <v>0.04640676373012542</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3210126974902778</v>
+        <v>0.3229126974902778</v>
       </c>
       <c r="C100">
-        <v>-212.7438276171245</v>
+        <v>-216.8656757437063</v>
       </c>
       <c r="D100">
-        <v>111.5521723828755</v>
+        <v>110.7873242562937</v>
       </c>
       <c r="E100">
-        <v>328.986</v>
+        <v>332.343</v>
       </c>
       <c r="F100">
-        <v>328.986</v>
+        <v>332.343</v>
       </c>
       <c r="G100">
         <v>4.69</v>
@@ -9475,37 +9475,37 @@
         <v>3.6</v>
       </c>
       <c r="M100">
-        <v>77.5748988</v>
+        <v>78.36647939999999</v>
       </c>
       <c r="N100">
-        <v>-73.97489880000001</v>
+        <v>-74.76647939999999</v>
       </c>
       <c r="O100">
-        <v>-18.4937247</v>
+        <v>-18.69161985</v>
       </c>
       <c r="P100">
-        <v>-55.4811741</v>
+        <v>-56.07485955</v>
       </c>
       <c r="Q100">
-        <v>-54.9611741</v>
+        <v>-55.55485955</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.630483131886542</v>
+        <v>9.215166263773085</v>
       </c>
       <c r="T100">
-        <v>44.33738987794795</v>
+        <v>88.6747797558959</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01160169093253139</v>
+        <v>0.01148450213523309</v>
       </c>
       <c r="W100">
-        <v>0.2330643212781091</v>
+        <v>0.233091954396512</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04640676373012542</v>
+        <v>0.04593800854093233</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3229126974902778</v>
-      </c>
-      <c r="C101">
-        <v>-216.8656757437063</v>
-      </c>
-      <c r="D101">
-        <v>110.7873242562937</v>
-      </c>
-      <c r="E101">
-        <v>332.343</v>
-      </c>
-      <c r="F101">
-        <v>332.343</v>
-      </c>
-      <c r="G101">
-        <v>4.69</v>
-      </c>
-      <c r="H101">
-        <v>335.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.12</v>
-      </c>
-      <c r="K101">
-        <v>0.52</v>
-      </c>
-      <c r="L101">
-        <v>3.6</v>
-      </c>
-      <c r="M101">
-        <v>78.36647939999999</v>
-      </c>
-      <c r="N101">
-        <v>-74.76647939999999</v>
-      </c>
-      <c r="O101">
-        <v>-18.69161985</v>
-      </c>
-      <c r="P101">
-        <v>-56.07485955</v>
-      </c>
-      <c r="Q101">
-        <v>-55.55485955</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.215166263773085</v>
-      </c>
-      <c r="T101">
-        <v>88.6747797558959</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01148450213523309</v>
-      </c>
-      <c r="W101">
-        <v>0.233091954396512</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04593800854093233</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
